--- a/data/fondi-pensione-covip.xlsx
+++ b/data/fondi-pensione-covip.xlsx
@@ -10,11 +10,13 @@
     <sheet name="Comparti" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Regole" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Longevita" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Glossario" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$2:$Q$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparti'!$A$1:$J$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regole'!$A$1:$M$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Glossario'!$A$1:$H$50</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -11209,4 +11211,1866 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="66" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="66" t="inlineStr">
+        <is>
+          <t>Gruppo</t>
+        </is>
+      </c>
+      <c r="C1" s="66" t="inlineStr">
+        <is>
+          <t>Termine</t>
+        </is>
+      </c>
+      <c r="D1" s="66" t="inlineStr">
+        <is>
+          <t>Per esteso</t>
+        </is>
+      </c>
+      <c r="E1" s="66" t="inlineStr">
+        <is>
+          <t>Definizione</t>
+        </is>
+      </c>
+      <c r="F1" s="66" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="G1" s="66" t="inlineStr">
+        <is>
+          <t>Consultata il</t>
+        </is>
+      </c>
+      <c r="H1" s="66" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="67" t="inlineStr">
+        <is>
+          <t>fondo-pensione-aperto</t>
+        </is>
+      </c>
+      <c r="B2" s="67" t="inlineStr">
+        <is>
+          <t>Fondi e documenti</t>
+        </is>
+      </c>
+      <c r="C2" s="67" t="inlineStr">
+        <is>
+          <t>Fondo pensione aperto</t>
+        </is>
+      </c>
+      <c r="D2" s="67" t="n"/>
+      <c r="E2" s="67" t="inlineStr">
+        <is>
+          <t>Fondo pensione istituito da una banca, una SGR, una SIM o un'assicurazione e aperto a tutti, anche a chi non lavora. Si aderisce da soli (adesione individuale) oppure tramite un accordo aziendale (adesione collettiva).</t>
+        </is>
+      </c>
+      <c r="F2" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G2" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H2" s="67" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="67" t="inlineStr">
+        <is>
+          <t>fondo-negoziale</t>
+        </is>
+      </c>
+      <c r="B3" s="67" t="inlineStr">
+        <is>
+          <t>Fondi e documenti</t>
+        </is>
+      </c>
+      <c r="C3" s="67" t="inlineStr">
+        <is>
+          <t>Fondo negoziale (chiuso)</t>
+        </is>
+      </c>
+      <c r="D3" s="67" t="n"/>
+      <c r="E3" s="67" t="inlineStr">
+        <is>
+          <t>Fondo pensione istituito da contratti o accordi collettivi per i lavoratori di una categoria, di un settore o di un'azienda. Di solito è il fondo a cui il datore di lavoro versa il proprio contributo: aderendo a un fondo aperto si può perderlo.</t>
+        </is>
+      </c>
+      <c r="F3" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G3" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H3" s="67" t="inlineStr">
+        <is>
+          <t>Sul contributo del datore di lavoro: Guida introduttiva COVIP (2018), p. 25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="67" t="inlineStr">
+        <is>
+          <t>albo-covip</t>
+        </is>
+      </c>
+      <c r="B4" s="67" t="inlineStr">
+        <is>
+          <t>Fondi e documenti</t>
+        </is>
+      </c>
+      <c r="C4" s="67" t="inlineStr">
+        <is>
+          <t>Albo COVIP</t>
+        </is>
+      </c>
+      <c r="D4" s="67" t="inlineStr">
+        <is>
+          <t>COVIP: Commissione di vigilanza sui fondi pensione</t>
+        </is>
+      </c>
+      <c r="E4" s="67" t="inlineStr">
+        <is>
+          <t>La COVIP è l'autorità pubblica che vigila sui fondi pensione. L'Albo è il suo elenco ufficiale delle forme pensionistiche complementari: questa dashboard parte dai fondi pensione aperti iscritti all'Albo.</t>
+        </is>
+      </c>
+      <c r="F4" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G4" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H4" s="67" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="67" t="inlineStr">
+        <is>
+          <t>contribuzione-definita</t>
+        </is>
+      </c>
+      <c r="B5" s="67" t="inlineStr">
+        <is>
+          <t>Fondi e documenti</t>
+        </is>
+      </c>
+      <c r="C5" s="67" t="inlineStr">
+        <is>
+          <t>Contribuzione definita</t>
+        </is>
+      </c>
+      <c r="D5" s="67" t="n"/>
+      <c r="E5" s="67" t="inlineStr">
+        <is>
+          <t>Si sa quanto si versa, non quanto si riceverà: la pensione complementare dipende dai contributi versati e dai risultati degli investimenti, al netto dei costi. Non c'è un importo garantito, salvo nei comparti con garanzia.</t>
+        </is>
+      </c>
+      <c r="F5" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G5" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H5" s="67" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="67" t="inlineStr">
+        <is>
+          <t>adesione</t>
+        </is>
+      </c>
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>Fondi e documenti</t>
+        </is>
+      </c>
+      <c r="C6" s="67" t="inlineStr">
+        <is>
+          <t>Adesione individuale e collettiva</t>
+        </is>
+      </c>
+      <c r="D6" s="67" t="n"/>
+      <c r="E6" s="67" t="inlineStr">
+        <is>
+          <t>Individuale: ti iscrivi tu, al fondo che scegli, qualunque lavoro tu faccia. Collettiva: l'iscrizione avviene in base a un accordo tra azienda e lavoratori, anche verso un fondo aperto. Alcune regole, per esempio sul riscatto, cambiano tra le due.</t>
+        </is>
+      </c>
+      <c r="F6" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G6" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H6" s="67" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="67" t="inlineStr">
+        <is>
+          <t>posizione-individuale</t>
+        </is>
+      </c>
+      <c r="B7" s="67" t="inlineStr">
+        <is>
+          <t>Fondi e documenti</t>
+        </is>
+      </c>
+      <c r="C7" s="67" t="inlineStr">
+        <is>
+          <t>Posizione individuale (montante)</t>
+        </is>
+      </c>
+      <c r="D7" s="67" t="n"/>
+      <c r="E7" s="67" t="inlineStr">
+        <is>
+          <t>Il valore del tuo conto nel fondo: i contributi versati più i rendimenti, meno i costi e gli eventuali prelievi. Al momento della pensione si parla anche di montante.</t>
+        </is>
+      </c>
+      <c r="F7" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G7" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H7" s="67" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="67" t="inlineStr">
+        <is>
+          <t>nota-informativa</t>
+        </is>
+      </c>
+      <c r="B8" s="67" t="inlineStr">
+        <is>
+          <t>Fondi e documenti</t>
+        </is>
+      </c>
+      <c r="C8" s="67" t="inlineStr">
+        <is>
+          <t>Nota informativa</t>
+        </is>
+      </c>
+      <c r="D8" s="67" t="n"/>
+      <c r="E8" s="67" t="inlineStr">
+        <is>
+          <t>Il documento ufficiale che descrive il fondo: comparti, costi, rendimenti passati e prestazioni. Segue uno schema fissato dalla COVIP, è pubblicato sul sito del fondo e va letto prima di aderire. In appendice c'è l'Informativa sulla sostenibilità.</t>
+        </is>
+      </c>
+      <c r="F8" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G8" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H8" s="67" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="67" t="inlineStr">
+        <is>
+          <t>scheda-costi</t>
+        </is>
+      </c>
+      <c r="B9" s="67" t="inlineStr">
+        <is>
+          <t>Fondi e documenti</t>
+        </is>
+      </c>
+      <c r="C9" s="67" t="inlineStr">
+        <is>
+          <t>Scheda dei costi</t>
+        </is>
+      </c>
+      <c r="D9" s="67" t="n"/>
+      <c r="E9" s="67" t="inlineStr">
+        <is>
+          <t>La parte della Nota informativa che elenca tutti i costi del fondo, con l'ISC. Viene consegnata prima dell'adesione: per confrontare i costi di due fondi la COVIP consiglia di confrontarne le schede.</t>
+        </is>
+      </c>
+      <c r="F9" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Guida introduttiva alla previdenza complementare (settembre 2018)</t>
+        </is>
+      </c>
+      <c r="G9" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H9" s="67" t="inlineStr">
+        <is>
+          <t>Guida introduttiva COVIP, pp. 16 e 25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>ciao-elsa</t>
+        </is>
+      </c>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>Fondi e documenti</t>
+        </is>
+      </c>
+      <c r="C10" s="67" t="inlineStr">
+        <is>
+          <t>Ciao Elsa</t>
+        </is>
+      </c>
+      <c r="D10" s="67" t="n"/>
+      <c r="E10" s="67" t="inlineStr">
+        <is>
+          <t>Sito di Elsa Srl che spiega la previdenza complementare, confronta i fondi pensione e per alcuni fondi aperti permette di aderire online. In questa dashboard è la fonte secondaria dei dati di dettaglio: vanno verificati sulla Nota informativa.</t>
+        </is>
+      </c>
+      <c r="F10" s="68" t="inlineStr">
+        <is>
+          <t>Ciao Elsa – home page (“Ma chi è Ciao Elsa?”)</t>
+        </is>
+      </c>
+      <c r="G10" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H10" s="67" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="67" t="inlineStr">
+        <is>
+          <t>sottoscrizione-online</t>
+        </is>
+      </c>
+      <c r="B11" s="67" t="inlineStr">
+        <is>
+          <t>Fondi e documenti</t>
+        </is>
+      </c>
+      <c r="C11" s="67" t="inlineStr">
+        <is>
+          <t>Sottoscrizione online</t>
+        </is>
+      </c>
+      <c r="D11" s="67" t="n"/>
+      <c r="E11" s="67" t="inlineStr">
+        <is>
+          <t>Adesione al fondo via internet tramite Ciao Elsa, che fa da broker: identificazione con SPID o CIE e questionario di autovalutazione COVIP. “Lista d'attesa” vuol dire che il fondo non è ancora sottoscrivibile su Ciao Elsa: ci si può iscrivere per essere avvisati.</t>
+        </is>
+      </c>
+      <c r="F11" s="68" t="inlineStr">
+        <is>
+          <t>Ciao Elsa – Sottoscrizione di fondi pensione su Ciao Elsa</t>
+        </is>
+      </c>
+      <c r="G11" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H11" s="67" t="inlineStr">
+        <is>
+          <t>La lista d'attesa è indicata nelle schede dei fondi di Ciao Elsa (es. Previdenza per Te di AXA MPS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>comparto</t>
+        </is>
+      </c>
+      <c r="B12" s="67" t="inlineStr">
+        <is>
+          <t>Investimento</t>
+        </is>
+      </c>
+      <c r="C12" s="67" t="inlineStr">
+        <is>
+          <t>Comparto (linea di investimento)</t>
+        </is>
+      </c>
+      <c r="D12" s="67" t="n"/>
+      <c r="E12" s="67" t="inlineStr">
+        <is>
+          <t>Una delle opzioni di investimento offerte dal fondo, con una propria politica di investimento e quindi un proprio livello di rischio e di rendimento atteso. Il fondo può consentire di dividere i versamenti tra più comparti.</t>
+        </is>
+      </c>
+      <c r="F12" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G12" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H12" s="67" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="67" t="inlineStr">
+        <is>
+          <t>azn</t>
+        </is>
+      </c>
+      <c r="B13" s="67" t="inlineStr">
+        <is>
+          <t>Investimento</t>
+        </is>
+      </c>
+      <c r="C13" s="67" t="inlineStr">
+        <is>
+          <t>AZN</t>
+        </is>
+      </c>
+      <c r="D13" s="67" t="inlineStr">
+        <is>
+          <t>Azionario</t>
+        </is>
+      </c>
+      <c r="E13" s="67" t="inlineStr">
+        <is>
+          <t>Comparto che investe solo o principalmente in azioni: nel lungo periodo può rendere di più, ma il suo valore può oscillare molto da un anno all'altro, anche in negativo. Per la COVIP un comparto è azionario se almeno il 50% è investito in azioni.</t>
+        </is>
+      </c>
+      <c r="F13" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G13" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H13" s="67" t="inlineStr">
+        <is>
+          <t>Sigla della categoria usata da Ciao Elsa. Rischio e rendimento: Guida introduttiva COVIP, p. 21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="67" t="inlineStr">
+        <is>
+          <t>bil</t>
+        </is>
+      </c>
+      <c r="B14" s="67" t="inlineStr">
+        <is>
+          <t>Investimento</t>
+        </is>
+      </c>
+      <c r="C14" s="67" t="inlineStr">
+        <is>
+          <t>BIL</t>
+        </is>
+      </c>
+      <c r="D14" s="67" t="inlineStr">
+        <is>
+          <t>Bilanciato</t>
+        </is>
+      </c>
+      <c r="E14" s="67" t="inlineStr">
+        <is>
+          <t>Comparto che investe sia in azioni sia in obbligazioni, in linea di massima in proporzioni simili: rischio e rendimento atteso intermedi. Per la COVIP è bilanciato un comparto con più del 30% e meno del 50% di azioni.</t>
+        </is>
+      </c>
+      <c r="F14" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G14" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H14" s="67" t="inlineStr">
+        <is>
+          <t>Sigla e categoria di Ciao Elsa, che non sempre segue le soglie COVIP: diversi comparti BIL hanno il 50% di azioni o più, e per la COVIP sarebbero azionari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="67" t="inlineStr">
+        <is>
+          <t>obb</t>
+        </is>
+      </c>
+      <c r="B15" s="67" t="inlineStr">
+        <is>
+          <t>Investimento</t>
+        </is>
+      </c>
+      <c r="C15" s="67" t="inlineStr">
+        <is>
+          <t>OBB</t>
+        </is>
+      </c>
+      <c r="D15" s="67" t="inlineStr">
+        <is>
+          <t>Obbligazionario (misto o puro)</t>
+        </is>
+      </c>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>Comparto che investe soprattutto in obbligazioni: rendimenti attesi più contenuti e oscillazioni ridotte. “Puro”: solo obbligazioni, niente azioni. “Misto”: anche azioni, ma al massimo il 30%.</t>
+        </is>
+      </c>
+      <c r="F15" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G15" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H15" s="67" t="inlineStr">
+        <is>
+          <t>Sigle di Ciao Elsa (OBB PURO, OBB MISTO), che non sempre seguono le soglie COVIP: alcuni OBB PURO hanno una piccola quota di azioni, e molti comparti con garanzia sono classificati come OBB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>gar</t>
+        </is>
+      </c>
+      <c r="B16" s="67" t="inlineStr">
+        <is>
+          <t>Investimento</t>
+        </is>
+      </c>
+      <c r="C16" s="67" t="inlineStr">
+        <is>
+          <t>GAR</t>
+        </is>
+      </c>
+      <c r="D16" s="67" t="inlineStr">
+        <is>
+          <t>Garantito</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="inlineStr">
+        <is>
+          <t>Comparto che garantisce la restituzione del capitale versato o un rendimento minimo, ma solo in certi casi previsti dal regolamento, per esempio al pensionamento.</t>
+        </is>
+      </c>
+      <c r="F16" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G16" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H16" s="67" t="inlineStr">
+        <is>
+          <t>Ciao Elsa usa la categoria GAR per pochi comparti: molti comparti con garanzia sono classificati come obbligazionari (OBB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>asset-allocation</t>
+        </is>
+      </c>
+      <c r="B17" s="67" t="inlineStr">
+        <is>
+          <t>Investimento</t>
+        </is>
+      </c>
+      <c r="C17" s="67" t="inlineStr">
+        <is>
+          <t>Asset allocation</t>
+        </is>
+      </c>
+      <c r="D17" s="67" t="n"/>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>Come è diviso il patrimonio di un comparto tra azioni (quote di società: possono rendere di più, ma oscillano molto) e obbligazioni (titoli di debito di Stati e imprese, che pagano interessi: oscillazioni più contenute). Più azioni vuol dire più rischio e più rendimento atteso nel lungo periodo.</t>
+        </is>
+      </c>
+      <c r="F17" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Guida introduttiva alla previdenza complementare (settembre 2018)</t>
+        </is>
+      </c>
+      <c r="G17" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H17" s="67" t="inlineStr">
+        <is>
+          <t>Guida introduttiva COVIP, pp. 17 e 21–22: composizione del portafoglio in titoli azionari e obbligazionari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="67" t="inlineStr">
+        <is>
+          <t>esg</t>
+        </is>
+      </c>
+      <c r="B18" s="67" t="inlineStr">
+        <is>
+          <t>Investimento</t>
+        </is>
+      </c>
+      <c r="C18" s="67" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D18" s="67" t="inlineStr">
+        <is>
+          <t>Environmental, Social, Governance</t>
+        </is>
+      </c>
+      <c r="E18" s="67" t="inlineStr">
+        <is>
+          <t>Fattori ambientali (es. emissioni di CO2, inquinamento), sociali (es. diritti umani, condizioni di lavoro) e di governo delle imprese (es. compensi dei manager) usati per valutare la sostenibilità degli investimenti nel lungo periodo.</t>
+        </is>
+      </c>
+      <c r="F18" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G18" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H18" s="67" t="inlineStr">
+        <is>
+          <t>Nella dashboard “ESG” vuol dire che, secondo Ciao Elsa, il fondo ha almeno una linea che prevede investimenti sostenibili. Quali comparti promuovono caratteristiche ambientali o sociali, o hanno obiettivi di investimento sostenibile, lo dice l'Informativa sulla sostenibilità allegata alla Nota informativa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>life-cycle</t>
+        </is>
+      </c>
+      <c r="B19" s="67" t="inlineStr">
+        <is>
+          <t>Investimento</t>
+        </is>
+      </c>
+      <c r="C19" s="67" t="inlineStr">
+        <is>
+          <t>Life cycle</t>
+        </is>
+      </c>
+      <c r="D19" s="67" t="n"/>
+      <c r="E19" s="67" t="inlineStr">
+        <is>
+          <t>Percorso che sposta automaticamente l'investimento verso comparti più prudenti man mano che ci si avvicina alla pensione, tenendo conto dell'età e degli anni che mancano. Dal 1° luglio 2026 è la destinazione dei versamenti di chi aderisce in modo automatico.</t>
+        </is>
+      </c>
+      <c r="F19" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G19" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H19" s="67" t="inlineStr">
+        <is>
+          <t>Nella dashboard “Life cycle” vuol dire che, secondo Ciao Elsa, il fondo offre questa opzione.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="67" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
+      <c r="B20" s="67" t="inlineStr">
+        <is>
+          <t>Investimento</t>
+        </is>
+      </c>
+      <c r="C20" s="67" t="inlineStr">
+        <is>
+          <t>Switch (cambio di comparto)</t>
+        </is>
+      </c>
+      <c r="D20" s="67" t="n"/>
+      <c r="E20" s="67" t="inlineStr">
+        <is>
+          <t>Spostare la posizione, o i versamenti futuri, da un comparto all'altro dello stesso fondo. La scelta del comparto non è vincolante, ma tra un cambio e l'altro va rispettato il periodo minimo previsto dal regolamento del fondo.</t>
+        </is>
+      </c>
+      <c r="F20" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Guida introduttiva alla previdenza complementare (settembre 2018)</t>
+        </is>
+      </c>
+      <c r="G20" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H20" s="67" t="inlineStr">
+        <is>
+          <t>Guida introduttiva COVIP, pp. 22 e 24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>spese-adesione</t>
+        </is>
+      </c>
+      <c r="B21" s="67" t="inlineStr">
+        <is>
+          <t>Costi e rendimenti</t>
+        </is>
+      </c>
+      <c r="C21" s="67" t="inlineStr">
+        <is>
+          <t>Spese di adesione</t>
+        </is>
+      </c>
+      <c r="D21" s="67" t="n"/>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>Costo pagato una sola volta, quando ti iscrivi. Pesa poco se resti nel fondo a lungo, molto se ci resti pochi anni.</t>
+        </is>
+      </c>
+      <c r="F21" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G21" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H21" s="67" t="inlineStr">
+        <is>
+          <t>Nella definizione dell'ISC è il “costo di iscrizione”, il cui peso diminuisce con gli anni di permanenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="67" t="inlineStr">
+        <is>
+          <t>spese-annue</t>
+        </is>
+      </c>
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t>Costi e rendimenti</t>
+        </is>
+      </c>
+      <c r="C22" s="67" t="inlineStr">
+        <is>
+          <t>Spese annue fisse</t>
+        </is>
+      </c>
+      <c r="D22" s="67" t="n"/>
+      <c r="E22" s="67" t="inlineStr">
+        <is>
+          <t>Importo fisso in euro prelevato ogni anno dalla posizione, qualunque sia il suo valore: pesa di più all'inizio, quando la posizione è piccola.</t>
+        </is>
+      </c>
+      <c r="F22" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G22" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H22" s="67" t="inlineStr">
+        <is>
+          <t>Nella definizione dell'ISC è la “spesa annua in cifra fissa”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="67" t="inlineStr">
+        <is>
+          <t>costo-versato</t>
+        </is>
+      </c>
+      <c r="B23" s="67" t="inlineStr">
+        <is>
+          <t>Costi e rendimenti</t>
+        </is>
+      </c>
+      <c r="C23" s="67" t="inlineStr">
+        <is>
+          <t>Costo % sul versato</t>
+        </is>
+      </c>
+      <c r="D23" s="67" t="n"/>
+      <c r="E23" s="67" t="inlineStr">
+        <is>
+          <t>Percentuale trattenuta da ogni versamento prima che venga investito: per esempio, lo 0,5% vuol dire 5 € ogni 1.000 € versati.</t>
+        </is>
+      </c>
+      <c r="F23" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G23" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H23" s="67" t="inlineStr">
+        <is>
+          <t>Nella definizione dell'ISC è la “spesa in percentuale sui versamenti”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="67" t="inlineStr">
+        <is>
+          <t>commissione-gestione</t>
+        </is>
+      </c>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>Costi e rendimenti</t>
+        </is>
+      </c>
+      <c r="C24" s="67" t="inlineStr">
+        <is>
+          <t>Commissione di gestione</t>
+        </is>
+      </c>
+      <c r="D24" s="67" t="n"/>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>Percentuale del patrimonio del comparto trattenuta ogni anno per gestirlo: per esempio, l'1% vuol dire 10 € l'anno ogni 1.000 € investiti. Si paga su tutto ciò che hai accumulato, quindi nel lungo periodo anche piccole differenze riducono molto la pensione.</t>
+        </is>
+      </c>
+      <c r="F24" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G24" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H24" s="67" t="inlineStr">
+        <is>
+          <t>Nella definizione dell'ISC sono le “commissioni in percentuale sul patrimonio”. Effetto delle piccole differenze di costo: Guida introduttiva COVIP, p. 25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="67" t="inlineStr">
+        <is>
+          <t>isc</t>
+        </is>
+      </c>
+      <c r="B25" s="67" t="inlineStr">
+        <is>
+          <t>Costi e rendimenti</t>
+        </is>
+      </c>
+      <c r="C25" s="67" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="D25" s="67" t="inlineStr">
+        <is>
+          <t>Indicatore sintetico dei costi</t>
+        </is>
+      </c>
+      <c r="E25" s="67" t="inlineStr">
+        <is>
+          <t>Tutti i costi di un comparto riassunti in un'unica percentuale: di quanto riducono ogni anno il rendimento. La COVIP lo calcola allo stesso modo per tutti i fondi, per 2, 5, 10 e 35 anni di permanenza (versamento di 2.500 € l'anno, rendimento ipotetico del 4%): è il modo ufficiale per confrontare i costi tra fondi.</t>
+        </is>
+      </c>
+      <c r="F25" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G25" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H25" s="67" t="inlineStr">
+        <is>
+          <t>Si trova nella Scheda dei costi di ogni fondo e nel Comparatore dei costi sul sito della COVIP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="67" t="inlineStr">
+        <is>
+          <t>rendimento-netto</t>
+        </is>
+      </c>
+      <c r="B26" s="67" t="inlineStr">
+        <is>
+          <t>Costi e rendimenti</t>
+        </is>
+      </c>
+      <c r="C26" s="67" t="inlineStr">
+        <is>
+          <t>Rendimento netto medio annuo</t>
+        </is>
+      </c>
+      <c r="D26" s="67" t="n"/>
+      <c r="E26" s="67" t="inlineStr">
+        <is>
+          <t>Di quanto è cresciuto in media, ogni anno, il valore del comparto, già al netto di costi e tasse, su un periodo dato (qui di solito 10 anni, per alcuni comparti 3 o 5). Si confrontano solo rendimenti dello stesso periodo, e quelli passati non garantiscono quelli futuri.</t>
+        </is>
+      </c>
+      <c r="F26" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Guida introduttiva alla previdenza complementare (settembre 2018)</t>
+        </is>
+      </c>
+      <c r="G26" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H26" s="67" t="inlineStr">
+        <is>
+          <t>Guida introduttiva COVIP, p. 17 (rendimenti medi annui composti a 3, 5 e 10 anni) e p. 8 (rendimenti al netto della fiscalità).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="67" t="inlineStr">
+        <is>
+          <t>tfr</t>
+        </is>
+      </c>
+      <c r="B27" s="67" t="inlineStr">
+        <is>
+          <t>Versamenti e uscite anticipate</t>
+        </is>
+      </c>
+      <c r="C27" s="67" t="inlineStr">
+        <is>
+          <t>TFR</t>
+        </is>
+      </c>
+      <c r="D27" s="67" t="inlineStr">
+        <is>
+          <t>Trattamento di fine rapporto</t>
+        </is>
+      </c>
+      <c r="E27" s="67" t="inlineStr">
+        <is>
+          <t>La liquidazione che il datore di lavoro accantona ogni anno per il dipendente, circa il 6,91% della retribuzione lorda, e paga alla fine del rapporto di lavoro. Si può lasciare in azienda, dove si rivaluta dell'1,5% più il 75% dell'inflazione, oppure versare al fondo pensione.</t>
+        </is>
+      </c>
+      <c r="F27" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G27" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H27" s="67" t="inlineStr">
+        <is>
+          <t>6,91% della retribuzione lorda: esempi della Guida introduttiva COVIP (2018).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="67" t="inlineStr">
+        <is>
+          <t>deducibilita</t>
+        </is>
+      </c>
+      <c r="B28" s="67" t="inlineStr">
+        <is>
+          <t>Versamenti e uscite anticipate</t>
+        </is>
+      </c>
+      <c r="C28" s="67" t="inlineStr">
+        <is>
+          <t>Deducibilità</t>
+        </is>
+      </c>
+      <c r="D28" s="67" t="n"/>
+      <c r="E28" s="67" t="inlineStr">
+        <is>
+          <t>I contributi versati al fondo (escluso il TFR) si sottraggono dal reddito su cui si calcolano le tasse, fino a 5.300 € l'anno dal 2026: si risparmia IRPEF secondo la propria aliquota.</t>
+        </is>
+      </c>
+      <c r="F28" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G28" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H28" s="67" t="inlineStr">
+        <is>
+          <t>Limite annuo: Legge 199/2025 (vedi Regole, “Deducibilità”).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="67" t="inlineStr">
+        <is>
+          <t>anticipazione</t>
+        </is>
+      </c>
+      <c r="B29" s="67" t="inlineStr">
+        <is>
+          <t>Versamenti e uscite anticipate</t>
+        </is>
+      </c>
+      <c r="C29" s="67" t="inlineStr">
+        <is>
+          <t>Anticipazione</t>
+        </is>
+      </c>
+      <c r="D29" s="67" t="n"/>
+      <c r="E29" s="67" t="inlineStr">
+        <is>
+          <t>Una parte della posizione chiesta prima della pensione per spese sanitarie gravi, per la prima casa o per altre esigenze, nei limiti di legge. Riduce la pensione futura, ma si può reintegrare rimettendo i soldi nel fondo.</t>
+        </is>
+      </c>
+      <c r="F29" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G29" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H29" s="67" t="inlineStr">
+        <is>
+          <t>Limiti, tempi e tasse: vedi Regole, tema “Prima della pensione”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="67" t="inlineStr">
+        <is>
+          <t>riscatto</t>
+        </is>
+      </c>
+      <c r="B30" s="67" t="inlineStr">
+        <is>
+          <t>Versamenti e uscite anticipate</t>
+        </is>
+      </c>
+      <c r="C30" s="67" t="inlineStr">
+        <is>
+          <t>Riscatto</t>
+        </is>
+      </c>
+      <c r="D30" s="67" t="n"/>
+      <c r="E30" s="67" t="inlineStr">
+        <is>
+          <t>Il ritiro in un'unica soluzione, prima della pensione, del 50% o di tutta la posizione, in casi precisi: perdita del lavoro, invalidità, perdita dei requisiti di partecipazione. In caso di decesso la posizione viene riscattata dai beneficiari o dagli eredi.</t>
+        </is>
+      </c>
+      <c r="F30" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G30" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H30" s="67" t="inlineStr">
+        <is>
+          <t>Decesso: D.Lgs. 252/2005, art. 14 c. 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="67" t="inlineStr">
+        <is>
+          <t>rita</t>
+        </is>
+      </c>
+      <c r="B31" s="67" t="inlineStr">
+        <is>
+          <t>Versamenti e uscite anticipate</t>
+        </is>
+      </c>
+      <c r="C31" s="67" t="inlineStr">
+        <is>
+          <t>RITA</t>
+        </is>
+      </c>
+      <c r="D31" s="67" t="inlineStr">
+        <is>
+          <t>Rendita integrativa temporanea anticipata</t>
+        </is>
+      </c>
+      <c r="E31" s="67" t="inlineStr">
+        <is>
+          <t>La posizione pagata a rate fino all'età della pensione di vecchiaia, per chi ha smesso di lavorare e ne è vicino: al massimo 5 anni, o 10 se è senza lavoro da più di 24 mesi. Servono almeno 5 anni di partecipazione.</t>
+        </is>
+      </c>
+      <c r="F31" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G31" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H31" s="67" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="67" t="inlineStr">
+        <is>
+          <t>trasferimento</t>
+        </is>
+      </c>
+      <c r="B32" s="67" t="inlineStr">
+        <is>
+          <t>Versamenti e uscite anticipate</t>
+        </is>
+      </c>
+      <c r="C32" s="67" t="inlineStr">
+        <is>
+          <t>Trasferimento</t>
+        </is>
+      </c>
+      <c r="D32" s="67" t="n"/>
+      <c r="E32" s="67" t="inlineStr">
+        <is>
+          <t>Spostare tutta la posizione in un altro fondo pensione: si può dopo 2 anni di iscrizione, o prima se cambi lavoro. Non si pagano tasse e l'anzianità di iscrizione si conserva.</t>
+        </is>
+      </c>
+      <c r="F32" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G32" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H32" s="67" t="inlineStr">
+        <is>
+          <t>Il fondo che lasci può applicare una spesa fissa per il trasferimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="67" t="inlineStr">
+        <is>
+          <t>capitale</t>
+        </is>
+      </c>
+      <c r="B33" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C33" s="67" t="inlineStr">
+        <is>
+          <t>Prestazione in capitale</t>
+        </is>
+      </c>
+      <c r="D33" s="67" t="n"/>
+      <c r="E33" s="67" t="inlineStr">
+        <is>
+          <t>La parte della posizione che alla pensione si riceve subito, in un'unica soluzione: fino al 50% del montante. Si può avere tutto in capitale solo se la rendita sarebbe molto bassa oppure per i “vecchi iscritti”.</t>
+        </is>
+      </c>
+      <c r="F33" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G33" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H33" s="67" t="inlineStr">
+        <is>
+          <t>Il 60% annunciato dalla Legge 199/2025 non è mai entrato in vigore: vedi Regole, “Capitale”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="67" t="inlineStr">
+        <is>
+          <t>vecchio-iscritto</t>
+        </is>
+      </c>
+      <c r="B34" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C34" s="67" t="inlineStr">
+        <is>
+          <t>Vecchio iscritto</t>
+        </is>
+      </c>
+      <c r="D34" s="67" t="n"/>
+      <c r="E34" s="67" t="inlineStr">
+        <is>
+          <t>Chi, assunto prima del 29 aprile 1993, entro quella data era già iscritto a un fondo pensione esistente al 15 novembre 1992. Alla pensione può prendere tutta la prestazione in capitale; la condizione si perde con il riscatto dell'intera posizione.</t>
+        </is>
+      </c>
+      <c r="F34" s="68" t="inlineStr">
+        <is>
+          <t>D.Lgs. 252/2005 – testo COVIP aggiornato alla Legge 199/2025</t>
+        </is>
+      </c>
+      <c r="G34" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H34" s="67" t="inlineStr">
+        <is>
+          <t>Art. 23 c. 7 del D.Lgs. 252/2005 e Guida introduttiva COVIP, p. 26. Il glossario COVIP (voce “Iscritti”) lo descrive in modo diverso: iscritto alla previdenza obbligatoria prima del 29/4/1993 e alla complementare prima dell'entrata in vigore della Legge 421/1992.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="67" t="inlineStr">
+        <is>
+          <t>rendita-vitalizia</t>
+        </is>
+      </c>
+      <c r="B35" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C35" s="67" t="inlineStr">
+        <is>
+          <t>Rendita vitalizia</t>
+        </is>
+      </c>
+      <c r="D35" s="67" t="n"/>
+      <c r="E35" s="67" t="inlineStr">
+        <is>
+          <t>Una pensione pagata per tutta la vita, dal fondo o da un'assicurazione convenzionata, in cambio del montante. Protegge dal rischio di longevità; nella forma base, alla morte il capitale residuo non viene restituito.</t>
+        </is>
+      </c>
+      <c r="F35" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G35" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H35" s="67" t="inlineStr">
+        <is>
+          <t>Forma base e varianti: Esempio COVIP di supplemento alla Nota informativa (28/7/2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="67" t="inlineStr">
+        <is>
+          <t>coefficiente-trasformazione</t>
+        </is>
+      </c>
+      <c r="B36" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C36" s="67" t="inlineStr">
+        <is>
+          <t>Coefficiente di trasformazione</t>
+        </is>
+      </c>
+      <c r="D36" s="67" t="n"/>
+      <c r="E36" s="67" t="inlineStr">
+        <is>
+          <t>Il numero che trasforma il montante in rendita annua. Dipende dall'età alla pensione, dalla speranza di vita, dal tasso tecnico e dai costi, e cambia da fondo a fondo: a parità di montante, un coefficiente più alto dà una rendita più alta.</t>
+        </is>
+      </c>
+      <c r="F36" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G36" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H36" s="67" t="inlineStr">
+        <is>
+          <t>Da cosa dipende: Guida introduttiva COVIP, p. 27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="67" t="inlineStr">
+        <is>
+          <t>tasso-tecnico</t>
+        </is>
+      </c>
+      <c r="B37" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C37" s="67" t="inlineStr">
+        <is>
+          <t>Tasso tecnico</t>
+        </is>
+      </c>
+      <c r="D37" s="67" t="n"/>
+      <c r="E37" s="67" t="inlineStr">
+        <is>
+          <t>Il rendimento minimo garantito considerato nel calcolo della rendita, al momento in cui viene fissata. È uno degli elementi del coefficiente di trasformazione.</t>
+        </is>
+      </c>
+      <c r="F37" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Guida introduttiva alla previdenza complementare (settembre 2018)</t>
+        </is>
+      </c>
+      <c r="G37" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H37" s="67" t="inlineStr">
+        <is>
+          <t>Guida introduttiva COVIP, p. 27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="67" t="inlineStr">
+        <is>
+          <t>rendita-reversibile</t>
+        </is>
+      </c>
+      <c r="B38" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C38" s="67" t="inlineStr">
+        <is>
+          <t>Rendita reversibile</t>
+        </is>
+      </c>
+      <c r="D38" s="67" t="n"/>
+      <c r="E38" s="67" t="inlineStr">
+        <is>
+          <t>Rendita vitalizia che, alla tua morte, continua in tutto o in parte a una persona che hai indicato. La rata è più bassa di quella della rendita vitalizia base.</t>
+        </is>
+      </c>
+      <c r="F38" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Esempio di supplemento alla Nota informativa per i fondi aperti (28 luglio 2026)</t>
+        </is>
+      </c>
+      <c r="G38" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H38" s="67" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="67" t="inlineStr">
+        <is>
+          <t>rendita-certa</t>
+        </is>
+      </c>
+      <c r="B39" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C39" s="67" t="inlineStr">
+        <is>
+          <t>Rendita certa e poi vitalizia</t>
+        </is>
+      </c>
+      <c r="D39" s="67" t="n"/>
+      <c r="E39" s="67" t="inlineStr">
+        <is>
+          <t>Rendita pagata comunque per un numero definito di anni, anche alla persona che hai indicato se muori prima, e poi per tutta la vita. La rata è più bassa di quella della rendita vitalizia base.</t>
+        </is>
+      </c>
+      <c r="F39" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Esempio di supplemento alla Nota informativa per i fondi aperti (28 luglio 2026)</t>
+        </is>
+      </c>
+      <c r="G39" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H39" s="67" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="67" t="inlineStr">
+        <is>
+          <t>rendita-controassicurata</t>
+        </is>
+      </c>
+      <c r="B40" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C40" s="67" t="inlineStr">
+        <is>
+          <t>Rendita controassicurata</t>
+        </is>
+      </c>
+      <c r="D40" s="67" t="n"/>
+      <c r="E40" s="67" t="inlineStr">
+        <is>
+          <t>Rendita vitalizia con restituzione del capitale: alla tua morte, la persona che hai indicato riceve il capitale residuo non ancora pagato. La rata è più bassa di quella della rendita vitalizia base.</t>
+        </is>
+      </c>
+      <c r="F40" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Esempio di supplemento alla Nota informativa per i fondi aperti (28 luglio 2026)</t>
+        </is>
+      </c>
+      <c r="G40" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H40" s="67" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="67" t="inlineStr">
+        <is>
+          <t>ltc</t>
+        </is>
+      </c>
+      <c r="B41" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C41" s="67" t="inlineStr">
+        <is>
+          <t>LTC</t>
+        </is>
+      </c>
+      <c r="D41" s="67" t="inlineStr">
+        <is>
+          <t>Long-term care</t>
+        </is>
+      </c>
+      <c r="E41" s="67" t="inlineStr">
+        <is>
+          <t>Copertura assicurativa abbinata alla rendita, che la aumenta se si perde l'autosufficienza.</t>
+        </is>
+      </c>
+      <c r="F41" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G41" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H41" s="67" t="inlineStr">
+        <is>
+          <t>Rendita con copertura LTC: Guida introduttiva COVIP, p. 27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="67" t="inlineStr">
+        <is>
+          <t>rendita-durata-definita</t>
+        </is>
+      </c>
+      <c r="B42" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C42" s="67" t="inlineStr">
+        <is>
+          <t>Rendita a durata definita</t>
+        </is>
+      </c>
+      <c r="D42" s="67" t="n"/>
+      <c r="E42" s="67" t="inlineStr">
+        <is>
+          <t>Dal 1° luglio 2026, alternativa alla vitalizia: rate per un numero di anni pari alla vita attesa secondo le tavole ISTAT. Il capitale resta investito, ogni rata è il residuo diviso per le rate che mancano, e alla morte il residuo va ai beneficiari.</t>
+        </is>
+      </c>
+      <c r="F42" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G42" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H42" s="67" t="inlineStr">
+        <is>
+          <t>Non protegge da una vita più lunga del previsto: vedi Regole e il grafico della longevità.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="67" t="inlineStr">
+        <is>
+          <t>prelievi-liberi</t>
+        </is>
+      </c>
+      <c r="B43" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C43" s="67" t="inlineStr">
+        <is>
+          <t>Prelievi liberi</t>
+        </is>
+      </c>
+      <c r="D43" s="67" t="inlineStr">
+        <is>
+          <t>Prelievi liberamente determinabili</t>
+        </is>
+      </c>
+      <c r="E43" s="67" t="inlineStr">
+        <is>
+          <t>Dal 1° luglio 2026, alternativa alla vitalizia: prelevi quando vuoi, entro la somma delle rate maturate e non ancora riscosse di una rendita teorica a durata definita. Il resto resta investito.</t>
+        </is>
+      </c>
+      <c r="F43" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G43" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H43" s="67" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="67" t="inlineStr">
+        <is>
+          <t>erogazione-frazionata</t>
+        </is>
+      </c>
+      <c r="B44" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C44" s="67" t="inlineStr">
+        <is>
+          <t>Erogazione frazionata</t>
+        </is>
+      </c>
+      <c r="D44" s="67" t="n"/>
+      <c r="E44" s="67" t="inlineStr">
+        <is>
+          <t>Dal 31 ottobre 2026: il montante pagato a rate per un periodo che scegli tu, di almeno 5 anni, indipendente dalla speranza di vita. Ha una tassazione meno favorevole delle altre forme.</t>
+        </is>
+      </c>
+      <c r="F44" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G44" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H44" s="67" t="inlineStr">
+        <is>
+          <t>Tassazione: vedi Regole, “Tasse sulle prestazioni”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="67" t="inlineStr">
+        <is>
+          <t>documento-rendite</t>
+        </is>
+      </c>
+      <c r="B45" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C45" s="67" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite</t>
+        </is>
+      </c>
+      <c r="D45" s="67" t="n"/>
+      <c r="E45" s="67" t="inlineStr">
+        <is>
+          <t>Documento del fondo che spiega nel dettaglio le prestazioni in rendita e, dal 2026, come si calcolano le rate e i prelievi delle nuove forme.</t>
+        </is>
+      </c>
+      <c r="F45" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Istruzioni sulle prestazioni (deliberazione 25 giugno 2026)</t>
+        </is>
+      </c>
+      <c r="G45" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H45" s="67" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="67" t="inlineStr">
+        <is>
+          <t>supplemento-nota</t>
+        </is>
+      </c>
+      <c r="B46" s="67" t="inlineStr">
+        <is>
+          <t>Alla pensione</t>
+        </is>
+      </c>
+      <c r="C46" s="67" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa</t>
+        </is>
+      </c>
+      <c r="D46" s="67" t="n"/>
+      <c r="E46" s="67" t="inlineStr">
+        <is>
+          <t>Documento che dal 2026 ogni fondo pubblica sul proprio sito per descrivere le prestazioni: tipi di rendita e nuove forme offerti, con condizioni e costi. Serve a confrontare i fondi in vista della pensione.</t>
+        </is>
+      </c>
+      <c r="F46" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Istruzioni sulle prestazioni (deliberazione 25 giugno 2026)</t>
+        </is>
+      </c>
+      <c r="G46" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H46" s="67" t="inlineStr">
+        <is>
+          <t>La COVIP ne ha pubblicato un esempio per i fondi aperti il 28/7/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="67" t="inlineStr">
+        <is>
+          <t>rischio-longevita</t>
+        </is>
+      </c>
+      <c r="B47" s="67" t="inlineStr">
+        <is>
+          <t>Longevità e decesso</t>
+        </is>
+      </c>
+      <c r="C47" s="67" t="inlineStr">
+        <is>
+          <t>Rischio di longevità</t>
+        </is>
+      </c>
+      <c r="D47" s="67" t="n"/>
+      <c r="E47" s="67" t="inlineStr">
+        <is>
+          <t>Il rischio di vivere più a lungo del previsto e di finire i risparmi. La rendita vitalizia protegge da questo rischio; il capitale e le nuove forme a rate no.</t>
+        </is>
+      </c>
+      <c r="F47" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G47" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H47" s="67" t="inlineStr">
+        <is>
+          <t>Guida introduttiva COVIP, pp. 26–27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="67" t="inlineStr">
+        <is>
+          <t>speranza-vita</t>
+        </is>
+      </c>
+      <c r="B48" s="67" t="inlineStr">
+        <is>
+          <t>Longevità e decesso</t>
+        </is>
+      </c>
+      <c r="C48" s="67" t="inlineStr">
+        <is>
+          <t>Speranza di vita</t>
+        </is>
+      </c>
+      <c r="D48" s="67" t="n"/>
+      <c r="E48" s="67" t="inlineStr">
+        <is>
+          <t>Quanti anni, in media, vive ancora chi ha raggiunto una certa età. È una media: molte persone vivono più a lungo.</t>
+        </is>
+      </c>
+      <c r="F48" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G48" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H48" s="67" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="67" t="inlineStr">
+        <is>
+          <t>tavole-mortalita</t>
+        </is>
+      </c>
+      <c r="B49" s="67" t="inlineStr">
+        <is>
+          <t>Longevità e decesso</t>
+        </is>
+      </c>
+      <c r="C49" s="67" t="inlineStr">
+        <is>
+          <t>Tavole di mortalità</t>
+        </is>
+      </c>
+      <c r="D49" s="67" t="n"/>
+      <c r="E49" s="67" t="inlineStr">
+        <is>
+          <t>Statistiche su quante persone sopravvivono a ogni età, per età e sesso; in Italia le pubblica l'ISTAT. Servono a calcolare la speranza di vita, i coefficienti della rendita vitalizia e la durata della rendita a durata definita.</t>
+        </is>
+      </c>
+      <c r="F49" s="68" t="inlineStr">
+        <is>
+          <t>COVIP – Glossario</t>
+        </is>
+      </c>
+      <c r="G49" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H49" s="67" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="67" t="inlineStr">
+        <is>
+          <t>beneficiari</t>
+        </is>
+      </c>
+      <c r="B50" s="67" t="inlineStr">
+        <is>
+          <t>Longevità e decesso</t>
+        </is>
+      </c>
+      <c r="C50" s="67" t="inlineStr">
+        <is>
+          <t>Beneficiari designati</t>
+        </is>
+      </c>
+      <c r="D50" s="67" t="n"/>
+      <c r="E50" s="67" t="inlineStr">
+        <is>
+          <t>Le persone, o gli enti, che indichi al fondo perché ricevano la posizione se muori prima della pensione, o il capitale residuo delle nuove forme a rate. Se non ne indichi, la posizione va agli eredi.</t>
+        </is>
+      </c>
+      <c r="F50" s="68" t="inlineStr">
+        <is>
+          <t>D.Lgs. 252/2005 – testo COVIP aggiornato alla Legge 199/2025</t>
+        </is>
+      </c>
+      <c r="G50" s="76" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H50" s="67" t="inlineStr">
+        <is>
+          <t>Art. 14 c. 3. Per le nuove forme indicarli è obbligatorio (Istruzioni COVIP del 25/6/2026).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H50"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId49"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/fondi-pensione-covip.xlsx
+++ b/data/fondi-pensione-covip.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Regole" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Longevita" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Glossario" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Prestazioni" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$2:$Q$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparti'!$A$1:$J$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regole'!$A$1:$M$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Glossario'!$A$1:$H$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Prestazioni'!$A$1:$V$39</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,11 +26,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -296,7 +299,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -491,6 +494,24 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1042,23 +1063,23 @@
       </c>
       <c r="H3" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A3)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I3" s="19">
         <f>IF($H3=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A3))</f>
-        <v/>
+        <v>0.01</v>
       </c>
       <c r="J3" s="19">
         <f>IF($H3=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A3))</f>
-        <v/>
+        <v>0.0145</v>
       </c>
       <c r="K3" s="19">
         <f>IF($H3=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A3))</f>
-        <v/>
+        <v>0.9</v>
       </c>
       <c r="L3" s="19">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A3,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A3,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0654</v>
       </c>
       <c r="M3" s="18" t="inlineStr">
         <is>
@@ -1116,23 +1137,23 @@
       </c>
       <c r="H4" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A4)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I4" s="23">
         <f>IF($H4=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A4))</f>
-        <v/>
+        <v>0.011</v>
       </c>
       <c r="J4" s="23">
         <f>IF($H4=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A4))</f>
-        <v/>
+        <v>0.016</v>
       </c>
       <c r="K4" s="23">
         <f>IF($H4=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A4))</f>
-        <v/>
+        <v>0.82</v>
       </c>
       <c r="L4" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A4,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A4,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0518</v>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
@@ -1178,21 +1199,21 @@
       <c r="G5" s="18" t="n"/>
       <c r="H5" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A5)</f>
-        <v/>
-      </c>
-      <c r="I5" s="19">
+        <v>0</v>
+      </c>
+      <c r="I5" s="19" t="str">
         <f>IF($H5=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A5))</f>
         <v/>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="19" t="str">
         <f>IF($H5=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A5))</f>
         <v/>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="19" t="str">
         <f>IF($H5=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A5))</f>
         <v/>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="19" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A5,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A5,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -1236,23 +1257,23 @@
       </c>
       <c r="H6" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A6)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="I6" s="23">
         <f>IF($H6=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A6))</f>
-        <v/>
+        <v>0.01</v>
       </c>
       <c r="J6" s="23">
         <f>IF($H6=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A6))</f>
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="K6" s="23">
         <f>IF($H6=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A6))</f>
-        <v/>
+        <v>0.9474</v>
       </c>
       <c r="L6" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A6,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A6,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0501</v>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
@@ -1310,23 +1331,23 @@
       </c>
       <c r="H7" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A7)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I7" s="19">
         <f>IF($H7=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A7))</f>
-        <v/>
+        <v>0.0085</v>
       </c>
       <c r="J7" s="19">
         <f>IF($H7=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A7))</f>
-        <v/>
+        <v>0.015</v>
       </c>
       <c r="K7" s="19">
         <f>IF($H7=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A7))</f>
-        <v/>
+        <v>0.93</v>
       </c>
       <c r="L7" s="19">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A7,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A7,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0559</v>
       </c>
       <c r="M7" s="18" t="inlineStr">
         <is>
@@ -1372,21 +1393,21 @@
       <c r="G8" s="22" t="n"/>
       <c r="H8" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="23">
+        <v>0</v>
+      </c>
+      <c r="I8" s="23" t="str">
         <f>IF($H8=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A8))</f>
         <v/>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="23" t="str">
         <f>IF($H8=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A8))</f>
         <v/>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="23" t="str">
         <f>IF($H8=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A8))</f>
         <v/>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="23" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A8,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A8,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -1430,23 +1451,23 @@
       </c>
       <c r="H9" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A9)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I9" s="19">
         <f>IF($H9=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A9))</f>
-        <v/>
+        <v>0.006500000000000001</v>
       </c>
       <c r="J9" s="19">
         <f>IF($H9=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A9))</f>
-        <v/>
+        <v>0.015</v>
       </c>
       <c r="K9" s="19">
         <f>IF($H9=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A9))</f>
-        <v/>
+        <v>0.89</v>
       </c>
       <c r="L9" s="19">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A9,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A9,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0498</v>
       </c>
       <c r="M9" s="18" t="inlineStr">
         <is>
@@ -1504,23 +1525,23 @@
       </c>
       <c r="H10" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A10)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I10" s="23">
         <f>IF($H10=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A10))</f>
-        <v/>
+        <v>0.01</v>
       </c>
       <c r="J10" s="23">
         <f>IF($H10=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A10))</f>
-        <v/>
+        <v>0.015</v>
       </c>
       <c r="K10" s="23">
         <f>IF($H10=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A10))</f>
-        <v/>
+        <v>0.9135</v>
       </c>
       <c r="L10" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A10,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A10,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0579</v>
       </c>
       <c r="M10" s="22" t="inlineStr">
         <is>
@@ -1578,23 +1599,23 @@
       </c>
       <c r="H11" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A11)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I11" s="19">
         <f>IF($H11=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A11))</f>
-        <v/>
+        <v>0.01</v>
       </c>
       <c r="J11" s="19">
         <f>IF($H11=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A11))</f>
-        <v/>
+        <v>0.0168</v>
       </c>
       <c r="K11" s="19">
         <f>IF($H11=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A11))</f>
-        <v/>
+        <v>0.8101</v>
       </c>
       <c r="L11" s="19">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A11,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A11,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0387</v>
       </c>
       <c r="M11" s="18" t="inlineStr">
         <is>
@@ -1636,21 +1657,21 @@
       <c r="G12" s="22" t="n"/>
       <c r="H12" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="23">
+        <v>0</v>
+      </c>
+      <c r="I12" s="23" t="str">
         <f>IF($H12=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A12))</f>
         <v/>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="23" t="str">
         <f>IF($H12=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A12))</f>
         <v/>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="23" t="str">
         <f>IF($H12=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A12))</f>
         <v/>
       </c>
-      <c r="L12" s="23">
+      <c r="L12" s="23" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A12,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A12,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -1682,21 +1703,21 @@
       <c r="G13" s="18" t="n"/>
       <c r="H13" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="19">
+        <v>0</v>
+      </c>
+      <c r="I13" s="19" t="str">
         <f>IF($H13=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A13))</f>
         <v/>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="19" t="str">
         <f>IF($H13=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A13))</f>
         <v/>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="19" t="str">
         <f>IF($H13=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A13))</f>
         <v/>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="19" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A13,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A13,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -1728,21 +1749,21 @@
       <c r="G14" s="22" t="n"/>
       <c r="H14" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="23">
+        <v>0</v>
+      </c>
+      <c r="I14" s="23" t="str">
         <f>IF($H14=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A14))</f>
         <v/>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="23" t="str">
         <f>IF($H14=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A14))</f>
         <v/>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="23" t="str">
         <f>IF($H14=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A14))</f>
         <v/>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="23" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A14,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A14,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -1774,21 +1795,21 @@
       <c r="G15" s="18" t="n"/>
       <c r="H15" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="19">
+        <v>0</v>
+      </c>
+      <c r="I15" s="19" t="str">
         <f>IF($H15=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A15))</f>
         <v/>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="19" t="str">
         <f>IF($H15=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A15))</f>
         <v/>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="19" t="str">
         <f>IF($H15=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A15))</f>
         <v/>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="19" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A15,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A15,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -1832,23 +1853,23 @@
       </c>
       <c r="H16" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A16)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I16" s="23">
         <f>IF($H16=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A16))</f>
-        <v/>
+        <v>0.015</v>
       </c>
       <c r="J16" s="23">
         <f>IF($H16=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A16))</f>
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="K16" s="23">
         <f>IF($H16=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A16))</f>
-        <v/>
+        <v>0.9</v>
       </c>
       <c r="L16" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A16,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A16,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0447</v>
       </c>
       <c r="M16" s="22" t="inlineStr">
         <is>
@@ -1906,23 +1927,23 @@
       </c>
       <c r="H17" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A17)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I17" s="19">
         <f>IF($H17=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A17))</f>
-        <v/>
+        <v>0.009000000000000001</v>
       </c>
       <c r="J17" s="19">
         <f>IF($H17=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A17))</f>
-        <v/>
+        <v>0.0105</v>
       </c>
       <c r="K17" s="19">
         <f>IF($H17=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A17))</f>
-        <v/>
+        <v>0.6919</v>
       </c>
       <c r="L17" s="19">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A17,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A17,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0398</v>
       </c>
       <c r="M17" s="18" t="inlineStr">
         <is>
@@ -1980,23 +2001,23 @@
       </c>
       <c r="H18" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A18)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I18" s="23">
         <f>IF($H18=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A18))</f>
-        <v/>
+        <v>0.009000000000000001</v>
       </c>
       <c r="J18" s="23">
         <f>IF($H18=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A18))</f>
-        <v/>
+        <v>0.0222</v>
       </c>
       <c r="K18" s="23">
         <f>IF($H18=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A18))</f>
-        <v/>
+        <v>0.9237</v>
       </c>
       <c r="L18" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A18,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A18,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.05019999999999999</v>
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
@@ -2054,23 +2075,23 @@
       </c>
       <c r="H19" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A19)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I19" s="19">
         <f>IF($H19=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A19))</f>
-        <v/>
+        <v>0.008</v>
       </c>
       <c r="J19" s="19">
         <f>IF($H19=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A19))</f>
-        <v/>
+        <v>0.015</v>
       </c>
       <c r="K19" s="19">
         <f>IF($H19=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A19))</f>
-        <v/>
+        <v>0.68</v>
       </c>
       <c r="L19" s="19">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A19,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A19,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0425</v>
       </c>
       <c r="M19" s="18" t="inlineStr">
         <is>
@@ -2128,23 +2149,23 @@
       </c>
       <c r="H20" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A20)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I20" s="23">
         <f>IF($H20=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A20))</f>
-        <v/>
+        <v>0.006</v>
       </c>
       <c r="J20" s="23">
         <f>IF($H20=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A20))</f>
-        <v/>
+        <v>0.014</v>
       </c>
       <c r="K20" s="23">
         <f>IF($H20=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A20))</f>
-        <v/>
+        <v>0.7635</v>
       </c>
       <c r="L20" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A20,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A20,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0603</v>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
@@ -2202,23 +2223,23 @@
       </c>
       <c r="H21" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A21)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I21" s="19">
         <f>IF($H21=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A21))</f>
-        <v/>
+        <v>0.005</v>
       </c>
       <c r="J21" s="19">
         <f>IF($H21=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A21))</f>
-        <v/>
+        <v>0.015</v>
       </c>
       <c r="K21" s="19">
         <f>IF($H21=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A21))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L21" s="19">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A21,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A21,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0617</v>
       </c>
       <c r="M21" s="18" t="inlineStr">
         <is>
@@ -2276,23 +2297,23 @@
       </c>
       <c r="H22" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A22)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I22" s="23">
         <f>IF($H22=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A22))</f>
-        <v/>
+        <v>0.0115</v>
       </c>
       <c r="J22" s="23">
         <f>IF($H22=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A22))</f>
-        <v/>
+        <v>0.014</v>
       </c>
       <c r="K22" s="23">
         <f>IF($H22=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A22))</f>
-        <v/>
+        <v>0.7664</v>
       </c>
       <c r="L22" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A22,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A22,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.05690000000000001</v>
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
@@ -2350,23 +2371,23 @@
       </c>
       <c r="H23" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A23)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="I23" s="19">
         <f>IF($H23=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A23))</f>
-        <v/>
+        <v>0.006</v>
       </c>
       <c r="J23" s="19">
         <f>IF($H23=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A23))</f>
-        <v/>
+        <v>0.016</v>
       </c>
       <c r="K23" s="19">
         <f>IF($H23=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A23))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L23" s="19">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A23,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A23,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.06059999999999999</v>
       </c>
       <c r="M23" s="18" t="inlineStr">
         <is>
@@ -2424,23 +2445,23 @@
       </c>
       <c r="H24" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A24)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I24" s="23">
         <f>IF($H24=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A24))</f>
-        <v/>
+        <v>0.006</v>
       </c>
       <c r="J24" s="23">
         <f>IF($H24=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A24))</f>
-        <v/>
+        <v>0.008</v>
       </c>
       <c r="K24" s="23">
         <f>IF($H24=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A24))</f>
-        <v/>
+        <v>0.81</v>
       </c>
       <c r="L24" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A24,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A24,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0536</v>
       </c>
       <c r="M24" s="22" t="inlineStr">
         <is>
@@ -2486,21 +2507,21 @@
       <c r="G25" s="18" t="n"/>
       <c r="H25" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="19">
+        <v>0</v>
+      </c>
+      <c r="I25" s="19" t="str">
         <f>IF($H25=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A25))</f>
         <v/>
       </c>
-      <c r="J25" s="19">
+      <c r="J25" s="19" t="str">
         <f>IF($H25=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A25))</f>
         <v/>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="19" t="str">
         <f>IF($H25=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A25))</f>
         <v/>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="19" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A25,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A25,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -2544,23 +2565,23 @@
       </c>
       <c r="H26" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A26)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I26" s="23">
         <f>IF($H26=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A26))</f>
-        <v/>
+        <v>0.013</v>
       </c>
       <c r="J26" s="23">
         <f>IF($H26=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A26))</f>
-        <v/>
+        <v>0.015</v>
       </c>
       <c r="K26" s="23">
         <f>IF($H26=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A26))</f>
-        <v/>
+        <v>0.56</v>
       </c>
       <c r="L26" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A26,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A26,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0392</v>
       </c>
       <c r="M26" s="22" t="inlineStr">
         <is>
@@ -2606,21 +2627,21 @@
       <c r="G27" s="18" t="n"/>
       <c r="H27" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="19">
+        <v>0</v>
+      </c>
+      <c r="I27" s="19" t="str">
         <f>IF($H27=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A27))</f>
         <v/>
       </c>
-      <c r="J27" s="19">
+      <c r="J27" s="19" t="str">
         <f>IF($H27=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A27))</f>
         <v/>
       </c>
-      <c r="K27" s="19">
+      <c r="K27" s="19" t="str">
         <f>IF($H27=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A27))</f>
         <v/>
       </c>
-      <c r="L27" s="19">
+      <c r="L27" s="19" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A27,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A27,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -2664,23 +2685,23 @@
       </c>
       <c r="H28" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A28)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I28" s="23">
         <f>IF($H28=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A28))</f>
-        <v/>
+        <v>0.01</v>
       </c>
       <c r="J28" s="23">
         <f>IF($H28=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A28))</f>
-        <v/>
+        <v>0.018</v>
       </c>
       <c r="K28" s="23">
         <f>IF($H28=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A28))</f>
-        <v/>
+        <v>0.86</v>
       </c>
       <c r="L28" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A28,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A28,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0338</v>
       </c>
       <c r="M28" s="22" t="inlineStr">
         <is>
@@ -2738,23 +2759,23 @@
       </c>
       <c r="H29" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A29)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I29" s="19">
         <f>IF($H29=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A29))</f>
-        <v/>
+        <v>0.006999999999999999</v>
       </c>
       <c r="J29" s="19">
         <f>IF($H29=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A29))</f>
-        <v/>
+        <v>0.018</v>
       </c>
       <c r="K29" s="19">
         <f>IF($H29=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A29))</f>
-        <v/>
+        <v>0.86</v>
       </c>
       <c r="L29" s="19">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A29,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A29,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0529</v>
       </c>
       <c r="M29" s="18" t="inlineStr">
         <is>
@@ -2812,23 +2833,23 @@
       </c>
       <c r="H30" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A30)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I30" s="23">
         <f>IF($H30=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A30))</f>
-        <v/>
+        <v>0.009000000000000001</v>
       </c>
       <c r="J30" s="23">
         <f>IF($H30=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A30))</f>
-        <v/>
+        <v>0.013</v>
       </c>
       <c r="K30" s="23">
         <f>IF($H30=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A30))</f>
-        <v/>
+        <v>0.95</v>
       </c>
       <c r="L30" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A30,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A30,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0395</v>
       </c>
       <c r="M30" s="22" t="inlineStr">
         <is>
@@ -2886,23 +2907,23 @@
       </c>
       <c r="H31" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A31)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="I31" s="19">
         <f>IF($H31=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A31))</f>
-        <v/>
+        <v>0.005500000000000001</v>
       </c>
       <c r="J31" s="19">
         <f>IF($H31=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A31))</f>
-        <v/>
+        <v>0.008</v>
       </c>
       <c r="K31" s="19">
         <f>IF($H31=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A31))</f>
-        <v/>
+        <v>0.94</v>
       </c>
       <c r="L31" s="19">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A31,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A31,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0748</v>
       </c>
       <c r="M31" s="18" t="inlineStr">
         <is>
@@ -2960,23 +2981,23 @@
       </c>
       <c r="H32" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A32)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I32" s="23">
         <f>IF($H32=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A32))</f>
-        <v/>
+        <v>0.01</v>
       </c>
       <c r="J32" s="23">
         <f>IF($H32=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A32))</f>
-        <v/>
+        <v>0.018</v>
       </c>
       <c r="K32" s="23">
         <f>IF($H32=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A32))</f>
-        <v/>
+        <v>0.8323999999999999</v>
       </c>
       <c r="L32" s="23">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A32,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A32,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.05019999999999999</v>
       </c>
       <c r="M32" s="22" t="inlineStr">
         <is>
@@ -3022,21 +3043,21 @@
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A33)</f>
-        <v/>
-      </c>
-      <c r="I33" s="19">
+        <v>0</v>
+      </c>
+      <c r="I33" s="19" t="str">
         <f>IF($H33=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A33))</f>
         <v/>
       </c>
-      <c r="J33" s="19">
+      <c r="J33" s="19" t="str">
         <f>IF($H33=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A33))</f>
         <v/>
       </c>
-      <c r="K33" s="19">
+      <c r="K33" s="19" t="str">
         <f>IF($H33=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A33))</f>
         <v/>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="19" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A33,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A33,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -3068,21 +3089,21 @@
       <c r="G34" s="22" t="n"/>
       <c r="H34" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="23">
+        <v>0</v>
+      </c>
+      <c r="I34" s="23" t="str">
         <f>IF($H34=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A34))</f>
         <v/>
       </c>
-      <c r="J34" s="23">
+      <c r="J34" s="23" t="str">
         <f>IF($H34=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A34))</f>
         <v/>
       </c>
-      <c r="K34" s="23">
+      <c r="K34" s="23" t="str">
         <f>IF($H34=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A34))</f>
         <v/>
       </c>
-      <c r="L34" s="23">
+      <c r="L34" s="23" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A34,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A34,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -3126,23 +3147,23 @@
       </c>
       <c r="H35" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A35)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I35" s="19">
         <f>IF($H35=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A35))</f>
-        <v/>
+        <v>0.008</v>
       </c>
       <c r="J35" s="19">
         <f>IF($H35=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A35))</f>
-        <v/>
+        <v>0.014</v>
       </c>
       <c r="K35" s="19">
         <f>IF($H35=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A35))</f>
-        <v/>
+        <v>0.85</v>
       </c>
       <c r="L35" s="19">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A35,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A35,Comparti!$G:$G,10))</f>
-        <v/>
+        <v>0.0463</v>
       </c>
       <c r="M35" s="18" t="inlineStr">
         <is>
@@ -3188,21 +3209,21 @@
       <c r="G36" s="22" t="n"/>
       <c r="H36" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="23">
+        <v>0</v>
+      </c>
+      <c r="I36" s="23" t="str">
         <f>IF($H36=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A36))</f>
         <v/>
       </c>
-      <c r="J36" s="23">
+      <c r="J36" s="23" t="str">
         <f>IF($H36=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A36))</f>
         <v/>
       </c>
-      <c r="K36" s="23">
+      <c r="K36" s="23" t="str">
         <f>IF($H36=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A36))</f>
         <v/>
       </c>
-      <c r="L36" s="23">
+      <c r="L36" s="23" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A36,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A36,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -3234,21 +3255,21 @@
       <c r="G37" s="18" t="n"/>
       <c r="H37" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="19">
+        <v>0</v>
+      </c>
+      <c r="I37" s="19" t="str">
         <f>IF($H37=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A37))</f>
         <v/>
       </c>
-      <c r="J37" s="19">
+      <c r="J37" s="19" t="str">
         <f>IF($H37=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A37))</f>
         <v/>
       </c>
-      <c r="K37" s="19">
+      <c r="K37" s="19" t="str">
         <f>IF($H37=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A37))</f>
         <v/>
       </c>
-      <c r="L37" s="19">
+      <c r="L37" s="19" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A37,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A37,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -3280,21 +3301,21 @@
       <c r="G38" s="22" t="n"/>
       <c r="H38" s="32">
         <f>COUNTIF(Comparti!$A:$A,$A38)</f>
-        <v/>
-      </c>
-      <c r="I38" s="23">
+        <v>0</v>
+      </c>
+      <c r="I38" s="23" t="str">
         <f>IF($H38=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A38))</f>
         <v/>
       </c>
-      <c r="J38" s="23">
+      <c r="J38" s="23" t="str">
         <f>IF($H38=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A38))</f>
         <v/>
       </c>
-      <c r="K38" s="23">
+      <c r="K38" s="23" t="str">
         <f>IF($H38=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A38))</f>
         <v/>
       </c>
-      <c r="L38" s="23">
+      <c r="L38" s="23" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A38,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A38,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -3326,21 +3347,21 @@
       <c r="G39" s="18" t="n"/>
       <c r="H39" s="31">
         <f>COUNTIF(Comparti!$A:$A,$A39)</f>
-        <v/>
-      </c>
-      <c r="I39" s="19">
+        <v>0</v>
+      </c>
+      <c r="I39" s="19" t="str">
         <f>IF($H39=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A39))</f>
         <v/>
       </c>
-      <c r="J39" s="19">
+      <c r="J39" s="19" t="str">
         <f>IF($H39=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A39))</f>
         <v/>
       </c>
-      <c r="K39" s="19">
+      <c r="K39" s="19" t="str">
         <f>IF($H39=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A39))</f>
         <v/>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="19" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A39,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A39,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -3372,21 +3393,21 @@
       <c r="G40" s="26" t="n"/>
       <c r="H40" s="33">
         <f>COUNTIF(Comparti!$A:$A,$A40)</f>
-        <v/>
-      </c>
-      <c r="I40" s="27">
+        <v>0</v>
+      </c>
+      <c r="I40" s="27" t="str">
         <f>IF($H40=0,"",_xlfn.MINIFS(Comparti!$H:$H,Comparti!$A:$A,$A40))</f>
         <v/>
       </c>
-      <c r="J40" s="27">
+      <c r="J40" s="27" t="str">
         <f>IF($H40=0,"",_xlfn.MAXIFS(Comparti!$H:$H,Comparti!$A:$A,$A40))</f>
         <v/>
       </c>
-      <c r="K40" s="27">
+      <c r="K40" s="27" t="str">
         <f>IF($H40=0,"",_xlfn.MAXIFS(Comparti!$D:$D,Comparti!$A:$A,$A40))</f>
         <v/>
       </c>
-      <c r="L40" s="27">
+      <c r="L40" s="27" t="str">
         <f>IF(COUNTIFS(Comparti!$A:$A,$A40,Comparti!$G:$G,10)=0,"",_xlfn.MAXIFS(Comparti!$F:$F,Comparti!$A:$A,$A40,Comparti!$G:$G,10))</f>
         <v/>
       </c>
@@ -3541,9 +3562,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="37">
+      <c r="A2" s="37" t="str">
         <f>Sheet1!$A$3</f>
-        <v/>
+        <v>ALLIANZ PREVIDENZA FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B2" s="38" t="inlineStr">
         <is>
@@ -3578,9 +3599,9 @@
       <c r="J2" s="52" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="39">
+      <c r="A3" s="39" t="str">
         <f>Sheet1!$A$3</f>
-        <v/>
+        <v>ALLIANZ PREVIDENZA FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B3" s="40" t="inlineStr">
         <is>
@@ -3615,9 +3636,9 @@
       <c r="J3" s="53" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="37">
+      <c r="A4" s="37" t="str">
         <f>Sheet1!$A$3</f>
-        <v/>
+        <v>ALLIANZ PREVIDENZA FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B4" s="38" t="inlineStr">
         <is>
@@ -3652,9 +3673,9 @@
       <c r="J4" s="52" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="39">
+      <c r="A5" s="39" t="str">
         <f>Sheet1!$A$3</f>
-        <v/>
+        <v>ALLIANZ PREVIDENZA FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B5" s="40" t="inlineStr">
         <is>
@@ -3689,9 +3710,9 @@
       <c r="J5" s="53" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="37">
+      <c r="A6" s="37" t="str">
         <f>Sheet1!$A$3</f>
-        <v/>
+        <v>ALLIANZ PREVIDENZA FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B6" s="38" t="inlineStr">
         <is>
@@ -3726,9 +3747,9 @@
       <c r="J6" s="52" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="39">
+      <c r="A7" s="39" t="str">
         <f>Sheet1!$A$4</f>
-        <v/>
+        <v>PREVIDENZA PER TE - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B7" s="40" t="inlineStr">
         <is>
@@ -3763,9 +3784,9 @@
       <c r="J7" s="53" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="37">
+      <c r="A8" s="37" t="str">
         <f>Sheet1!$A$4</f>
-        <v/>
+        <v>PREVIDENZA PER TE - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B8" s="38" t="inlineStr">
         <is>
@@ -3800,9 +3821,9 @@
       <c r="J8" s="52" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="39">
+      <c r="A9" s="39" t="str">
         <f>Sheet1!$A$4</f>
-        <v/>
+        <v>PREVIDENZA PER TE - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B9" s="40" t="inlineStr">
         <is>
@@ -3837,9 +3858,9 @@
       <c r="J9" s="53" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="37">
+      <c r="A10" s="37" t="str">
         <f>Sheet1!$A$4</f>
-        <v/>
+        <v>PREVIDENZA PER TE - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B10" s="38" t="inlineStr">
         <is>
@@ -3874,9 +3895,9 @@
       <c r="J10" s="52" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="39">
+      <c r="A11" s="39" t="str">
         <f>Sheet1!$A$4</f>
-        <v/>
+        <v>PREVIDENZA PER TE - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B11" s="40" t="inlineStr">
         <is>
@@ -3911,9 +3932,9 @@
       <c r="J11" s="53" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="37">
+      <c r="A12" s="37" t="str">
         <f>Sheet1!$A$6</f>
-        <v/>
+        <v>FONDO PENSIONE FIDEURAM FONDO PENSIONE APERTO</v>
       </c>
       <c r="B12" s="38" t="inlineStr">
         <is>
@@ -3952,9 +3973,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39">
+      <c r="A13" s="39" t="str">
         <f>Sheet1!$A$6</f>
-        <v/>
+        <v>FONDO PENSIONE FIDEURAM FONDO PENSIONE APERTO</v>
       </c>
       <c r="B13" s="40" t="inlineStr">
         <is>
@@ -3989,9 +4010,9 @@
       <c r="J13" s="53" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="37">
+      <c r="A14" s="37" t="str">
         <f>Sheet1!$A$6</f>
-        <v/>
+        <v>FONDO PENSIONE FIDEURAM FONDO PENSIONE APERTO</v>
       </c>
       <c r="B14" s="38" t="inlineStr">
         <is>
@@ -4026,9 +4047,9 @@
       <c r="J14" s="52" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="39">
+      <c r="A15" s="39" t="str">
         <f>Sheet1!$A$6</f>
-        <v/>
+        <v>FONDO PENSIONE FIDEURAM FONDO PENSIONE APERTO</v>
       </c>
       <c r="B15" s="40" t="inlineStr">
         <is>
@@ -4063,9 +4084,9 @@
       <c r="J15" s="53" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="37">
+      <c r="A16" s="37" t="str">
         <f>Sheet1!$A$6</f>
-        <v/>
+        <v>FONDO PENSIONE FIDEURAM FONDO PENSIONE APERTO</v>
       </c>
       <c r="B16" s="38" t="inlineStr">
         <is>
@@ -4100,9 +4121,9 @@
       <c r="J16" s="52" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="39">
+      <c r="A17" s="39" t="str">
         <f>Sheet1!$A$6</f>
-        <v/>
+        <v>FONDO PENSIONE FIDEURAM FONDO PENSIONE APERTO</v>
       </c>
       <c r="B17" s="40" t="inlineStr">
         <is>
@@ -4137,9 +4158,9 @@
       <c r="J17" s="53" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="37">
+      <c r="A18" s="37" t="str">
         <f>Sheet1!$A$7</f>
-        <v/>
+        <v>GENERALI GLOBAL - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B18" s="38" t="inlineStr">
         <is>
@@ -4174,9 +4195,9 @@
       <c r="J18" s="52" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="39">
+      <c r="A19" s="39" t="str">
         <f>Sheet1!$A$7</f>
-        <v/>
+        <v>GENERALI GLOBAL - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B19" s="40" t="inlineStr">
         <is>
@@ -4211,9 +4232,9 @@
       <c r="J19" s="53" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="37">
+      <c r="A20" s="37" t="str">
         <f>Sheet1!$A$7</f>
-        <v/>
+        <v>GENERALI GLOBAL - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B20" s="38" t="inlineStr">
         <is>
@@ -4252,9 +4273,9 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39">
+      <c r="A21" s="39" t="str">
         <f>Sheet1!$A$7</f>
-        <v/>
+        <v>GENERALI GLOBAL - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B21" s="40" t="inlineStr">
         <is>
@@ -4293,9 +4314,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="37">
+      <c r="A22" s="37" t="str">
         <f>Sheet1!$A$7</f>
-        <v/>
+        <v>GENERALI GLOBAL - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B22" s="38" t="inlineStr">
         <is>
@@ -4330,9 +4351,9 @@
       <c r="J22" s="52" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="39">
+      <c r="A23" s="39" t="str">
         <f>Sheet1!$A$9</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO TESEO</v>
       </c>
       <c r="B23" s="40" t="inlineStr">
         <is>
@@ -4367,9 +4388,9 @@
       <c r="J23" s="53" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="37">
+      <c r="A24" s="37" t="str">
         <f>Sheet1!$A$9</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO TESEO</v>
       </c>
       <c r="B24" s="38" t="inlineStr">
         <is>
@@ -4404,9 +4425,9 @@
       <c r="J24" s="52" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="39">
+      <c r="A25" s="39" t="str">
         <f>Sheet1!$A$9</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO TESEO</v>
       </c>
       <c r="B25" s="40" t="inlineStr">
         <is>
@@ -4441,9 +4462,9 @@
       <c r="J25" s="53" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="37">
+      <c r="A26" s="37" t="str">
         <f>Sheet1!$A$9</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO TESEO</v>
       </c>
       <c r="B26" s="38" t="inlineStr">
         <is>
@@ -4478,9 +4499,9 @@
       <c r="J26" s="52" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="39">
+      <c r="A27" s="39" t="str">
         <f>Sheet1!$A$10</f>
-        <v/>
+        <v>DESTINAZIONE FUTURO - FONDO PENSIONE APERTO BY CREDEMVITA</v>
       </c>
       <c r="B27" s="40" t="inlineStr">
         <is>
@@ -4515,9 +4536,9 @@
       <c r="J27" s="53" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="37">
+      <c r="A28" s="37" t="str">
         <f>Sheet1!$A$10</f>
-        <v/>
+        <v>DESTINAZIONE FUTURO - FONDO PENSIONE APERTO BY CREDEMVITA</v>
       </c>
       <c r="B28" s="38" t="inlineStr">
         <is>
@@ -4552,9 +4573,9 @@
       <c r="J28" s="52" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="39">
+      <c r="A29" s="39" t="str">
         <f>Sheet1!$A$10</f>
-        <v/>
+        <v>DESTINAZIONE FUTURO - FONDO PENSIONE APERTO BY CREDEMVITA</v>
       </c>
       <c r="B29" s="40" t="inlineStr">
         <is>
@@ -4589,9 +4610,9 @@
       <c r="J29" s="53" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="37">
+      <c r="A30" s="37" t="str">
         <f>Sheet1!$A$10</f>
-        <v/>
+        <v>DESTINAZIONE FUTURO - FONDO PENSIONE APERTO BY CREDEMVITA</v>
       </c>
       <c r="B30" s="38" t="inlineStr">
         <is>
@@ -4626,9 +4647,9 @@
       <c r="J30" s="52" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="39">
+      <c r="A31" s="39" t="str">
         <f>Sheet1!$A$11</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO VITTORIA FORMULA LAVORO</v>
       </c>
       <c r="B31" s="40" t="inlineStr">
         <is>
@@ -4663,9 +4684,9 @@
       <c r="J31" s="53" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="37">
+      <c r="A32" s="37" t="str">
         <f>Sheet1!$A$11</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO VITTORIA FORMULA LAVORO</v>
       </c>
       <c r="B32" s="38" t="inlineStr">
         <is>
@@ -4704,9 +4725,9 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="39">
+      <c r="A33" s="39" t="str">
         <f>Sheet1!$A$11</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO VITTORIA FORMULA LAVORO</v>
       </c>
       <c r="B33" s="40" t="inlineStr">
         <is>
@@ -4741,9 +4762,9 @@
       <c r="J33" s="53" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="37">
+      <c r="A34" s="37" t="str">
         <f>Sheet1!$A$11</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO VITTORIA FORMULA LAVORO</v>
       </c>
       <c r="B34" s="38" t="inlineStr">
         <is>
@@ -4778,9 +4799,9 @@
       <c r="J34" s="52" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="39">
+      <c r="A35" s="39" t="str">
         <f>Sheet1!$A$16</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO PREVIGEST FUND MEDIOLANUM</v>
       </c>
       <c r="B35" s="40" t="inlineStr">
         <is>
@@ -4815,9 +4836,9 @@
       <c r="J35" s="53" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="37">
+      <c r="A36" s="37" t="str">
         <f>Sheet1!$A$16</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO PREVIGEST FUND MEDIOLANUM</v>
       </c>
       <c r="B36" s="38" t="inlineStr">
         <is>
@@ -4852,9 +4873,9 @@
       <c r="J36" s="52" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="39">
+      <c r="A37" s="39" t="str">
         <f>Sheet1!$A$16</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO PREVIGEST FUND MEDIOLANUM</v>
       </c>
       <c r="B37" s="40" t="inlineStr">
         <is>
@@ -4889,9 +4910,9 @@
       <c r="J37" s="53" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="37">
+      <c r="A38" s="37" t="str">
         <f>Sheet1!$A$17</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO ZURICH CONTRIBUTION</v>
       </c>
       <c r="B38" s="38" t="inlineStr">
         <is>
@@ -4926,9 +4947,9 @@
       <c r="J38" s="52" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="39">
+      <c r="A39" s="39" t="str">
         <f>Sheet1!$A$17</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO ZURICH CONTRIBUTION</v>
       </c>
       <c r="B39" s="40" t="inlineStr">
         <is>
@@ -4963,9 +4984,9 @@
       <c r="J39" s="53" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="37">
+      <c r="A40" s="37" t="str">
         <f>Sheet1!$A$17</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO ZURICH CONTRIBUTION</v>
       </c>
       <c r="B40" s="38" t="inlineStr">
         <is>
@@ -5000,9 +5021,9 @@
       <c r="J40" s="52" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="39">
+      <c r="A41" s="39" t="str">
         <f>Sheet1!$A$18</f>
-        <v/>
+        <v>ZED OMNIFUND - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B41" s="40" t="inlineStr">
         <is>
@@ -5037,9 +5058,9 @@
       <c r="J41" s="53" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="37">
+      <c r="A42" s="37" t="str">
         <f>Sheet1!$A$18</f>
-        <v/>
+        <v>ZED OMNIFUND - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B42" s="38" t="inlineStr">
         <is>
@@ -5078,9 +5099,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="39">
+      <c r="A43" s="39" t="str">
         <f>Sheet1!$A$18</f>
-        <v/>
+        <v>ZED OMNIFUND - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B43" s="40" t="inlineStr">
         <is>
@@ -5115,9 +5136,9 @@
       <c r="J43" s="53" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="37">
+      <c r="A44" s="37" t="str">
         <f>Sheet1!$A$18</f>
-        <v/>
+        <v>ZED OMNIFUND - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B44" s="38" t="inlineStr">
         <is>
@@ -5152,9 +5173,9 @@
       <c r="J44" s="52" t="n"/>
     </row>
     <row r="45" ht="26.25" customHeight="1">
-      <c r="A45" s="39">
+      <c r="A45" s="39" t="str">
         <f>Sheet1!$A$18</f>
-        <v/>
+        <v>ZED OMNIFUND - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B45" s="40" t="inlineStr">
         <is>
@@ -5193,9 +5214,9 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="37">
+      <c r="A46" s="37" t="str">
         <f>Sheet1!$A$19</f>
-        <v/>
+        <v>PLURIFONDS IL FONDO PENSIONE APERTO DI ITAS VITA</v>
       </c>
       <c r="B46" s="38" t="inlineStr">
         <is>
@@ -5230,9 +5251,9 @@
       <c r="J46" s="52" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="39">
+      <c r="A47" s="39" t="str">
         <f>Sheet1!$A$19</f>
-        <v/>
+        <v>PLURIFONDS IL FONDO PENSIONE APERTO DI ITAS VITA</v>
       </c>
       <c r="B47" s="40" t="inlineStr">
         <is>
@@ -5267,9 +5288,9 @@
       <c r="J47" s="53" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="37">
+      <c r="A48" s="37" t="str">
         <f>Sheet1!$A$19</f>
-        <v/>
+        <v>PLURIFONDS IL FONDO PENSIONE APERTO DI ITAS VITA</v>
       </c>
       <c r="B48" s="38" t="inlineStr">
         <is>
@@ -5304,9 +5325,9 @@
       <c r="J48" s="52" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="39">
+      <c r="A49" s="39" t="str">
         <f>Sheet1!$A$19</f>
-        <v/>
+        <v>PLURIFONDS IL FONDO PENSIONE APERTO DI ITAS VITA</v>
       </c>
       <c r="B49" s="40" t="inlineStr">
         <is>
@@ -5341,9 +5362,9 @@
       <c r="J49" s="53" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="37">
+      <c r="A50" s="37" t="str">
         <f>Sheet1!$A$19</f>
-        <v/>
+        <v>PLURIFONDS IL FONDO PENSIONE APERTO DI ITAS VITA</v>
       </c>
       <c r="B50" s="38" t="inlineStr">
         <is>
@@ -5378,9 +5399,9 @@
       <c r="J50" s="52" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="39">
+      <c r="A51" s="39" t="str">
         <f>Sheet1!$A$20</f>
-        <v/>
+        <v>EURORISPARMIO PREVIDENZA COMPLEMENTARE FONDO PENSIONE APERTO</v>
       </c>
       <c r="B51" s="40" t="inlineStr">
         <is>
@@ -5415,9 +5436,9 @@
       <c r="J51" s="53" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="37">
+      <c r="A52" s="37" t="str">
         <f>Sheet1!$A$20</f>
-        <v/>
+        <v>EURORISPARMIO PREVIDENZA COMPLEMENTARE FONDO PENSIONE APERTO</v>
       </c>
       <c r="B52" s="38" t="inlineStr">
         <is>
@@ -5452,9 +5473,9 @@
       <c r="J52" s="52" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="39">
+      <c r="A53" s="39" t="str">
         <f>Sheet1!$A$20</f>
-        <v/>
+        <v>EURORISPARMIO PREVIDENZA COMPLEMENTARE FONDO PENSIONE APERTO</v>
       </c>
       <c r="B53" s="40" t="inlineStr">
         <is>
@@ -5489,9 +5510,9 @@
       <c r="J53" s="53" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="37">
+      <c r="A54" s="37" t="str">
         <f>Sheet1!$A$20</f>
-        <v/>
+        <v>EURORISPARMIO PREVIDENZA COMPLEMENTARE FONDO PENSIONE APERTO</v>
       </c>
       <c r="B54" s="38" t="inlineStr">
         <is>
@@ -5526,9 +5547,9 @@
       <c r="J54" s="52" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="39">
+      <c r="A55" s="39" t="str">
         <f>Sheet1!$A$20</f>
-        <v/>
+        <v>EURORISPARMIO PREVIDENZA COMPLEMENTARE FONDO PENSIONE APERTO</v>
       </c>
       <c r="B55" s="40" t="inlineStr">
         <is>
@@ -5563,9 +5584,9 @@
       <c r="J55" s="53" t="n"/>
     </row>
     <row r="56" ht="26.25" customHeight="1">
-      <c r="A56" s="37">
+      <c r="A56" s="37" t="str">
         <f>Sheet1!$A$21</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO AUREO</v>
       </c>
       <c r="B56" s="38" t="inlineStr">
         <is>
@@ -5604,9 +5625,9 @@
       </c>
     </row>
     <row r="57" ht="26.25" customHeight="1">
-      <c r="A57" s="39">
+      <c r="A57" s="39" t="str">
         <f>Sheet1!$A$21</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO AUREO</v>
       </c>
       <c r="B57" s="40" t="inlineStr">
         <is>
@@ -5645,9 +5666,9 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="37">
+      <c r="A58" s="37" t="str">
         <f>Sheet1!$A$21</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO AUREO</v>
       </c>
       <c r="B58" s="38" t="inlineStr">
         <is>
@@ -5682,9 +5703,9 @@
       <c r="J58" s="52" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="39">
+      <c r="A59" s="39" t="str">
         <f>Sheet1!$A$21</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO AUREO</v>
       </c>
       <c r="B59" s="40" t="inlineStr">
         <is>
@@ -5719,9 +5740,9 @@
       <c r="J59" s="53" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="37">
+      <c r="A60" s="37" t="str">
         <f>Sheet1!$A$21</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO AUREO</v>
       </c>
       <c r="B60" s="38" t="inlineStr">
         <is>
@@ -5756,9 +5777,9 @@
       <c r="J60" s="52" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="39">
+      <c r="A61" s="39" t="str">
         <f>Sheet1!$A$22</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO CREDIT AGRICOLE VITA</v>
       </c>
       <c r="B61" s="40" t="inlineStr">
         <is>
@@ -5793,9 +5814,9 @@
       <c r="J61" s="53" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="37">
+      <c r="A62" s="37" t="str">
         <f>Sheet1!$A$22</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO CREDIT AGRICOLE VITA</v>
       </c>
       <c r="B62" s="38" t="inlineStr">
         <is>
@@ -5830,9 +5851,9 @@
       <c r="J62" s="52" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="39">
+      <c r="A63" s="39" t="str">
         <f>Sheet1!$A$22</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO CREDIT AGRICOLE VITA</v>
       </c>
       <c r="B63" s="40" t="inlineStr">
         <is>
@@ -5871,9 +5892,9 @@
       </c>
     </row>
     <row r="64" ht="26.25" customHeight="1">
-      <c r="A64" s="37">
+      <c r="A64" s="37" t="str">
         <f>Sheet1!$A$23</f>
-        <v/>
+        <v>ARTI &amp; MESTIERI - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B64" s="38" t="inlineStr">
         <is>
@@ -5912,9 +5933,9 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="39">
+      <c r="A65" s="39" t="str">
         <f>Sheet1!$A$23</f>
-        <v/>
+        <v>ARTI &amp; MESTIERI - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B65" s="40" t="inlineStr">
         <is>
@@ -5949,9 +5970,9 @@
       <c r="J65" s="53" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="37">
+      <c r="A66" s="37" t="str">
         <f>Sheet1!$A$23</f>
-        <v/>
+        <v>ARTI &amp; MESTIERI - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B66" s="38" t="inlineStr">
         <is>
@@ -5986,9 +6007,9 @@
       <c r="J66" s="52" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="39">
+      <c r="A67" s="39" t="str">
         <f>Sheet1!$A$23</f>
-        <v/>
+        <v>ARTI &amp; MESTIERI - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B67" s="40" t="inlineStr">
         <is>
@@ -6023,9 +6044,9 @@
       <c r="J67" s="53" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="37">
+      <c r="A68" s="37" t="str">
         <f>Sheet1!$A$23</f>
-        <v/>
+        <v>ARTI &amp; MESTIERI - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B68" s="38" t="inlineStr">
         <is>
@@ -6060,9 +6081,9 @@
       <c r="J68" s="52" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="39">
+      <c r="A69" s="39" t="str">
         <f>Sheet1!$A$23</f>
-        <v/>
+        <v>ARTI &amp; MESTIERI - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B69" s="40" t="inlineStr">
         <is>
@@ -6097,9 +6118,9 @@
       <c r="J69" s="53" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="37">
+      <c r="A70" s="37" t="str">
         <f>Sheet1!$A$24</f>
-        <v/>
+        <v>SECONDAPENSIONE FONDO PENSIONE APERTO</v>
       </c>
       <c r="B70" s="38" t="inlineStr">
         <is>
@@ -6134,9 +6155,9 @@
       <c r="J70" s="52" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="39">
+      <c r="A71" s="39" t="str">
         <f>Sheet1!$A$24</f>
-        <v/>
+        <v>SECONDAPENSIONE FONDO PENSIONE APERTO</v>
       </c>
       <c r="B71" s="40" t="inlineStr">
         <is>
@@ -6171,9 +6192,9 @@
       <c r="J71" s="53" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="37">
+      <c r="A72" s="37" t="str">
         <f>Sheet1!$A$24</f>
-        <v/>
+        <v>SECONDAPENSIONE FONDO PENSIONE APERTO</v>
       </c>
       <c r="B72" s="38" t="inlineStr">
         <is>
@@ -6208,9 +6229,9 @@
       <c r="J72" s="52" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="39">
+      <c r="A73" s="39" t="str">
         <f>Sheet1!$A$24</f>
-        <v/>
+        <v>SECONDAPENSIONE FONDO PENSIONE APERTO</v>
       </c>
       <c r="B73" s="40" t="inlineStr">
         <is>
@@ -6245,9 +6266,9 @@
       <c r="J73" s="53" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="37">
+      <c r="A74" s="37" t="str">
         <f>Sheet1!$A$24</f>
-        <v/>
+        <v>SECONDAPENSIONE FONDO PENSIONE APERTO</v>
       </c>
       <c r="B74" s="38" t="inlineStr">
         <is>
@@ -6282,9 +6303,9 @@
       <c r="J74" s="52" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="39">
+      <c r="A75" s="39" t="str">
         <f>Sheet1!$A$26</f>
-        <v/>
+        <v>PROGRAMMA OPEN FONDO PENSIONE APERTO</v>
       </c>
       <c r="B75" s="40" t="inlineStr">
         <is>
@@ -6323,9 +6344,9 @@
       </c>
     </row>
     <row r="76" ht="26.25" customHeight="1">
-      <c r="A76" s="37">
+      <c r="A76" s="37" t="str">
         <f>Sheet1!$A$26</f>
-        <v/>
+        <v>PROGRAMMA OPEN FONDO PENSIONE APERTO</v>
       </c>
       <c r="B76" s="38" t="inlineStr">
         <is>
@@ -6364,9 +6385,9 @@
       </c>
     </row>
     <row r="77" ht="26.25" customHeight="1">
-      <c r="A77" s="39">
+      <c r="A77" s="39" t="str">
         <f>Sheet1!$A$26</f>
-        <v/>
+        <v>PROGRAMMA OPEN FONDO PENSIONE APERTO</v>
       </c>
       <c r="B77" s="40" t="inlineStr">
         <is>
@@ -6399,9 +6420,9 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="37">
+      <c r="A78" s="37" t="str">
         <f>Sheet1!$A$28</f>
-        <v/>
+        <v>AZIMUT PREVIDENZA - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B78" s="38" t="inlineStr">
         <is>
@@ -6436,9 +6457,9 @@
       <c r="J78" s="52" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="39">
+      <c r="A79" s="39" t="str">
         <f>Sheet1!$A$28</f>
-        <v/>
+        <v>AZIMUT PREVIDENZA - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B79" s="40" t="inlineStr">
         <is>
@@ -6473,9 +6494,9 @@
       <c r="J79" s="53" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="37">
+      <c r="A80" s="37" t="str">
         <f>Sheet1!$A$28</f>
-        <v/>
+        <v>AZIMUT PREVIDENZA - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B80" s="38" t="inlineStr">
         <is>
@@ -6510,9 +6531,9 @@
       <c r="J80" s="52" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="39">
+      <c r="A81" s="39" t="str">
         <f>Sheet1!$A$29</f>
-        <v/>
+        <v>AZIONE DI PREVIDENZA - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B81" s="40" t="inlineStr">
         <is>
@@ -6547,9 +6568,9 @@
       <c r="J81" s="53" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="37">
+      <c r="A82" s="37" t="str">
         <f>Sheet1!$A$29</f>
-        <v/>
+        <v>AZIONE DI PREVIDENZA - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B82" s="38" t="inlineStr">
         <is>
@@ -6584,9 +6605,9 @@
       <c r="J82" s="52" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="39">
+      <c r="A83" s="39" t="str">
         <f>Sheet1!$A$29</f>
-        <v/>
+        <v>AZIONE DI PREVIDENZA - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B83" s="40" t="inlineStr">
         <is>
@@ -6621,9 +6642,9 @@
       <c r="J83" s="53" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="37">
+      <c r="A84" s="37" t="str">
         <f>Sheet1!$A$29</f>
-        <v/>
+        <v>AZIONE DI PREVIDENZA - FONDO PENSIONE APERTO</v>
       </c>
       <c r="B84" s="38" t="inlineStr">
         <is>
@@ -6658,9 +6679,9 @@
       <c r="J84" s="52" t="n"/>
     </row>
     <row r="85" ht="26.25" customHeight="1">
-      <c r="A85" s="39">
+      <c r="A85" s="39" t="str">
         <f>Sheet1!$A$30</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO CNP</v>
       </c>
       <c r="B85" s="40" t="inlineStr">
         <is>
@@ -6699,9 +6720,9 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="37">
+      <c r="A86" s="37" t="str">
         <f>Sheet1!$A$30</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO CNP</v>
       </c>
       <c r="B86" s="38" t="inlineStr">
         <is>
@@ -6736,9 +6757,9 @@
       <c r="J86" s="52" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="39">
+      <c r="A87" s="39" t="str">
         <f>Sheet1!$A$30</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO CNP</v>
       </c>
       <c r="B87" s="40" t="inlineStr">
         <is>
@@ -6773,9 +6794,9 @@
       <c r="J87" s="53" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="37">
+      <c r="A88" s="37" t="str">
         <f>Sheet1!$A$30</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO CNP</v>
       </c>
       <c r="B88" s="38" t="inlineStr">
         <is>
@@ -6810,9 +6831,9 @@
       <c r="J88" s="52" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="39">
+      <c r="A89" s="39" t="str">
         <f>Sheet1!$A$30</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO CNP</v>
       </c>
       <c r="B89" s="40" t="inlineStr">
         <is>
@@ -6847,9 +6868,9 @@
       <c r="J89" s="53" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="37">
+      <c r="A90" s="37" t="str">
         <f>Sheet1!$A$31</f>
-        <v/>
+        <v>INSIEME - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B90" s="38" t="inlineStr">
         <is>
@@ -6884,9 +6905,9 @@
       <c r="J90" s="52" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="39">
+      <c r="A91" s="39" t="str">
         <f>Sheet1!$A$31</f>
-        <v/>
+        <v>INSIEME - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B91" s="40" t="inlineStr">
         <is>
@@ -6925,9 +6946,9 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="37">
+      <c r="A92" s="37" t="str">
         <f>Sheet1!$A$31</f>
-        <v/>
+        <v>INSIEME - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B92" s="38" t="inlineStr">
         <is>
@@ -6962,9 +6983,9 @@
       <c r="J92" s="52" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="39">
+      <c r="A93" s="39" t="str">
         <f>Sheet1!$A$31</f>
-        <v/>
+        <v>INSIEME - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B93" s="40" t="inlineStr">
         <is>
@@ -6999,9 +7020,9 @@
       <c r="J93" s="53" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="37">
+      <c r="A94" s="37" t="str">
         <f>Sheet1!$A$31</f>
-        <v/>
+        <v>INSIEME - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B94" s="38" t="inlineStr">
         <is>
@@ -7036,9 +7057,9 @@
       <c r="J94" s="52" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="39">
+      <c r="A95" s="39" t="str">
         <f>Sheet1!$A$31</f>
-        <v/>
+        <v>INSIEME - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
       </c>
       <c r="B95" s="40" t="inlineStr">
         <is>
@@ -7077,9 +7098,9 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="37">
+      <c r="A96" s="37" t="str">
         <f>Sheet1!$A$32</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO BIM VITA</v>
       </c>
       <c r="B96" s="38" t="inlineStr">
         <is>
@@ -7114,9 +7135,9 @@
       <c r="J96" s="52" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="39">
+      <c r="A97" s="39" t="str">
         <f>Sheet1!$A$32</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO BIM VITA</v>
       </c>
       <c r="B97" s="40" t="inlineStr">
         <is>
@@ -7151,9 +7172,9 @@
       <c r="J97" s="53" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="37">
+      <c r="A98" s="37" t="str">
         <f>Sheet1!$A$32</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO BIM VITA</v>
       </c>
       <c r="B98" s="38" t="inlineStr">
         <is>
@@ -7188,9 +7209,9 @@
       <c r="J98" s="52" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="39">
+      <c r="A99" s="39" t="str">
         <f>Sheet1!$A$32</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO BIM VITA</v>
       </c>
       <c r="B99" s="40" t="inlineStr">
         <is>
@@ -7225,9 +7246,9 @@
       <c r="J99" s="53" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="37">
+      <c r="A100" s="37" t="str">
         <f>Sheet1!$A$35</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO IL MELOGRANO</v>
       </c>
       <c r="B100" s="38" t="inlineStr">
         <is>
@@ -7262,9 +7283,9 @@
       <c r="J100" s="52" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="39">
+      <c r="A101" s="39" t="str">
         <f>Sheet1!$A$35</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO IL MELOGRANO</v>
       </c>
       <c r="B101" s="40" t="inlineStr">
         <is>
@@ -7299,9 +7320,9 @@
       <c r="J101" s="53" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="37">
+      <c r="A102" s="37" t="str">
         <f>Sheet1!$A$35</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO IL MELOGRANO</v>
       </c>
       <c r="B102" s="38" t="inlineStr">
         <is>
@@ -7336,9 +7357,9 @@
       <c r="J102" s="52" t="n"/>
     </row>
     <row r="103" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A103" s="41">
+      <c r="A103" s="41" t="str">
         <f>Sheet1!$A$35</f>
-        <v/>
+        <v>FONDO PENSIONE APERTO IL MELOGRANO</v>
       </c>
       <c r="B103" s="42" t="inlineStr">
         <is>
@@ -9689,15 +9710,15 @@
       </c>
       <c r="H9" s="75">
         <f>B9/B$9</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I9" s="75">
         <f>C9/C$9</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J9" s="75">
         <f>D9/D$9</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -9724,15 +9745,15 @@
       </c>
       <c r="H10" s="75">
         <f>B10/B$9</f>
-        <v/>
+        <v>0.9886443165142793</v>
       </c>
       <c r="I10" s="75">
         <f>C10/C$9</f>
-        <v/>
+        <v>0.993390253570013</v>
       </c>
       <c r="J10" s="75">
         <f>D10/D$9</f>
-        <v/>
+        <v>0.9910236948056234</v>
       </c>
     </row>
     <row r="11">
@@ -9759,15 +9780,15 @@
       </c>
       <c r="H11" s="75">
         <f>B11/B$9</f>
-        <v/>
+        <v>0.9762614290551981</v>
       </c>
       <c r="I11" s="75">
         <f>C11/C$9</f>
-        <v/>
+        <v>0.9862020204184387</v>
       </c>
       <c r="J11" s="75">
         <f>D11/D$9</f>
-        <v/>
+        <v>0.9812443623083185</v>
       </c>
     </row>
     <row r="12">
@@ -9794,15 +9815,15 @@
       </c>
       <c r="H12" s="75">
         <f>B12/B$9</f>
-        <v/>
+        <v>0.9629190653572638</v>
       </c>
       <c r="I12" s="75">
         <f>C12/C$9</f>
-        <v/>
+        <v>0.9784353005452773</v>
       </c>
       <c r="J12" s="75">
         <f>D12/D$9</f>
-        <v/>
+        <v>0.9706840032561107</v>
       </c>
     </row>
     <row r="13">
@@ -9829,15 +9850,15 @@
       </c>
       <c r="H13" s="75">
         <f>B13/B$9</f>
-        <v/>
+        <v>0.9485720735974715</v>
       </c>
       <c r="I13" s="75">
         <f>C13/C$9</f>
-        <v/>
+        <v>0.969972254062798</v>
       </c>
       <c r="J13" s="75">
         <f>D13/D$9</f>
-        <v/>
+        <v>0.9592766154049238</v>
       </c>
     </row>
     <row r="14">
@@ -9864,15 +9885,15 @@
       </c>
       <c r="H14" s="75">
         <f>B14/B$9</f>
-        <v/>
+        <v>0.9328366632802799</v>
       </c>
       <c r="I14" s="75">
         <f>C14/C$9</f>
-        <v/>
+        <v>0.9607271792344693</v>
       </c>
       <c r="J14" s="75">
         <f>D14/D$9</f>
-        <v/>
+        <v>0.9467911909004906</v>
       </c>
     </row>
     <row r="15">
@@ -9899,15 +9920,15 @@
       </c>
       <c r="H15" s="75">
         <f>B15/B$9</f>
-        <v/>
+        <v>0.9153741957331527</v>
       </c>
       <c r="I15" s="75">
         <f>C15/C$9</f>
-        <v/>
+        <v>0.9504108326994976</v>
       </c>
       <c r="J15" s="75">
         <f>D15/D$9</f>
-        <v/>
+        <v>0.9329197192704552</v>
       </c>
     </row>
     <row r="16">
@@ -9934,15 +9955,15 @@
       </c>
       <c r="H16" s="75">
         <f>B16/B$9</f>
-        <v/>
+        <v>0.8962862625578508</v>
       </c>
       <c r="I16" s="75">
         <f>C16/C$9</f>
-        <v/>
+        <v>0.9389803635896172</v>
       </c>
       <c r="J16" s="75">
         <f>D16/D$9</f>
-        <v/>
+        <v>0.9176622005148175</v>
       </c>
     </row>
     <row r="17">
@@ -9969,15 +9990,15 @@
       </c>
       <c r="H17" s="75">
         <f>B17/B$9</f>
-        <v/>
+        <v>0.8751777853030817</v>
       </c>
       <c r="I17" s="75">
         <f>C17/C$9</f>
-        <v/>
+        <v>0.9260715395245697</v>
       </c>
       <c r="J17" s="75">
         <f>D17/D$9</f>
-        <v/>
+        <v>0.9006556222911579</v>
       </c>
     </row>
     <row r="18">
@@ -10004,15 +10025,15 @@
       </c>
       <c r="H18" s="75">
         <f>B18/B$9</f>
-        <v/>
+        <v>0.8523761146856305</v>
       </c>
       <c r="I18" s="75">
         <f>C18/C$9</f>
-        <v/>
+        <v>0.9117272113726205</v>
       </c>
       <c r="J18" s="75">
         <f>D18/D$9</f>
-        <v/>
+        <v>0.8820979913317053</v>
       </c>
     </row>
     <row r="19">
@@ -10039,15 +10060,15 @@
       </c>
       <c r="H19" s="75">
         <f>B19/B$9</f>
-        <v/>
+        <v>0.8273845806524438</v>
       </c>
       <c r="I19" s="75">
         <f>C19/C$9</f>
-        <v/>
+        <v>0.895679561207109</v>
       </c>
       <c r="J19" s="75">
         <f>D19/D$9</f>
-        <v/>
+        <v>0.8615822937979891</v>
       </c>
     </row>
     <row r="20">
@@ -10074,15 +10095,15 @@
       </c>
       <c r="H20" s="75">
         <f>B20/B$9</f>
-        <v/>
+        <v>0.8013771306016481</v>
       </c>
       <c r="I20" s="75">
         <f>C20/C$9</f>
-        <v/>
+        <v>0.8780142907645666</v>
       </c>
       <c r="J20" s="75">
         <f>D20/D$9</f>
-        <v/>
+        <v>0.8397575517567597</v>
       </c>
     </row>
     <row r="21">
@@ -10109,15 +10130,15 @@
       </c>
       <c r="H21" s="75">
         <f>B21/B$9</f>
-        <v/>
+        <v>0.7735748955864094</v>
       </c>
       <c r="I21" s="75">
         <f>C21/C$9</f>
-        <v/>
+        <v>0.8582921786452699</v>
       </c>
       <c r="J21" s="75">
         <f>D21/D$9</f>
-        <v/>
+        <v>0.8160077442633049</v>
       </c>
     </row>
     <row r="22">
@@ -10144,15 +10165,15 @@
       </c>
       <c r="H22" s="75">
         <f>B22/B$9</f>
-        <v/>
+        <v>0.7434924935094255</v>
       </c>
       <c r="I22" s="75">
         <f>C22/C$9</f>
-        <v/>
+        <v>0.8361489924689599</v>
       </c>
       <c r="J22" s="75">
         <f>D22/D$9</f>
-        <v/>
+        <v>0.7899038567311288</v>
       </c>
     </row>
     <row r="23">
@@ -10179,15 +10200,15 @@
       </c>
       <c r="H23" s="75">
         <f>B23/B$9</f>
-        <v/>
+        <v>0.7105429506716334</v>
       </c>
       <c r="I23" s="75">
         <f>C23/C$9</f>
-        <v/>
+        <v>0.8111133726847141</v>
       </c>
       <c r="J23" s="75">
         <f>D23/D$9</f>
-        <v/>
+        <v>0.7609288715816338</v>
       </c>
     </row>
     <row r="24">
@@ -10214,15 +10235,15 @@
       </c>
       <c r="H24" s="75">
         <f>B24/B$9</f>
-        <v/>
+        <v>0.6750197539225646</v>
       </c>
       <c r="I24" s="75">
         <f>C24/C$9</f>
-        <v/>
+        <v>0.7836138279751893</v>
       </c>
       <c r="J24" s="75">
         <f>D24/D$9</f>
-        <v/>
+        <v>0.7294348007832266</v>
       </c>
     </row>
     <row r="25">
@@ -10249,15 +10270,15 @@
       </c>
       <c r="H25" s="75">
         <f>B25/B$9</f>
-        <v/>
+        <v>0.6355683485720736</v>
       </c>
       <c r="I25" s="75">
         <f>C25/C$9</f>
-        <v/>
+        <v>0.7525148103313444</v>
       </c>
       <c r="J25" s="75">
         <f>D25/D$9</f>
-        <v/>
+        <v>0.6941786020724705</v>
       </c>
     </row>
     <row r="26">
@@ -10284,15 +10305,15 @@
       </c>
       <c r="H26" s="75">
         <f>B26/B$9</f>
-        <v/>
+        <v>0.5937464725138277</v>
       </c>
       <c r="I26" s="75">
         <f>C26/C$9</f>
-        <v/>
+        <v>0.7183198174553012</v>
       </c>
       <c r="J26" s="75">
         <f>D26/D$9</f>
-        <v/>
+        <v>0.6561943106065606</v>
       </c>
     </row>
     <row r="27">
@@ -10319,15 +10340,15 @@
       </c>
       <c r="H27" s="75">
         <f>B27/B$9</f>
-        <v/>
+        <v>0.5499040523761147</v>
       </c>
       <c r="I27" s="75">
         <f>C27/C$9</f>
-        <v/>
+        <v>0.680707467835067</v>
       </c>
       <c r="J27" s="75">
         <f>D27/D$9</f>
-        <v/>
+        <v>0.6154929267595098</v>
       </c>
     </row>
     <row r="28">
@@ -10354,15 +10375,15 @@
       </c>
       <c r="H28" s="75">
         <f>B28/B$9</f>
-        <v/>
+        <v>0.5042216954509539</v>
       </c>
       <c r="I28" s="75">
         <f>C28/C$9</f>
-        <v/>
+        <v>0.6400848447191662</v>
       </c>
       <c r="J28" s="75">
         <f>D28/D$9</f>
-        <v/>
+        <v>0.5723714606296614</v>
       </c>
     </row>
     <row r="29">
@@ -10389,15 +10410,15 @@
       </c>
       <c r="H29" s="75">
         <f>B29/B$9</f>
-        <v/>
+        <v>0.45811039620724686</v>
       </c>
       <c r="I29" s="75">
         <f>C29/C$9</f>
-        <v/>
+        <v>0.5973303909070458</v>
       </c>
       <c r="J29" s="75">
         <f>D29/D$9</f>
-        <v/>
+        <v>0.5279629507403252</v>
       </c>
     </row>
     <row r="30">
@@ -10424,15 +10445,15 @@
       </c>
       <c r="H30" s="75">
         <f>B30/B$9</f>
-        <v/>
+        <v>0.4108251495654137</v>
       </c>
       <c r="I30" s="75">
         <f>C30/C$9</f>
-        <v/>
+        <v>0.5514692491456609</v>
       </c>
       <c r="J30" s="75">
         <f>D30/D$9</f>
-        <v/>
+        <v>0.48140936791850925</v>
       </c>
     </row>
     <row r="31">
@@ -10459,15 +10480,15 @@
       </c>
       <c r="H31" s="75">
         <f>B31/B$9</f>
-        <v/>
+        <v>0.36245625917146407</v>
       </c>
       <c r="I31" s="75">
         <f>C31/C$9</f>
-        <v/>
+        <v>0.5023514413960812</v>
       </c>
       <c r="J31" s="75">
         <f>D31/D$9</f>
-        <v/>
+        <v>0.43267771104217545</v>
       </c>
     </row>
     <row r="32">
@@ -10494,15 +10515,15 @@
       </c>
       <c r="H32" s="75">
         <f>B32/B$9</f>
-        <v/>
+        <v>0.31379388192798285</v>
       </c>
       <c r="I32" s="75">
         <f>C32/C$9</f>
-        <v/>
+        <v>0.4502340728679015</v>
       </c>
       <c r="J32" s="75">
         <f>D32/D$9</f>
-        <v/>
+        <v>0.3823069984379469</v>
       </c>
     </row>
     <row r="33">
@@ -10529,15 +10550,15 @@
       </c>
       <c r="H33" s="75">
         <f>B33/B$9</f>
-        <v/>
+        <v>0.26645219550739363</v>
       </c>
       <c r="I33" s="75">
         <f>C33/C$9</f>
-        <v/>
+        <v>0.39624197885309653</v>
       </c>
       <c r="J33" s="75">
         <f>D33/D$9</f>
-        <v/>
+        <v>0.33165027610938774</v>
       </c>
     </row>
     <row r="34">
@@ -10564,15 +10585,15 @@
       </c>
       <c r="H34" s="75">
         <f>B34/B$9</f>
-        <v/>
+        <v>0.22142454001580314</v>
       </c>
       <c r="I34" s="75">
         <f>C34/C$9</f>
-        <v/>
+        <v>0.3420249177798965</v>
       </c>
       <c r="J34" s="75">
         <f>D34/D$9</f>
-        <v/>
+        <v>0.2820275889380239</v>
       </c>
     </row>
     <row r="35">
@@ -10599,15 +10620,15 @@
       </c>
       <c r="H35" s="75">
         <f>B35/B$9</f>
-        <v/>
+        <v>0.17963652782481093</v>
       </c>
       <c r="I35" s="75">
         <f>C35/C$9</f>
-        <v/>
+        <v>0.2885256087501473</v>
       </c>
       <c r="J35" s="75">
         <f>D35/D$9</f>
-        <v/>
+        <v>0.2343629683409236</v>
       </c>
     </row>
     <row r="36">
@@ -10634,15 +10655,15 @@
       </c>
       <c r="H36" s="75">
         <f>B36/B$9</f>
-        <v/>
+        <v>0.14197990743876285</v>
       </c>
       <c r="I36" s="75">
         <f>C36/C$9</f>
-        <v/>
+        <v>0.23783303159180263</v>
       </c>
       <c r="J36" s="75">
         <f>D36/D$9</f>
-        <v/>
+        <v>0.19017446593184167</v>
       </c>
     </row>
     <row r="37">
@@ -10669,15 +10690,15 @@
       </c>
       <c r="H37" s="75">
         <f>B37/B$9</f>
-        <v/>
+        <v>0.10927869962749746</v>
       </c>
       <c r="I37" s="75">
         <f>C37/C$9</f>
-        <v/>
+        <v>0.19162908288429195</v>
       </c>
       <c r="J37" s="75">
         <f>D37/D$9</f>
-        <v/>
+        <v>0.1506941236002024</v>
       </c>
     </row>
     <row r="38">
@@ -10704,15 +10725,15 @@
       </c>
       <c r="H38" s="75">
         <f>B38/B$9</f>
-        <v/>
+        <v>0.08190540693080484</v>
       </c>
       <c r="I38" s="75">
         <f>C38/C$9</f>
-        <v/>
+        <v>0.15061008923693317</v>
       </c>
       <c r="J38" s="75">
         <f>D38/D$9</f>
-        <v/>
+        <v>0.11646095967262887</v>
       </c>
     </row>
     <row r="39">
@@ -10739,15 +10760,15 @@
       </c>
       <c r="H39" s="75">
         <f>B39/B$9</f>
-        <v/>
+        <v>0.059758437746924034</v>
       </c>
       <c r="I39" s="75">
         <f>C39/C$9</f>
-        <v/>
+        <v>0.11539738823957921</v>
       </c>
       <c r="J39" s="75">
         <f>D39/D$9</f>
-        <v/>
+        <v>0.0877609838734517</v>
       </c>
     </row>
     <row r="40">
@@ -10774,15 +10795,15 @@
       </c>
       <c r="H40" s="75">
         <f>B40/B$9</f>
-        <v/>
+        <v>0.04257816909357715</v>
       </c>
       <c r="I40" s="75">
         <f>C40/C$9</f>
-        <v/>
+        <v>0.08606596891169507</v>
       </c>
       <c r="J40" s="75">
         <f>D40/D$9</f>
-        <v/>
+        <v>0.0644621917145183</v>
       </c>
     </row>
     <row r="41">
@@ -10809,15 +10830,15 @@
       </c>
       <c r="H41" s="75">
         <f>B41/B$9</f>
-        <v/>
+        <v>0.029597019979681678</v>
       </c>
       <c r="I41" s="75">
         <f>C41/C$9</f>
-        <v/>
+        <v>0.06227302430715503</v>
       </c>
       <c r="J41" s="75">
         <f>D41/D$9</f>
-        <v/>
+        <v>0.04604756561723099</v>
       </c>
     </row>
     <row r="42">
@@ -10844,15 +10865,15 @@
       </c>
       <c r="H42" s="75">
         <f>B42/B$9</f>
-        <v/>
+        <v>0.01995710576814539</v>
       </c>
       <c r="I42" s="75">
         <f>C42/C$9</f>
-        <v/>
+        <v>0.04346149313850472</v>
       </c>
       <c r="J42" s="75">
         <f>D42/D$9</f>
-        <v/>
+        <v>0.03178008052273777</v>
       </c>
     </row>
     <row r="43">
@@ -10879,15 +10900,15 @@
       </c>
       <c r="H43" s="75">
         <f>B43/B$9</f>
-        <v/>
+        <v>0.012856981600632126</v>
       </c>
       <c r="I43" s="75">
         <f>C43/C$9</f>
-        <v/>
+        <v>0.029042175967090533</v>
       </c>
       <c r="J43" s="75">
         <f>D43/D$9</f>
-        <v/>
+        <v>0.02099971399027567</v>
       </c>
     </row>
     <row r="44">
@@ -10914,15 +10935,15 @@
       </c>
       <c r="H44" s="75">
         <f>B44/B$9</f>
-        <v/>
+        <v>0.007766113556834858</v>
       </c>
       <c r="I44" s="75">
         <f>C44/C$9</f>
-        <v/>
+        <v>0.01842587335425884</v>
       </c>
       <c r="J44" s="75">
         <f>D44/D$9</f>
-        <v/>
+        <v>0.013134446571183421</v>
       </c>
     </row>
     <row r="45">
@@ -10949,15 +10970,15 @@
       </c>
       <c r="H45" s="75">
         <f>B45/B$9</f>
-        <v/>
+        <v>0.004447454565978101</v>
       </c>
       <c r="I45" s="75">
         <f>C45/C$9</f>
-        <v/>
+        <v>0.011119800314953882</v>
       </c>
       <c r="J45" s="75">
         <f>D45/D$9</f>
-        <v/>
+        <v>0.0078102655490286665</v>
       </c>
     </row>
     <row r="46">
@@ -10984,15 +11005,15 @@
       </c>
       <c r="H46" s="75">
         <f>B46/B$9</f>
-        <v/>
+        <v>0.0023930466192572525</v>
       </c>
       <c r="I46" s="75">
         <f>C46/C$9</f>
-        <v/>
+        <v>0.006363353937459158</v>
       </c>
       <c r="J46" s="75">
         <f>D46/D$9</f>
-        <v/>
+        <v>0.004389149231073856</v>
       </c>
     </row>
     <row r="47">
@@ -11019,15 +11040,15 @@
       </c>
       <c r="H47" s="75">
         <f>B47/B$9</f>
-        <v/>
+        <v>0.0012078112653798397</v>
       </c>
       <c r="I47" s="75">
         <f>C47/C$9</f>
-        <v/>
+        <v>0.0034280694612574586</v>
       </c>
       <c r="J47" s="75">
         <f>D47/D$9</f>
-        <v/>
+        <v>0.0023320792906958835</v>
       </c>
     </row>
     <row r="48">
@@ -11054,15 +11075,15 @@
       </c>
       <c r="H48" s="75">
         <f>B48/B$9</f>
-        <v/>
+        <v>0.0005756857433118863</v>
       </c>
       <c r="I48" s="75">
         <f>C48/C$9</f>
-        <v/>
+        <v>0.0017354601647615886</v>
       </c>
       <c r="J48" s="75">
         <f>D48/D$9</f>
-        <v/>
+        <v>0.0011550392713352254</v>
       </c>
     </row>
     <row r="49">
@@ -11089,15 +11110,15 @@
       </c>
       <c r="H49" s="75">
         <f>B49/B$9</f>
-        <v/>
+        <v>0.000248335026526696</v>
       </c>
       <c r="I49" s="75">
         <f>C49/C$9</f>
-        <v/>
+        <v>0.000824879214115076</v>
       </c>
       <c r="J49" s="75">
         <f>D49/D$9</f>
-        <v/>
+        <v>0.0005390183266231052</v>
       </c>
     </row>
     <row r="50">
@@ -11124,15 +11145,15 @@
       </c>
       <c r="H50" s="75">
         <f>B50/B$9</f>
-        <v/>
+        <v>0.00010159160176092109</v>
       </c>
       <c r="I50" s="75">
         <f>C50/C$9</f>
-        <v/>
+        <v>0.00036423238025860496</v>
       </c>
       <c r="J50" s="75">
         <f>D50/D$9</f>
-        <v/>
+        <v>0.00023100785426704508</v>
       </c>
     </row>
     <row r="51">
@@ -11159,15 +11180,15 @@
       </c>
       <c r="H51" s="75">
         <f>B51/B$9</f>
-        <v/>
+        <v>3.3863867253640366e-05</v>
       </c>
       <c r="I51" s="75">
         <f>C51/C$9</f>
-        <v/>
+        <v>0.00014997803893001383</v>
       </c>
       <c r="J51" s="75">
         <f>D51/D$9</f>
-        <v/>
+        <v>9.90033661144479e-05</v>
       </c>
     </row>
     <row r="52">
@@ -11194,15 +11215,15 @@
       </c>
       <c r="H52" s="75">
         <f>B52/B$9</f>
-        <v/>
+        <v>1.1287955751213456e-05</v>
       </c>
       <c r="I52" s="75">
         <f>C52/C$9</f>
-        <v/>
+        <v>5.356358533214779e-05</v>
       </c>
       <c r="J52" s="75">
         <f>D52/D$9</f>
-        <v/>
+        <v>3.30011220381493e-05</v>
       </c>
     </row>
   </sheetData>
@@ -13073,4 +13094,2792 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="80" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="66" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="B1" s="66" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (fonte)</t>
+        </is>
+      </c>
+      <c r="C1" s="66" t="inlineStr">
+        <is>
+          <t>Compagnia che paga la rendita</t>
+        </is>
+      </c>
+      <c r="D1" s="66" t="inlineStr">
+        <is>
+          <t>Rendita reversibile</t>
+        </is>
+      </c>
+      <c r="E1" s="66" t="inlineStr">
+        <is>
+          <t>Rendita certa e poi vitalizia</t>
+        </is>
+      </c>
+      <c r="F1" s="66" t="inlineStr">
+        <is>
+          <t>Rendita controassicurata</t>
+        </is>
+      </c>
+      <c r="G1" s="66" t="inlineStr">
+        <is>
+          <t>Rendita con LTC (non autosufficienza)</t>
+        </is>
+      </c>
+      <c r="H1" s="66" t="inlineStr">
+        <is>
+          <t>N. varianti oltre alla vitalizia</t>
+        </is>
+      </c>
+      <c r="I1" s="66" t="inlineStr">
+        <is>
+          <t>Rendita annua a 67 anni ogni 10.000 €</t>
+        </is>
+      </c>
+      <c r="J1" s="66" t="inlineStr">
+        <is>
+          <t>Tasso di conversione a 67 anni</t>
+        </is>
+      </c>
+      <c r="K1" s="66" t="inlineStr">
+        <is>
+          <t>Tasso tecnico</t>
+        </is>
+      </c>
+      <c r="L1" s="66" t="inlineStr">
+        <is>
+          <t>Basi del coefficiente</t>
+        </is>
+      </c>
+      <c r="M1" s="66" t="inlineStr">
+        <is>
+          <t>Costo della rendita (rata annuale)</t>
+        </is>
+      </c>
+      <c r="N1" s="66" t="inlineStr">
+        <is>
+          <t>Costo anticipazione (€)</t>
+        </is>
+      </c>
+      <c r="O1" s="66" t="inlineStr">
+        <is>
+          <t>Costo riscatto (€)</t>
+        </is>
+      </c>
+      <c r="P1" s="66" t="inlineStr">
+        <is>
+          <t>Costo trasferimento (€)</t>
+        </is>
+      </c>
+      <c r="Q1" s="66" t="inlineStr">
+        <is>
+          <t>Costo RITA (€)</t>
+        </is>
+      </c>
+      <c r="R1" s="66" t="inlineStr">
+        <is>
+          <t>Scheda costi (fonte)</t>
+        </is>
+      </c>
+      <c r="S1" s="66" t="inlineStr">
+        <is>
+          <t>Nuove prestazioni (durata definita e prelievi)</t>
+        </is>
+      </c>
+      <c r="T1" s="66" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (fonte)</t>
+        </is>
+      </c>
+      <c r="U1" s="66" t="inlineStr">
+        <is>
+          <t>Consultata il</t>
+        </is>
+      </c>
+      <c r="V1" s="66" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="67" t="str">
+        <f>Sheet1!$A$3</f>
+        <v>ALLIANZ PREVIDENZA FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
+      </c>
+      <c r="B2" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C2" s="67" t="inlineStr">
+        <is>
+          <t>Allianz S.p.A.</t>
+        </is>
+      </c>
+      <c r="D2" s="67" t="inlineStr">
+        <is>
+          <t>Sì (100% o 60%)</t>
+        </is>
+      </c>
+      <c r="E2" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F2" s="67" t="inlineStr">
+        <is>
+          <t>Sì (cashback)</t>
+        </is>
+      </c>
+      <c r="G2" s="67" t="inlineStr">
+        <is>
+          <t>Sì (rendita raddoppiata, con questionario medico)</t>
+        </is>
+      </c>
+      <c r="H2" s="78">
+        <f>COUNTIF(D2:G2,"Sì*")</f>
+        <v>4</v>
+      </c>
+      <c r="I2" s="79" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="J2" s="80">
+        <f>IF(I2="","",I2/10000)</f>
+        <v>0.04625</v>
+      </c>
+      <c r="K2" s="81" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L2" s="67" t="inlineStr">
+        <is>
+          <t>Tavola AZPS62, nati 1955–1962 senza correzione d'età, tasso tecnico 0,5% (rata iniziale più alta, rivalutazioni più basse)</t>
+        </is>
+      </c>
+      <c r="M2" s="80" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="N2" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="79" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (settembre 2026)</t>
+        </is>
+      </c>
+      <c r="S2" s="67" t="inlineStr">
+        <is>
+          <t>Rendita a durata definita a rate trimestrali (19 anni a 67 anni); prelievi ogni 3 mesi almeno, minimo 500 €; comparto predefinito Linea Flessibile con garanzia; nessuna spesa di erogazione</t>
+        </is>
+      </c>
+      <c r="T2" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (settembre 2026)</t>
+        </is>
+      </c>
+      <c r="U2" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V2" s="67" t="inlineStr">
+        <is>
+          <t>Costo della rendita dall'1,80% (rata annuale) al 3,30% (mensile); rivalutazione annua con 1,20 punti trattenuti dalla gestione separata VITARIV Group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="67" t="str">
+        <f>Sheet1!$A$4</f>
+        <v>PREVIDENZA PER TE - FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B3" s="68" t="inlineStr">
+        <is>
+          <t>Documento sull'erogazione delle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C3" s="67" t="inlineStr">
+        <is>
+          <t>AXA MPS Assicurazioni Vita S.p.A.</t>
+        </is>
+      </c>
+      <c r="D3" s="67" t="inlineStr">
+        <is>
+          <t>Sì (totale o parziale)</t>
+        </is>
+      </c>
+      <c r="E3" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F3" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H3" s="78">
+        <f>COUNTIF(D3:G3,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I3" s="79" t="n">
+        <v>421.6</v>
+      </c>
+      <c r="J3" s="80">
+        <f>IF(I3="","",I3/10000)</f>
+        <v>0.04216</v>
+      </c>
+      <c r="K3" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62I, nati 1958–1966 senza correzione d'età, tasso tecnico 0% (Regolamento, allegato n. 2: 42,16 € per 1.000 €)</t>
+        </is>
+      </c>
+      <c r="M3" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N3" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="O3" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="P3" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q3" s="79" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi</t>
+        </is>
+      </c>
+      <c r="S3" s="67" t="inlineStr">
+        <is>
+          <t>Rendita a durata definita a rate trimestrali, anche per una durata più lunga della vita attesa; prelievi senza importo minimo; 5 € per ogni rata o prelievo</t>
+        </is>
+      </c>
+      <c r="T3" s="68" t="inlineStr">
+        <is>
+          <t>Informativa sulle nuove prestazioni pensionistiche (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U3" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V3" s="67" t="inlineStr">
+        <is>
+          <t>RITA: 5 € su ogni rata trimestrale. Rivalutazione della rendita con almeno 0,75 punti trattenuti dalla gestione separata MPV12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="67" t="str">
+        <f>Sheet1!$A$5</f>
+        <v>ALMEGLIO - FONDO PENSIONE APERTO ALLEANZA A CONTRIBUZIONE DEFINITA</v>
+      </c>
+      <c r="B4" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C4" s="67" t="inlineStr">
+        <is>
+          <t>Alleanza Assicurazioni S.p.A.</t>
+        </is>
+      </c>
+      <c r="D4" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E4" s="67" t="n"/>
+      <c r="F4" s="67" t="n"/>
+      <c r="G4" s="67" t="n"/>
+      <c r="H4" s="78">
+        <f>COUNTIF(D4:G4,"Sì*")</f>
+        <v>1</v>
+      </c>
+      <c r="I4" s="79" t="n"/>
+      <c r="J4" s="80" t="str">
+        <f>IF(I4="","",I4/10000)</f>
+        <v/>
+      </c>
+      <c r="K4" s="81" t="n"/>
+      <c r="L4" s="67" t="inlineStr">
+        <is>
+          <t>Coefficienti diversi secondo la data di adesione (tasso tecnico 2,5%, 2% o 1,75%; tavola RG48 per le adesioni più vecchie)</t>
+        </is>
+      </c>
+      <c r="M4" s="80" t="n"/>
+      <c r="N4" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="79" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="Q4" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="68" t="inlineStr">
+        <is>
+          <t>Scheda I costi (maggio 2021)</t>
+        </is>
+      </c>
+      <c r="S4" s="67" t="inlineStr">
+        <is>
+          <t>Previste dal 1/7/2026 (documento sulle rendite, ed. luglio 2026)</t>
+        </is>
+      </c>
+      <c r="T4" s="67" t="n"/>
+      <c r="U4" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V4" s="67" t="inlineStr">
+        <is>
+          <t>Fondo chiuso a nuove adesioni, confluisce in Generali Global dal 1/1/2027: coefficienti non confrontabili con quelli di un nuovo iscritto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="67" t="str">
+        <f>Sheet1!$A$6</f>
+        <v>FONDO PENSIONE FIDEURAM FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B5" s="67" t="n"/>
+      <c r="C5" s="67" t="n"/>
+      <c r="D5" s="67" t="n"/>
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+      <c r="G5" s="67" t="n"/>
+      <c r="H5" s="78">
+        <f>COUNTIF(D5:G5,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="79" t="n"/>
+      <c r="J5" s="80" t="str">
+        <f>IF(I5="","",I5/10000)</f>
+        <v/>
+      </c>
+      <c r="K5" s="81" t="n"/>
+      <c r="L5" s="67" t="n"/>
+      <c r="M5" s="80" t="n"/>
+      <c r="N5" s="79" t="n"/>
+      <c r="O5" s="79" t="n"/>
+      <c r="P5" s="79" t="n"/>
+      <c r="Q5" s="79" t="n"/>
+      <c r="R5" s="67" t="n"/>
+      <c r="S5" s="67" t="n"/>
+      <c r="T5" s="67" t="n"/>
+      <c r="U5" s="83" t="n"/>
+      <c r="V5" s="67" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="67" t="str">
+        <f>Sheet1!$A$7</f>
+        <v>GENERALI GLOBAL - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
+      </c>
+      <c r="B6" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C6" s="67" t="inlineStr">
+        <is>
+          <t>Generali Italia S.p.A.</t>
+        </is>
+      </c>
+      <c r="D6" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E6" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F6" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="G6" s="67" t="inlineStr">
+        <is>
+          <t>Sì (rendita raddoppiata)</t>
+        </is>
+      </c>
+      <c r="H6" s="78">
+        <f>COUNTIF(D6:G6,"Sì*")</f>
+        <v>4</v>
+      </c>
+      <c r="I6" s="79" t="n">
+        <v>424.3</v>
+      </c>
+      <c r="J6" s="80">
+        <f>IF(I6="","",I6/10000)</f>
+        <v>0.04243</v>
+      </c>
+      <c r="K6" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62U unisex, nati 1958–1966 senza correzione d'età, tasso tecnico 0% (Regolamento, allegato A)</t>
+        </is>
+      </c>
+      <c r="M6" s="80" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="N6" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="O6" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="P6" s="79" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="R6" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="S6" s="67" t="inlineStr">
+        <is>
+          <t>Rate annuali, semestrali, trimestrali o mensili (minimo 200 € a rata); comparto predefinito Obbligazionario Breve Termine; 20 € per accedere, 5 € a rata</t>
+        </is>
+      </c>
+      <c r="T6" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U6" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V6" s="67" t="inlineStr">
+        <is>
+          <t>Coefficienti nel Regolamento (luglio 2026), allegato A all'allegato n. 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="67" t="str">
+        <f>Sheet1!$A$8</f>
+        <v>PREVIDSYSTEM - FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B7" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (giugno 2026)</t>
+        </is>
+      </c>
+      <c r="C7" s="67" t="inlineStr">
+        <is>
+          <t>Intesa Sanpaolo Assicurazioni S.p.A.</t>
+        </is>
+      </c>
+      <c r="D7" s="67" t="inlineStr">
+        <is>
+          <t>Sì (100% o 50%)</t>
+        </is>
+      </c>
+      <c r="E7" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="G7" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="78">
+        <f>COUNTIF(D7:G7,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I7" s="79" t="n">
+        <v>429.1</v>
+      </c>
+      <c r="J7" s="80">
+        <f>IF(I7="","",I7/10000)</f>
+        <v>0.042910000000000004</v>
+      </c>
+      <c r="K7" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62D/A per anno di nascita (nati 1958–1966 senza correzione), tasso tecnico 0%</t>
+        </is>
+      </c>
+      <c r="M7" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N7" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="O7" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="P7" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q7" s="79" t="n"/>
+      <c r="R7" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa (marzo 2026)</t>
+        </is>
+      </c>
+      <c r="S7" s="67" t="inlineStr">
+        <is>
+          <t>Rate mensili, trimestrali o annuali (minimo 150 € a rata); comparto predefinito Crescita Prudente; 20 € per accedere, 2 € a rata</t>
+        </is>
+      </c>
+      <c r="T7" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U7" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V7" s="67" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="67" t="str">
+        <f>Sheet1!$A$9</f>
+        <v>FONDO PENSIONE APERTO TESEO</v>
+      </c>
+      <c r="B8" s="67" t="n"/>
+      <c r="C8" s="67" t="inlineStr">
+        <is>
+          <t>Società Reale Mutua di Assicurazioni</t>
+        </is>
+      </c>
+      <c r="D8" s="67" t="n"/>
+      <c r="E8" s="67" t="n"/>
+      <c r="F8" s="67" t="n"/>
+      <c r="G8" s="67" t="n"/>
+      <c r="H8" s="78">
+        <f>COUNTIF(D8:G8,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="79" t="n"/>
+      <c r="J8" s="80" t="str">
+        <f>IF(I8="","",I8/10000)</f>
+        <v/>
+      </c>
+      <c r="K8" s="81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L8" s="67" t="inlineStr">
+        <is>
+          <t>Tasso tecnico 1% per chi ha aderito dal 21/12/2012 (2% prima); rivalutazione con l'80% del rendimento della gestione separata Previ Reale (scheda I costi)</t>
+        </is>
+      </c>
+      <c r="M8" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N8" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="S8" s="67" t="n"/>
+      <c r="T8" s="67" t="n"/>
+      <c r="U8" s="83" t="n">
+        <v>46304</v>
+      </c>
+      <c r="V8" s="67" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite non trovato: la Nota informativa rimanda al sito www.fondoteseo.com. Nessuna spesa per anticipazioni, riscatti, trasferimenti e RITA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="67" t="str">
+        <f>Sheet1!$A$10</f>
+        <v>DESTINAZIONE FUTURO - FONDO PENSIONE APERTO BY CREDEMVITA</v>
+      </c>
+      <c r="B9" s="67" t="n"/>
+      <c r="C9" s="67" t="n"/>
+      <c r="D9" s="67" t="n"/>
+      <c r="E9" s="67" t="n"/>
+      <c r="F9" s="67" t="n"/>
+      <c r="G9" s="67" t="n"/>
+      <c r="H9" s="78">
+        <f>COUNTIF(D9:G9,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="79" t="n"/>
+      <c r="J9" s="80" t="str">
+        <f>IF(I9="","",I9/10000)</f>
+        <v/>
+      </c>
+      <c r="K9" s="81" t="n"/>
+      <c r="L9" s="67" t="n"/>
+      <c r="M9" s="80" t="n"/>
+      <c r="N9" s="79" t="n"/>
+      <c r="O9" s="79" t="n"/>
+      <c r="P9" s="79" t="n"/>
+      <c r="Q9" s="79" t="n"/>
+      <c r="R9" s="67" t="n"/>
+      <c r="S9" s="67" t="n"/>
+      <c r="T9" s="67" t="n"/>
+      <c r="U9" s="83" t="n"/>
+      <c r="V9" s="67" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="67" t="str">
+        <f>Sheet1!$A$11</f>
+        <v>FONDO PENSIONE APERTO VITTORIA FORMULA LAVORO</v>
+      </c>
+      <c r="B10" s="67" t="n"/>
+      <c r="C10" s="67" t="n"/>
+      <c r="D10" s="67" t="n"/>
+      <c r="E10" s="67" t="n"/>
+      <c r="F10" s="67" t="n"/>
+      <c r="G10" s="67" t="n"/>
+      <c r="H10" s="78">
+        <f>COUNTIF(D10:G10,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="79" t="n"/>
+      <c r="J10" s="80" t="str">
+        <f>IF(I10="","",I10/10000)</f>
+        <v/>
+      </c>
+      <c r="K10" s="81" t="n"/>
+      <c r="L10" s="67" t="n"/>
+      <c r="M10" s="80" t="n"/>
+      <c r="N10" s="79" t="n"/>
+      <c r="O10" s="79" t="n"/>
+      <c r="P10" s="79" t="n"/>
+      <c r="Q10" s="79" t="n"/>
+      <c r="R10" s="67" t="n"/>
+      <c r="S10" s="67" t="n"/>
+      <c r="T10" s="67" t="n"/>
+      <c r="U10" s="83" t="n"/>
+      <c r="V10" s="67" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="67" t="str">
+        <f>Sheet1!$A$12</f>
+        <v>ARCA PREVIDENZA FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B11" s="67" t="n"/>
+      <c r="C11" s="67" t="n"/>
+      <c r="D11" s="67" t="n"/>
+      <c r="E11" s="67" t="n"/>
+      <c r="F11" s="67" t="n"/>
+      <c r="G11" s="67" t="n"/>
+      <c r="H11" s="78">
+        <f>COUNTIF(D11:G11,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="79" t="n"/>
+      <c r="J11" s="80" t="str">
+        <f>IF(I11="","",I11/10000)</f>
+        <v/>
+      </c>
+      <c r="K11" s="81" t="n"/>
+      <c r="L11" s="67" t="n"/>
+      <c r="M11" s="80" t="n"/>
+      <c r="N11" s="79" t="n"/>
+      <c r="O11" s="79" t="n"/>
+      <c r="P11" s="79" t="n"/>
+      <c r="Q11" s="79" t="n"/>
+      <c r="R11" s="67" t="n"/>
+      <c r="S11" s="67" t="n"/>
+      <c r="T11" s="67" t="n"/>
+      <c r="U11" s="83" t="n"/>
+      <c r="V11" s="67" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="67" t="str">
+        <f>Sheet1!$A$13</f>
+        <v>FONDO PENSIONE APERTO UNIPOL PREVIDENZA FPA</v>
+      </c>
+      <c r="B12" s="67" t="n"/>
+      <c r="C12" s="67" t="n"/>
+      <c r="D12" s="67" t="n"/>
+      <c r="E12" s="67" t="n"/>
+      <c r="F12" s="67" t="n"/>
+      <c r="G12" s="67" t="n"/>
+      <c r="H12" s="78">
+        <f>COUNTIF(D12:G12,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="79" t="n"/>
+      <c r="J12" s="80" t="str">
+        <f>IF(I12="","",I12/10000)</f>
+        <v/>
+      </c>
+      <c r="K12" s="81" t="n"/>
+      <c r="L12" s="67" t="n"/>
+      <c r="M12" s="80" t="n"/>
+      <c r="N12" s="79" t="n"/>
+      <c r="O12" s="79" t="n"/>
+      <c r="P12" s="79" t="n"/>
+      <c r="Q12" s="79" t="n"/>
+      <c r="R12" s="67" t="n"/>
+      <c r="S12" s="67" t="n"/>
+      <c r="T12" s="67" t="n"/>
+      <c r="U12" s="83" t="n"/>
+      <c r="V12" s="67" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="67" t="str">
+        <f>Sheet1!$A$14</f>
+        <v>FONDO PENSIONE APERTO VERA VITA</v>
+      </c>
+      <c r="B13" s="67" t="n"/>
+      <c r="C13" s="67" t="n"/>
+      <c r="D13" s="67" t="n"/>
+      <c r="E13" s="67" t="n"/>
+      <c r="F13" s="67" t="n"/>
+      <c r="G13" s="67" t="n"/>
+      <c r="H13" s="78">
+        <f>COUNTIF(D13:G13,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="79" t="n"/>
+      <c r="J13" s="80" t="str">
+        <f>IF(I13="","",I13/10000)</f>
+        <v/>
+      </c>
+      <c r="K13" s="81" t="n"/>
+      <c r="L13" s="67" t="n"/>
+      <c r="M13" s="80" t="n"/>
+      <c r="N13" s="79" t="n"/>
+      <c r="O13" s="79" t="n"/>
+      <c r="P13" s="79" t="n"/>
+      <c r="Q13" s="79" t="n"/>
+      <c r="R13" s="67" t="n"/>
+      <c r="S13" s="67" t="n"/>
+      <c r="T13" s="67" t="n"/>
+      <c r="U13" s="83" t="n"/>
+      <c r="V13" s="67" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="67" t="str">
+        <f>Sheet1!$A$15</f>
+        <v>UNICREDIT - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
+      </c>
+      <c r="B14" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C14" s="67" t="inlineStr">
+        <is>
+          <t>UniCredit Vita Assicurazioni S.p.A. (oggi UniCredit Allianz Vita)</t>
+        </is>
+      </c>
+      <c r="D14" s="67" t="inlineStr">
+        <is>
+          <t>Sì (totale o parziale)</t>
+        </is>
+      </c>
+      <c r="E14" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F14" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="78">
+        <f>COUNTIF(D14:G14,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I14" s="79" t="n"/>
+      <c r="J14" s="80" t="str">
+        <f>IF(I14="","",I14/10000)</f>
+        <v/>
+      </c>
+      <c r="K14" s="81" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L14" s="67" t="inlineStr">
+        <is>
+          <t>Tavola RG48 distinta per sesso, con correzione d'età per anno di nascita, tasso tecnico 2%</t>
+        </is>
+      </c>
+      <c r="M14" s="80" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="N14" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q14" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (marzo 2026)</t>
+        </is>
+      </c>
+      <c r="S14" s="67" t="inlineStr">
+        <is>
+          <t>Rendita a durata definita a rate trimestrali; comparto predefinito Linea Tranquilla; nessuna spesa di erogazione oltre a quelle di gestione</t>
+        </is>
+      </c>
+      <c r="T14" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U14" s="83" t="n">
+        <v>46304</v>
+      </c>
+      <c r="V14" s="67" t="inlineStr">
+        <is>
+          <t>Coefficienti diversi per uomini e donne (tavola RG48, tasso tecnico 2%): a 67 anni, prima della correzione per anno di nascita, 684,6 € (uomini) e 575,5 € (donne) l'anno ogni 10.000 €, non confrontabili con i coefficienti unisex degli altri fondi. Documenti pubblicati nell'archivio prodotti di UniCredit Allianz Vita. Costo della rendita dall'1,80% (annuale) al 3,30% (mensile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="67" t="str">
+        <f>Sheet1!$A$16</f>
+        <v>FONDO PENSIONE APERTO PREVIGEST FUND MEDIOLANUM</v>
+      </c>
+      <c r="B15" s="68" t="inlineStr">
+        <is>
+          <t>Documento sull'erogazione delle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C15" s="67" t="inlineStr">
+        <is>
+          <t>Mediolanum Vita S.p.A.</t>
+        </is>
+      </c>
+      <c r="D15" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F15" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="78">
+        <f>COUNTIF(D15:G15,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I15" s="79" t="n"/>
+      <c r="J15" s="80" t="str">
+        <f>IF(I15="","",I15/10000)</f>
+        <v/>
+      </c>
+      <c r="K15" s="81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L15" s="67" t="inlineStr">
+        <is>
+          <t>Tavola IPS55U unisex (adesioni individuali), tasso tecnico 1%</t>
+        </is>
+      </c>
+      <c r="M15" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N15" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="68" t="inlineStr">
+        <is>
+          <t>Scheda I costi</t>
+        </is>
+      </c>
+      <c r="S15" s="67" t="inlineStr">
+        <is>
+          <t>Rate mensili, trimestrali, semestrali o annuali; comparto predefinito Obbligazionario; nessun costo per accedere né a rata</t>
+        </is>
+      </c>
+      <c r="T15" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U15" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V15" s="67" t="inlineStr">
+        <is>
+          <t>I coefficienti non sono pubblicati nel documento sulle rendite (rinvio alle tabelle depositate presso il fondo). Tasso tecnico 1%: rata iniziale più alta, rivalutazioni successive più basse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="67" t="str">
+        <f>Sheet1!$A$17</f>
+        <v>FONDO PENSIONE APERTO ZURICH CONTRIBUTION</v>
+      </c>
+      <c r="B16" s="67" t="n"/>
+      <c r="C16" s="67" t="n"/>
+      <c r="D16" s="67" t="n"/>
+      <c r="E16" s="67" t="n"/>
+      <c r="F16" s="67" t="n"/>
+      <c r="G16" s="67" t="n"/>
+      <c r="H16" s="78">
+        <f>COUNTIF(D16:G16,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="79" t="n"/>
+      <c r="J16" s="80" t="str">
+        <f>IF(I16="","",I16/10000)</f>
+        <v/>
+      </c>
+      <c r="K16" s="81" t="n"/>
+      <c r="L16" s="67" t="n"/>
+      <c r="M16" s="80" t="n"/>
+      <c r="N16" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="79" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="P16" s="79" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="Q16" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (marzo 2026)</t>
+        </is>
+      </c>
+      <c r="S16" s="67" t="n"/>
+      <c r="T16" s="67" t="n"/>
+      <c r="U16" s="83" t="n">
+        <v>46304</v>
+      </c>
+      <c r="V16" s="67" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite e supplemento non trovati sul sito pubblico. RITA: 2 € su ogni rata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="67" t="str">
+        <f>Sheet1!$A$18</f>
+        <v>ZED OMNIFUND - FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B17" s="67" t="n"/>
+      <c r="C17" s="67" t="n"/>
+      <c r="D17" s="67" t="n"/>
+      <c r="E17" s="67" t="n"/>
+      <c r="F17" s="67" t="n"/>
+      <c r="G17" s="67" t="n"/>
+      <c r="H17" s="78">
+        <f>COUNTIF(D17:G17,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="79" t="n"/>
+      <c r="J17" s="80" t="str">
+        <f>IF(I17="","",I17/10000)</f>
+        <v/>
+      </c>
+      <c r="K17" s="81" t="n"/>
+      <c r="L17" s="67" t="n"/>
+      <c r="M17" s="80" t="n"/>
+      <c r="N17" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="79" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q17" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (marzo 2026)</t>
+        </is>
+      </c>
+      <c r="S17" s="67" t="n"/>
+      <c r="T17" s="67" t="n"/>
+      <c r="U17" s="83" t="n">
+        <v>46304</v>
+      </c>
+      <c r="V17" s="67" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite e supplemento non trovati sul sito pubblico. RITA: 2 € su ogni rata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="67" t="str">
+        <f>Sheet1!$A$19</f>
+        <v>PLURIFONDS IL FONDO PENSIONE APERTO DI ITAS VITA</v>
+      </c>
+      <c r="B18" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (febbraio 2021)</t>
+        </is>
+      </c>
+      <c r="C18" s="67" t="inlineStr">
+        <is>
+          <t>ITAS Vita S.p.A.</t>
+        </is>
+      </c>
+      <c r="D18" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E18" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F18" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" s="78">
+        <f>COUNTIF(D18:G18,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I18" s="79" t="n">
+        <v>424.8</v>
+      </c>
+      <c r="J18" s="80">
+        <f>IF(I18="","",I18/10000)</f>
+        <v>0.042480000000000004</v>
+      </c>
+      <c r="K18" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62D unisex, nati 1958–1966 senza correzione, tasso tecnico 0%</t>
+        </is>
+      </c>
+      <c r="M18" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N18" s="79" t="n"/>
+      <c r="O18" s="79" t="n"/>
+      <c r="P18" s="79" t="n"/>
+      <c r="Q18" s="79" t="n"/>
+      <c r="R18" s="67" t="n"/>
+      <c r="S18" s="67" t="n"/>
+      <c r="T18" s="67" t="n"/>
+      <c r="U18" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V18" s="67" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite del 2021, precedente alle nuove prestazioni. Oltre all'1,25% di erogazione, caricamento di gestione dell'1% sul premio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="67" t="str">
+        <f>Sheet1!$A$20</f>
+        <v>EURORISPARMIO PREVIDENZA COMPLEMENTARE FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B19" s="67" t="n"/>
+      <c r="C19" s="67" t="n"/>
+      <c r="D19" s="67" t="n"/>
+      <c r="E19" s="67" t="n"/>
+      <c r="F19" s="67" t="n"/>
+      <c r="G19" s="67" t="n"/>
+      <c r="H19" s="78">
+        <f>COUNTIF(D19:G19,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="79" t="n"/>
+      <c r="J19" s="80" t="str">
+        <f>IF(I19="","",I19/10000)</f>
+        <v/>
+      </c>
+      <c r="K19" s="81" t="n"/>
+      <c r="L19" s="67" t="n"/>
+      <c r="M19" s="80" t="n"/>
+      <c r="N19" s="79" t="n"/>
+      <c r="O19" s="79" t="n"/>
+      <c r="P19" s="79" t="n"/>
+      <c r="Q19" s="79" t="n"/>
+      <c r="R19" s="67" t="n"/>
+      <c r="S19" s="67" t="n"/>
+      <c r="T19" s="67" t="n"/>
+      <c r="U19" s="83" t="n"/>
+      <c r="V19" s="67" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="67" t="str">
+        <f>Sheet1!$A$21</f>
+        <v>FONDO PENSIONE APERTO AUREO</v>
+      </c>
+      <c r="B20" s="67" t="n"/>
+      <c r="C20" s="67" t="n"/>
+      <c r="D20" s="67" t="n"/>
+      <c r="E20" s="67" t="n"/>
+      <c r="F20" s="67" t="n"/>
+      <c r="G20" s="67" t="n"/>
+      <c r="H20" s="78">
+        <f>COUNTIF(D20:G20,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="79" t="n"/>
+      <c r="J20" s="80" t="str">
+        <f>IF(I20="","",I20/10000)</f>
+        <v/>
+      </c>
+      <c r="K20" s="81" t="n"/>
+      <c r="L20" s="67" t="n"/>
+      <c r="M20" s="80" t="n"/>
+      <c r="N20" s="79" t="n"/>
+      <c r="O20" s="79" t="n"/>
+      <c r="P20" s="79" t="n"/>
+      <c r="Q20" s="79" t="n"/>
+      <c r="R20" s="67" t="n"/>
+      <c r="S20" s="67" t="n"/>
+      <c r="T20" s="67" t="n"/>
+      <c r="U20" s="83" t="n"/>
+      <c r="V20" s="67" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="67" t="str">
+        <f>Sheet1!$A$22</f>
+        <v>FONDO PENSIONE APERTO CREDIT AGRICOLE VITA</v>
+      </c>
+      <c r="B21" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (maggio 2022)</t>
+        </is>
+      </c>
+      <c r="C21" s="67" t="inlineStr">
+        <is>
+          <t>Crédit Agricole Vita S.p.A.</t>
+        </is>
+      </c>
+      <c r="D21" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F21" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" s="78">
+        <f>COUNTIF(D21:G21,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I21" s="79" t="n">
+        <v>429.4</v>
+      </c>
+      <c r="J21" s="80">
+        <f>IF(I21="","",I21/10000)</f>
+        <v>0.04294</v>
+      </c>
+      <c r="K21" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62I unisex, nati 1958–1966 senza correzione, tasso tecnico 0%</t>
+        </is>
+      </c>
+      <c r="M21" s="80" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="N21" s="79" t="n"/>
+      <c r="O21" s="79" t="n"/>
+      <c r="P21" s="79" t="n"/>
+      <c r="Q21" s="79" t="n"/>
+      <c r="R21" s="67" t="n"/>
+      <c r="S21" s="67" t="inlineStr">
+        <is>
+          <t>Rate annuali, semestrali o trimestrali; comparto predefinito Linea Garantita</t>
+        </is>
+      </c>
+      <c r="T21" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U21" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V21" s="67" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite del 2022: verificare se è stato aggiornato. Costo della rendita dallo 0,90% (annuale) al 2% (mensile), dal supplemento 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="67" t="str">
+        <f>Sheet1!$A$23</f>
+        <v>ARTI &amp; MESTIERI - FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B22" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (allegato n. 2 al Regolamento)</t>
+        </is>
+      </c>
+      <c r="C22" s="67" t="inlineStr">
+        <is>
+          <t>Unipol Assicurazioni S.p.A. (convenzione nata con Fondiaria-SAI)</t>
+        </is>
+      </c>
+      <c r="D22" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E22" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F22" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="G22" s="67" t="inlineStr">
+        <is>
+          <t>Sì (rendita raddoppiata)</t>
+        </is>
+      </c>
+      <c r="H22" s="78">
+        <f>COUNTIF(D22:G22,"Sì*")</f>
+        <v>4</v>
+      </c>
+      <c r="I22" s="79" t="n">
+        <v>408.18</v>
+      </c>
+      <c r="J22" s="80">
+        <f>IF(I22="","",I22/10000)</f>
+        <v>0.040818</v>
+      </c>
+      <c r="K22" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62 per impegni immediati unisex (40% uomini, 60% donne), tasso tecnico 0% (tabella A-quater)</t>
+        </is>
+      </c>
+      <c r="M22" s="80" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="N22" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="79" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q22" s="79" t="n"/>
+      <c r="R22" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi</t>
+        </is>
+      </c>
+      <c r="S22" s="67" t="inlineStr">
+        <is>
+          <t>Rate annuali, trimestrali o mensili; comparto predefinito Garanzia 1+; 50 € all'attivazione e 2 € a rata</t>
+        </is>
+      </c>
+      <c r="T22" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U22" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V22" s="67" t="inlineStr">
+        <is>
+          <t>La convenzione per le rendite scade il 31/12/2026: i coefficienti potrebbero cambiare. Costo della rendita dallo 0,90% (annuale) al 2% (mensile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="67" t="str">
+        <f>Sheet1!$A$24</f>
+        <v>SECONDAPENSIONE FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B23" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite</t>
+        </is>
+      </c>
+      <c r="C23" s="67" t="inlineStr">
+        <is>
+          <t>Crédit Agricole Vita S.p.A.</t>
+        </is>
+      </c>
+      <c r="D23" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E23" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="F23" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="G23" s="67" t="inlineStr">
+        <is>
+          <t>Sì (rendita raddoppiata)</t>
+        </is>
+      </c>
+      <c r="H23" s="78">
+        <f>COUNTIF(D23:G23,"Sì*")</f>
+        <v>4</v>
+      </c>
+      <c r="I23" s="79" t="n">
+        <v>443.46</v>
+      </c>
+      <c r="J23" s="80">
+        <f>IF(I23="","",I23/10000)</f>
+        <v>0.044346</v>
+      </c>
+      <c r="K23" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62I (60% uomini, 40% donne), nati 1958–1966 senza correzione, tasso tecnico 0%, rate annuali anticipate (22,5498 € per 1 € di rendita)</t>
+        </is>
+      </c>
+      <c r="M23" s="80" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="N23" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="79" t="n"/>
+      <c r="R23" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi</t>
+        </is>
+      </c>
+      <c r="S23" s="67" t="inlineStr">
+        <is>
+          <t>Rate trimestrali, semestrali o annuali; comparto predefinito SecondaPensione Prudente ESG</t>
+        </is>
+      </c>
+      <c r="T23" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U23" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V23" s="67" t="inlineStr">
+        <is>
+          <t>Costo della rendita 0,80% più 0,10% per ogni rata nell'anno. Nessuna spesa per anticipazioni, riscatti e trasferimenti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="67" t="str">
+        <f>Sheet1!$A$25</f>
+        <v>FONDO PENSIONE APERTO GIUSTINIANO</v>
+      </c>
+      <c r="B24" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C24" s="67" t="inlineStr">
+        <is>
+          <t>Intesa Sanpaolo Assicurazioni S.p.A.</t>
+        </is>
+      </c>
+      <c r="D24" s="67" t="inlineStr">
+        <is>
+          <t>Sì (100% o 50%)</t>
+        </is>
+      </c>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F24" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="G24" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" s="78">
+        <f>COUNTIF(D24:G24,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I24" s="79" t="n">
+        <v>429.1</v>
+      </c>
+      <c r="J24" s="80">
+        <f>IF(I24="","",I24/10000)</f>
+        <v>0.042910000000000004</v>
+      </c>
+      <c r="K24" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62D/A per anno di nascita (nati 1958–1966 senza correzione), tasso tecnico 0%</t>
+        </is>
+      </c>
+      <c r="M24" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N24" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="O24" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="P24" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q24" s="79" t="n"/>
+      <c r="R24" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (marzo 2026)</t>
+        </is>
+      </c>
+      <c r="S24" s="67" t="inlineStr">
+        <is>
+          <t>Rate mensili, trimestrali o annuali (minimo 150 € a rata); comparto predefinito Giustiniano Monetaria; 20 € per accedere, 2 € a rata</t>
+        </is>
+      </c>
+      <c r="T24" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U24" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V24" s="67" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="67" t="str">
+        <f>Sheet1!$A$26</f>
+        <v>PROGRAMMA OPEN FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B25" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C25" s="67" t="inlineStr">
+        <is>
+          <t>Groupama Assicurazioni S.p.A.</t>
+        </is>
+      </c>
+      <c r="D25" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E25" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5, 10 o 15 anni)</t>
+        </is>
+      </c>
+      <c r="F25" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G25" s="67" t="inlineStr">
+        <is>
+          <t>Sì (+20%, costo 5% della posizione)</t>
+        </is>
+      </c>
+      <c r="H25" s="78">
+        <f>COUNTIF(D25:G25,"Sì*")</f>
+        <v>3</v>
+      </c>
+      <c r="I25" s="79" t="n">
+        <v>431.78</v>
+      </c>
+      <c r="J25" s="80">
+        <f>IF(I25="","",I25/10000)</f>
+        <v>0.043177999999999994</v>
+      </c>
+      <c r="K25" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="67" t="inlineStr">
+        <is>
+          <t>Tavola ANIA 2005 unificata per sesso (iscritti dal 21/12/2012), nati 1949–1960, tasso tecnico 0%</t>
+        </is>
+      </c>
+      <c r="M25" s="80" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N25" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="79" t="n"/>
+      <c r="Q25" s="79" t="n"/>
+      <c r="R25" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (marzo 2026)</t>
+        </is>
+      </c>
+      <c r="S25" s="67" t="inlineStr">
+        <is>
+          <t>Rate trimestrali, semestrali o annuali; comparto predefinito Nuovo Obbligazionario Etico; 15 € a rata</t>
+        </is>
+      </c>
+      <c r="T25" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U25" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V25" s="67" t="inlineStr">
+        <is>
+          <t>Anticipazioni e riscatti senza spese; il testo estratto della Scheda costi non riporta gli importi per trasferimento e RITA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="67" t="str">
+        <f>Sheet1!$A$27</f>
+        <v>FONDO PENSIONE APERTO IL MIO DOMANI</v>
+      </c>
+      <c r="B26" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C26" s="67" t="inlineStr">
+        <is>
+          <t>Intesa Sanpaolo Assicurazioni S.p.A.</t>
+        </is>
+      </c>
+      <c r="D26" s="67" t="inlineStr">
+        <is>
+          <t>Sì (100% o 50%)</t>
+        </is>
+      </c>
+      <c r="E26" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>Sì (80% del capitale)</t>
+        </is>
+      </c>
+      <c r="G26" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" s="78">
+        <f>COUNTIF(D26:G26,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I26" s="79" t="n">
+        <v>429.1</v>
+      </c>
+      <c r="J26" s="80">
+        <f>IF(I26="","",I26/10000)</f>
+        <v>0.042910000000000004</v>
+      </c>
+      <c r="K26" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62D/A per anno di nascita (nati 1958–1966 senza correzione), tasso tecnico 0% (tabella A: 42,91 € per 1.000 €)</t>
+        </is>
+      </c>
+      <c r="M26" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N26" s="79" t="n"/>
+      <c r="O26" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="P26" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q26" s="79" t="n"/>
+      <c r="R26" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (marzo 2026)</t>
+        </is>
+      </c>
+      <c r="S26" s="67" t="inlineStr">
+        <is>
+          <t>Rate mensili, trimestrali o annuali (minimo 150 € a rata); comparto predefinito Linea Breve Termine; durata anche più lunga della vita attesa; 20 € per accedere, 2 € a rata</t>
+        </is>
+      </c>
+      <c r="T26" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U26" s="83" t="n">
+        <v>46304</v>
+      </c>
+      <c r="V26" s="67" t="inlineStr">
+        <is>
+          <t>Stessi coefficienti di Previdsystem e Giustiniano (stessa compagnia). Il testo estratto della Scheda costi non riporta il costo dell'anticipazione.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="67" t="str">
+        <f>Sheet1!$A$28</f>
+        <v>AZIMUT PREVIDENZA - FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B27" s="67" t="n"/>
+      <c r="C27" s="67" t="n"/>
+      <c r="D27" s="67" t="n"/>
+      <c r="E27" s="67" t="n"/>
+      <c r="F27" s="67" t="n"/>
+      <c r="G27" s="67" t="n"/>
+      <c r="H27" s="78">
+        <f>COUNTIF(D27:G27,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="79" t="n"/>
+      <c r="J27" s="80" t="str">
+        <f>IF(I27="","",I27/10000)</f>
+        <v/>
+      </c>
+      <c r="K27" s="81" t="n"/>
+      <c r="L27" s="67" t="n"/>
+      <c r="M27" s="80" t="n"/>
+      <c r="N27" s="79" t="n"/>
+      <c r="O27" s="79" t="n"/>
+      <c r="P27" s="79" t="n"/>
+      <c r="Q27" s="79" t="n"/>
+      <c r="R27" s="67" t="n"/>
+      <c r="S27" s="67" t="n"/>
+      <c r="T27" s="67" t="n"/>
+      <c r="U27" s="83" t="n"/>
+      <c r="V27" s="67" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="67" t="str">
+        <f>Sheet1!$A$29</f>
+        <v>AZIONE DI PREVIDENZA - FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B28" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C28" s="67" t="inlineStr">
+        <is>
+          <t>HDI Assicurazioni S.p.A.</t>
+        </is>
+      </c>
+      <c r="D28" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E28" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F28" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="G28" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="78">
+        <f>COUNTIF(D28:G28,"Sì*")</f>
+        <v>3</v>
+      </c>
+      <c r="I28" s="79" t="n">
+        <v>441.45</v>
+      </c>
+      <c r="J28" s="80">
+        <f>IF(I28="","",I28/10000)</f>
+        <v>0.044145</v>
+      </c>
+      <c r="K28" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62D (70% uomini, 30% donne), nati 1958–1966 senza correzione, tasso tecnico 0% (Regolamento, tabella A: 22,6524 € per 1 € di rendita)</t>
+        </is>
+      </c>
+      <c r="M28" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N28" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="79" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q28" s="79" t="n"/>
+      <c r="R28" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="S28" s="67" t="inlineStr">
+        <is>
+          <t>Rate annuali, semestrali, trimestrali o mensili; prelievo minimo 2.000 € (o la rendita figurativa se inferiore); 25 € a rata per la rendita a durata definita</t>
+        </is>
+      </c>
+      <c r="T28" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U28" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V28" s="67" t="inlineStr">
+        <is>
+          <t>Coefficienti nel Regolamento (luglio 2026), espressi come capitale necessario per 1 € di rendita annua.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="67" t="str">
+        <f>Sheet1!$A$30</f>
+        <v>FONDO PENSIONE APERTO CNP</v>
+      </c>
+      <c r="B29" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C29" s="67" t="inlineStr">
+        <is>
+          <t>CNP Vita Assicura S.p.A.</t>
+        </is>
+      </c>
+      <c r="D29" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E29" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F29" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="78">
+        <f>COUNTIF(D29:G29,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I29" s="79" t="n"/>
+      <c r="J29" s="80" t="str">
+        <f>IF(I29="","",I29/10000)</f>
+        <v/>
+      </c>
+      <c r="K29" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62D ponderata 40% uomini e 60% donne (adesioni individuali), tasso tecnico 0%</t>
+        </is>
+      </c>
+      <c r="M29" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N29" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="79" t="n"/>
+      <c r="R29" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, I costi (marzo 2026)</t>
+        </is>
+      </c>
+      <c r="S29" s="67" t="inlineStr">
+        <is>
+          <t>Rate annuali o semestrali (minimo 500 € a semestre); comparto predefinito con garanzia di restituzione del capitale; 6 € a rata</t>
+        </is>
+      </c>
+      <c r="T29" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U29" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V29" s="67" t="inlineStr">
+        <is>
+          <t>Coefficienti numerici non pubblicati nei documenti consultati (basi tecniche dal documento sulle proiezioni pensionistiche).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="67" t="str">
+        <f>Sheet1!$A$31</f>
+        <v>INSIEME - FONDO PENSIONE APERTO A CONTRIBUZIONE DEFINITA</v>
+      </c>
+      <c r="B30" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C30" s="67" t="inlineStr">
+        <is>
+          <t>Allianz S.p.A.</t>
+        </is>
+      </c>
+      <c r="D30" s="67" t="inlineStr">
+        <is>
+          <t>Sì (100% o 60%)</t>
+        </is>
+      </c>
+      <c r="E30" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F30" s="67" t="inlineStr">
+        <is>
+          <t>Sì (cashback)</t>
+        </is>
+      </c>
+      <c r="G30" s="67" t="inlineStr">
+        <is>
+          <t>Sì (rendita raddoppiata, con questionario medico)</t>
+        </is>
+      </c>
+      <c r="H30" s="78">
+        <f>COUNTIF(D30:G30,"Sì*")</f>
+        <v>4</v>
+      </c>
+      <c r="I30" s="79" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="J30" s="80">
+        <f>IF(I30="","",I30/10000)</f>
+        <v>0.04625</v>
+      </c>
+      <c r="K30" s="81" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L30" s="67" t="inlineStr">
+        <is>
+          <t>Tavola AZPS62, nati 1955–1962 senza correzione d'età, tasso tecnico 0,5% (stessi coefficienti di Allianz Previdenza)</t>
+        </is>
+      </c>
+      <c r="M30" s="80" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="N30" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (settembre 2026)</t>
+        </is>
+      </c>
+      <c r="S30" s="67" t="inlineStr">
+        <is>
+          <t>Rendita a durata definita a rate trimestrali (19 anni a 67 anni); prelievi ogni 3 mesi almeno, minimo 500 €; comparto predefinito Linea Flessibile con garanzia; nessuna spesa di erogazione</t>
+        </is>
+      </c>
+      <c r="T30" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (settembre 2026)</t>
+        </is>
+      </c>
+      <c r="U30" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V30" s="67" t="inlineStr">
+        <is>
+          <t>Costo della rendita dall'1,80% (rata annuale) al 3,30% (mensile); rivalutazione annua con 1,20 punti trattenuti dalla gestione separata VITARIV Group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="67" t="str">
+        <f>Sheet1!$A$32</f>
+        <v>FONDO PENSIONE APERTO BIM VITA</v>
+      </c>
+      <c r="B31" s="67" t="n"/>
+      <c r="C31" s="67" t="n"/>
+      <c r="D31" s="67" t="n"/>
+      <c r="E31" s="67" t="n"/>
+      <c r="F31" s="67" t="n"/>
+      <c r="G31" s="67" t="n"/>
+      <c r="H31" s="78">
+        <f>COUNTIF(D31:G31,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="79" t="n"/>
+      <c r="J31" s="80" t="str">
+        <f>IF(I31="","",I31/10000)</f>
+        <v/>
+      </c>
+      <c r="K31" s="81" t="n"/>
+      <c r="L31" s="67" t="n"/>
+      <c r="M31" s="80" t="n"/>
+      <c r="N31" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q31" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="S31" s="67" t="inlineStr">
+        <is>
+          <t>Prelievi ogni 3 mesi almeno, minimo 1.000 € lordi; rate di frazionamento da mensili ad annuali (solo annuali se la rata è sotto i 100 €)</t>
+        </is>
+      </c>
+      <c r="T31" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U31" s="83" t="n">
+        <v>46304</v>
+      </c>
+      <c r="V31" s="67" t="inlineStr">
+        <is>
+          <t>Oggi si chiama Unipol Fondo Pensione Aperto BV. Documento sulle rendite non trovato sul sito pubblico. RITA: 3 € su ogni rata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="67" t="str">
+        <f>Sheet1!$A$33</f>
+        <v>FONDO PENSIONE APERTO PENSPLAN PROFI</v>
+      </c>
+      <c r="B32" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite</t>
+        </is>
+      </c>
+      <c r="C32" s="67" t="inlineStr">
+        <is>
+          <t>ITAS Vita S.p.A.</t>
+        </is>
+      </c>
+      <c r="D32" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E32" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F32" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G32" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" s="78">
+        <f>COUNTIF(D32:G32,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I32" s="79" t="n"/>
+      <c r="J32" s="80" t="str">
+        <f>IF(I32="","",I32/10000)</f>
+        <v/>
+      </c>
+      <c r="K32" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62D, tasso tecnico 0%</t>
+        </is>
+      </c>
+      <c r="M32" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N32" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="R32" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi</t>
+        </is>
+      </c>
+      <c r="S32" s="67" t="inlineStr">
+        <is>
+          <t>Rate non più frequenti di trimestrali; comparto predefinito Ethical Life Short Term; nessun costo per accedere; durata anche più lunga della vita attesa</t>
+        </is>
+      </c>
+      <c r="T32" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa</t>
+        </is>
+      </c>
+      <c r="U32" s="83" t="n">
+        <v>46304</v>
+      </c>
+      <c r="V32" s="67" t="inlineStr">
+        <is>
+          <t>I coefficienti non sono pubblicati nel documento sulle rendite (sono nella convenzione con ITAS Vita). Oltre all'1,25% di erogazione, caricamento dell'1% sul premio. RITA: 50 € per aprire la pratica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="67" t="str">
+        <f>Sheet1!$A$34</f>
+        <v>RAIFFEISEN FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B33" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite</t>
+        </is>
+      </c>
+      <c r="C33" s="67" t="inlineStr">
+        <is>
+          <t>Assimoco Vita S.p.A. (convenzione fino all'8/9/2030)</t>
+        </is>
+      </c>
+      <c r="D33" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E33" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5, 10 o 20 anni)</t>
+        </is>
+      </c>
+      <c r="F33" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G33" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" s="78">
+        <f>COUNTIF(D33:G33,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I33" s="79" t="n"/>
+      <c r="J33" s="80" t="str">
+        <f>IF(I33="","",I33/10000)</f>
+        <v/>
+      </c>
+      <c r="K33" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="67" t="inlineStr">
+        <is>
+          <t>Tavola IPS55U-I unisex, nati 1949–1960 senza correzione, tasso tecnico 0%</t>
+        </is>
+      </c>
+      <c r="M33" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N33" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q33" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi</t>
+        </is>
+      </c>
+      <c r="S33" s="67" t="inlineStr">
+        <is>
+          <t>Rate annuali, semestrali o trimestrali (minimo 2.000 € a rata, altrimenti meno frequenti); comparto predefinito Guaranty</t>
+        </is>
+      </c>
+      <c r="T33" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U33" s="83" t="n">
+        <v>46304</v>
+      </c>
+      <c r="V33" s="67" t="inlineStr">
+        <is>
+          <t>Il documento pubblica solo un esempio: a 67 anni, con rate mensili, 42,21 € l'anno ogni 1.000 € (422,10 € ogni 10.000 €); il coefficiente per rate annuali non è pubblicato. Oltre all'1,25% di erogazione, caricamento dell'1% sul premio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="67" t="str">
+        <f>Sheet1!$A$35</f>
+        <v>FONDO PENSIONE APERTO IL MELOGRANO</v>
+      </c>
+      <c r="B34" s="67" t="n"/>
+      <c r="C34" s="67" t="n"/>
+      <c r="D34" s="67" t="n"/>
+      <c r="E34" s="67" t="n"/>
+      <c r="F34" s="67" t="n"/>
+      <c r="G34" s="67" t="n"/>
+      <c r="H34" s="78">
+        <f>COUNTIF(D34:G34,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="79" t="n"/>
+      <c r="J34" s="80" t="str">
+        <f>IF(I34="","",I34/10000)</f>
+        <v/>
+      </c>
+      <c r="K34" s="81" t="n"/>
+      <c r="L34" s="67" t="n"/>
+      <c r="M34" s="80" t="n"/>
+      <c r="N34" s="79" t="n"/>
+      <c r="O34" s="79" t="n"/>
+      <c r="P34" s="79" t="n"/>
+      <c r="Q34" s="79" t="n"/>
+      <c r="R34" s="67" t="n"/>
+      <c r="S34" s="67" t="n"/>
+      <c r="T34" s="67" t="n"/>
+      <c r="U34" s="83" t="n"/>
+      <c r="V34" s="67" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="67" t="str">
+        <f>Sheet1!$A$36</f>
+        <v>FONDO PENSIONE APERTO UBI PREVIDENZA</v>
+      </c>
+      <c r="B35" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C35" s="67" t="inlineStr">
+        <is>
+          <t>Intesa Sanpaolo Assicurazioni S.p.A.</t>
+        </is>
+      </c>
+      <c r="D35" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E35" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F35" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" s="78">
+        <f>COUNTIF(D35:G35,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I35" s="79" t="n">
+        <v>453.5</v>
+      </c>
+      <c r="J35" s="80">
+        <f>IF(I35="","",I35/10000)</f>
+        <v>0.04535</v>
+      </c>
+      <c r="K35" s="81" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L35" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62D (40% uomini, 60% donne), adesioni dal 1/6/2017, nati 1958–1966 senza correzione, tasso tecnico 0,5% (Regolamento, allegato A1)</t>
+        </is>
+      </c>
+      <c r="M35" s="80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N35" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="79" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q35" s="79" t="n"/>
+      <c r="R35" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (marzo 2026)</t>
+        </is>
+      </c>
+      <c r="S35" s="67" t="inlineStr">
+        <is>
+          <t>Rate mensili, trimestrali o annuali (minimo 150 € a rata); comparto predefinito Capitale Sicuro</t>
+        </is>
+      </c>
+      <c r="T35" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U35" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V35" s="67" t="inlineStr">
+        <is>
+          <t>Tasso tecnico 0,5%: rata iniziale più alta, rivalutazioni successive più basse. Costo della rendita dall'1% (annuale) all'1,75% (bimestrale), più 2,58 € a rata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="67" t="str">
+        <f>Sheet1!$A$37</f>
+        <v>FONDO PENSIONE APERTO SOLUZIONE PREVIDENTE</v>
+      </c>
+      <c r="B36" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C36" s="67" t="inlineStr">
+        <is>
+          <t>Helvetia Vita S.p.A.</t>
+        </is>
+      </c>
+      <c r="D36" s="67" t="inlineStr">
+        <is>
+          <t>Sì (100% o 60%)</t>
+        </is>
+      </c>
+      <c r="E36" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni, anche reversibile)</t>
+        </is>
+      </c>
+      <c r="F36" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G36" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" s="78">
+        <f>COUNTIF(D36:G36,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I36" s="79" t="n">
+        <v>427.9</v>
+      </c>
+      <c r="J36" s="80">
+        <f>IF(I36="","",I36/10000)</f>
+        <v>0.042789999999999995</v>
+      </c>
+      <c r="K36" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62UI, nati 1958–1966 senza correzione, tasso tecnico 0% (tabella 1)</t>
+        </is>
+      </c>
+      <c r="M36" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N36" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="79" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q36" s="79" t="n">
+        <v>5</v>
+      </c>
+      <c r="R36" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (2026)</t>
+        </is>
+      </c>
+      <c r="S36" s="67" t="inlineStr">
+        <is>
+          <t>Rate trimestrali, quadrimestrali, semestrali o annuali; prelievo minimo 1.200 €; comparto predefinito Linea 1 Garantita; nessun costo per accedere</t>
+        </is>
+      </c>
+      <c r="T36" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U36" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V36" s="67" t="inlineStr">
+        <is>
+          <t>RITA: 5 € per ogni rata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="67" t="str">
+        <f>Sheet1!$A$38</f>
+        <v>BAP PENSIONE 2007 FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B37" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C37" s="67" t="inlineStr">
+        <is>
+          <t>Intesa Sanpaolo Assicurazioni S.p.A.</t>
+        </is>
+      </c>
+      <c r="D37" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E37" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F37" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G37" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" s="78">
+        <f>COUNTIF(D37:G37,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I37" s="79" t="n">
+        <v>461.32</v>
+      </c>
+      <c r="J37" s="80">
+        <f>IF(I37="","",I37/10000)</f>
+        <v>0.046132</v>
+      </c>
+      <c r="K37" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="67" t="inlineStr">
+        <is>
+          <t>Tavola IPS55U-I unisex, nati 1947–1960 senza correzione, tasso tecnico 0% (Regolamento, tabelle)</t>
+        </is>
+      </c>
+      <c r="M37" s="80" t="n"/>
+      <c r="N37" s="79" t="n">
+        <v>25</v>
+      </c>
+      <c r="O37" s="79" t="n">
+        <v>25</v>
+      </c>
+      <c r="P37" s="79" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q37" s="79" t="n"/>
+      <c r="R37" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (marzo 2026)</t>
+        </is>
+      </c>
+      <c r="S37" s="67" t="inlineStr">
+        <is>
+          <t>Rate mensili, trimestrali o annuali (minimo 150 € a rata); comparto predefinito BAP Pensione TFR; 20 € per accedere, 2 € a rata</t>
+        </is>
+      </c>
+      <c r="T37" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U37" s="83" t="n">
+        <v>46303</v>
+      </c>
+      <c r="V37" s="67" t="inlineStr">
+        <is>
+          <t>Tavola IPS55, più datata delle A62: ipotizza una vita più breve e quindi una rata più alta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="67" t="str">
+        <f>Sheet1!$A$39</f>
+        <v>CORE PENSION FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B38" s="67" t="n"/>
+      <c r="C38" s="67" t="n"/>
+      <c r="D38" s="67" t="n"/>
+      <c r="E38" s="67" t="n"/>
+      <c r="F38" s="67" t="n"/>
+      <c r="G38" s="67" t="n"/>
+      <c r="H38" s="78">
+        <f>COUNTIF(D38:G38,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="79" t="n"/>
+      <c r="J38" s="80" t="str">
+        <f>IF(I38="","",I38/10000)</f>
+        <v/>
+      </c>
+      <c r="K38" s="81" t="n"/>
+      <c r="L38" s="67" t="n"/>
+      <c r="M38" s="80" t="n"/>
+      <c r="N38" s="79" t="n"/>
+      <c r="O38" s="79" t="n"/>
+      <c r="P38" s="79" t="n"/>
+      <c r="Q38" s="79" t="n"/>
+      <c r="R38" s="67" t="n"/>
+      <c r="S38" s="67" t="n"/>
+      <c r="T38" s="67" t="n"/>
+      <c r="U38" s="83" t="n"/>
+      <c r="V38" s="67" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="67" t="str">
+        <f>Sheet1!$A$40</f>
+        <v>AZIMUT SUSTAINABLE FUTURE - FONDO PENSIONE APERTO</v>
+      </c>
+      <c r="B39" s="67" t="n"/>
+      <c r="C39" s="67" t="n"/>
+      <c r="D39" s="67" t="n"/>
+      <c r="E39" s="67" t="n"/>
+      <c r="F39" s="67" t="n"/>
+      <c r="G39" s="67" t="n"/>
+      <c r="H39" s="78">
+        <f>COUNTIF(D39:G39,"Sì*")</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="79" t="n"/>
+      <c r="J39" s="80" t="str">
+        <f>IF(I39="","",I39/10000)</f>
+        <v/>
+      </c>
+      <c r="K39" s="81" t="n"/>
+      <c r="L39" s="67" t="n"/>
+      <c r="M39" s="80" t="n"/>
+      <c r="N39" s="79" t="n"/>
+      <c r="O39" s="79" t="n"/>
+      <c r="P39" s="79" t="n"/>
+      <c r="Q39" s="79" t="n"/>
+      <c r="R39" s="67" t="n"/>
+      <c r="S39" s="67" t="n"/>
+      <c r="T39" s="67" t="n"/>
+      <c r="U39" s="83" t="n"/>
+      <c r="V39" s="67" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:V39"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T21" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T23" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T24" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T25" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T26" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T28" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T29" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T30" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T31" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T37" r:id="rId67"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/fondi-pensione-covip.xlsx
+++ b/data/fondi-pensione-covip.xlsx
@@ -26,12 +26,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -13779,33 +13778,93 @@
         <f>Sheet1!$A$10</f>
         <v>DESTINAZIONE FUTURO - FONDO PENSIONE APERTO BY CREDEMVITA</v>
       </c>
-      <c r="B9" s="67" t="n"/>
-      <c r="C9" s="67" t="n"/>
-      <c r="D9" s="67" t="n"/>
-      <c r="E9" s="67" t="n"/>
-      <c r="F9" s="67" t="n"/>
-      <c r="G9" s="67" t="n"/>
+      <c r="B9" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C9" s="67" t="inlineStr">
+        <is>
+          <t>Credemvita S.p.A.</t>
+        </is>
+      </c>
+      <c r="D9" s="67" t="inlineStr">
+        <is>
+          <t>Sì (totale o parziale)</t>
+        </is>
+      </c>
+      <c r="E9" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F9" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="G9" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H9" s="78">
         <f>COUNTIF(D9:G9,"Sì*")</f>
+        <v>3</v>
+      </c>
+      <c r="I9" s="79" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="J9" s="80">
+        <f>IF(I9="","",I9/10000)</f>
+        <v>0.04205</v>
+      </c>
+      <c r="K9" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="79" t="n"/>
-      <c r="J9" s="80" t="str">
-        <f>IF(I9="","",I9/10000)</f>
-        <v/>
-      </c>
-      <c r="K9" s="81" t="n"/>
-      <c r="L9" s="67" t="n"/>
-      <c r="M9" s="80" t="n"/>
-      <c r="N9" s="79" t="n"/>
-      <c r="O9" s="79" t="n"/>
-      <c r="P9" s="79" t="n"/>
-      <c r="Q9" s="79" t="n"/>
-      <c r="R9" s="67" t="n"/>
-      <c r="S9" s="67" t="n"/>
-      <c r="T9" s="67" t="n"/>
-      <c r="U9" s="83" t="n"/>
-      <c r="V9" s="67" t="n"/>
+      <c r="L9" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62U unisex, nati 1958–1966 senza correzione d'età, tasso tecnico 0% (42,05 € per 1.000 €)</t>
+        </is>
+      </c>
+      <c r="M9" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="79" t="n">
+        <v>18</v>
+      </c>
+      <c r="R9" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi</t>
+        </is>
+      </c>
+      <c r="S9" s="67" t="inlineStr">
+        <is>
+          <t>Rate trimestrali, semestrali o annuali (minimo 1.000 € a rata, altrimenti meno frequenti); prelievi ogni 3 mesi almeno; comparto predefinito Prudente Garantito; 18 € a rata o prelievo</t>
+        </is>
+      </c>
+      <c r="T9" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U9" s="83" t="n">
+        <v>46305</v>
+      </c>
+      <c r="V9" s="67" t="inlineStr">
+        <is>
+          <t>Nessun costo per la gestione e l'erogazione della rendita vitalizia. RITA: 18 € su ogni rata.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="67" t="str">
@@ -13878,66 +13937,184 @@
         <f>Sheet1!$A$13</f>
         <v>FONDO PENSIONE APERTO UNIPOL PREVIDENZA FPA</v>
       </c>
-      <c r="B12" s="67" t="n"/>
-      <c r="C12" s="67" t="n"/>
-      <c r="D12" s="67" t="n"/>
-      <c r="E12" s="67" t="n"/>
-      <c r="F12" s="67" t="n"/>
-      <c r="G12" s="67" t="n"/>
+      <c r="B12" s="68" t="inlineStr">
+        <is>
+          <t>Documento sull'erogazione delle rendite (giugno 2025)</t>
+        </is>
+      </c>
+      <c r="C12" s="67" t="inlineStr">
+        <is>
+          <t>Unipol Assicurazioni S.p.A.</t>
+        </is>
+      </c>
+      <c r="D12" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E12" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F12" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H12" s="78">
         <f>COUNTIF(D12:G12,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I12" s="79" t="n">
+        <v>408.18</v>
+      </c>
+      <c r="J12" s="80">
+        <f>IF(I12="","",I12/10000)</f>
+        <v>0.040818</v>
+      </c>
+      <c r="K12" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="79" t="n"/>
-      <c r="J12" s="80" t="str">
-        <f>IF(I12="","",I12/10000)</f>
-        <v/>
-      </c>
-      <c r="K12" s="81" t="n"/>
-      <c r="L12" s="67" t="n"/>
-      <c r="M12" s="80" t="n"/>
-      <c r="N12" s="79" t="n"/>
-      <c r="O12" s="79" t="n"/>
-      <c r="P12" s="79" t="n"/>
-      <c r="Q12" s="79" t="n"/>
-      <c r="R12" s="67" t="n"/>
-      <c r="S12" s="67" t="n"/>
-      <c r="T12" s="67" t="n"/>
-      <c r="U12" s="83" t="n"/>
-      <c r="V12" s="67" t="n"/>
+      <c r="L12" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62I unisex (40% uomini, 60% donne), nati 1958–1966 senza correzione d'età, tasso tecnico 0% (24,4988 € per 1 € di rendita, adesioni individuali)</t>
+        </is>
+      </c>
+      <c r="M12" s="80" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="N12" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="O12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi</t>
+        </is>
+      </c>
+      <c r="S12" s="67" t="inlineStr">
+        <is>
+          <t>Rate da mensili ad annuali (solo annuali se la rata è sotto i 100 €); prelievi ogni 3 mesi almeno, minimo 1.000 € lordi</t>
+        </is>
+      </c>
+      <c r="T12" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa</t>
+        </is>
+      </c>
+      <c r="U12" s="83" t="n">
+        <v>46305</v>
+      </c>
+      <c r="V12" s="67" t="inlineStr">
+        <is>
+          <t>La prima anticipazione è gratuita, le successive costano 50 €. RITA: 3 € su ogni rata. Costo della rendita dallo 0,9% (annuale) al 2% (mensile). Stessi coefficienti di BIM Vita, Vera Vita e Arti &amp; Mestieri.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="67" t="str">
         <f>Sheet1!$A$14</f>
         <v>FONDO PENSIONE APERTO VERA VITA</v>
       </c>
-      <c r="B13" s="67" t="n"/>
-      <c r="C13" s="67" t="n"/>
-      <c r="D13" s="67" t="n"/>
-      <c r="E13" s="67" t="n"/>
-      <c r="F13" s="67" t="n"/>
-      <c r="G13" s="67" t="n"/>
+      <c r="B13" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (dicembre 2023)</t>
+        </is>
+      </c>
+      <c r="C13" s="67" t="inlineStr">
+        <is>
+          <t>Banco BPM Vita S.p.A.</t>
+        </is>
+      </c>
+      <c r="D13" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E13" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F13" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H13" s="78">
         <f>COUNTIF(D13:G13,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I13" s="79" t="n">
+        <v>408.18</v>
+      </c>
+      <c r="J13" s="80">
+        <f>IF(I13="","",I13/10000)</f>
+        <v>0.040818</v>
+      </c>
+      <c r="K13" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="79" t="n"/>
-      <c r="J13" s="80" t="str">
-        <f>IF(I13="","",I13/10000)</f>
-        <v/>
-      </c>
-      <c r="K13" s="81" t="n"/>
-      <c r="L13" s="67" t="n"/>
+      <c r="L13" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62I unisex (40% uomini, 60% donne), tasso tecnico 0% (24,4988 € per 1 € di rendita)</t>
+        </is>
+      </c>
       <c r="M13" s="80" t="n"/>
-      <c r="N13" s="79" t="n"/>
-      <c r="O13" s="79" t="n"/>
-      <c r="P13" s="79" t="n"/>
-      <c r="Q13" s="79" t="n"/>
-      <c r="R13" s="67" t="n"/>
-      <c r="S13" s="67" t="n"/>
-      <c r="T13" s="67" t="n"/>
-      <c r="U13" s="83" t="n"/>
-      <c r="V13" s="67" t="n"/>
+      <c r="N13" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="79" t="n">
+        <v>25</v>
+      </c>
+      <c r="P13" s="79" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q13" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi</t>
+        </is>
+      </c>
+      <c r="S13" s="67" t="inlineStr">
+        <is>
+          <t>Rate annuali, semestrali, trimestrali o mensili (minimo 600 € a rata, altrimenti meno frequenti); comparto predefinito Popolare Bond; 3 € a rata o prelievo</t>
+        </is>
+      </c>
+      <c r="T13" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U13" s="83" t="n">
+        <v>46305</v>
+      </c>
+      <c r="V13" s="67" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite del 2023, precedente alle nuove prestazioni. RITA: 3 € su ogni rata.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="67" t="str">
@@ -14126,24 +14303,56 @@
         <f>Sheet1!$A$17</f>
         <v>FONDO PENSIONE APERTO ZURICH CONTRIBUTION</v>
       </c>
-      <c r="B16" s="67" t="n"/>
-      <c r="C16" s="67" t="n"/>
-      <c r="D16" s="67" t="n"/>
-      <c r="E16" s="67" t="n"/>
-      <c r="F16" s="67" t="n"/>
-      <c r="G16" s="67" t="n"/>
+      <c r="B16" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C16" s="67" t="inlineStr">
+        <is>
+          <t>Zurich Investments Life S.p.A.</t>
+        </is>
+      </c>
+      <c r="D16" s="67" t="inlineStr">
+        <is>
+          <t>Sì (100% o 60%)</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 anni)</t>
+        </is>
+      </c>
+      <c r="F16" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H16" s="78">
         <f>COUNTIF(D16:G16,"Sì*")</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="79" t="n"/>
-      <c r="J16" s="80" t="str">
+        <v>2</v>
+      </c>
+      <c r="I16" s="79" t="n">
+        <v>421.6</v>
+      </c>
+      <c r="J16" s="80">
         <f>IF(I16="","",I16/10000)</f>
-        <v/>
+        <v>0.04216</v>
       </c>
       <c r="K16" s="81" t="n"/>
-      <c r="L16" s="67" t="n"/>
-      <c r="M16" s="80" t="n"/>
+      <c r="L16" s="67" t="inlineStr">
+        <is>
+          <t>Coefficienti nel Regolamento (allegato 2), nati 1958–1966 senza correzione d'età (42,16 € per 1.000 €); tavola e tasso tecnico non indicati</t>
+        </is>
+      </c>
+      <c r="M16" s="80" t="n">
+        <v>0.0125</v>
+      </c>
       <c r="N16" s="79" t="n">
         <v>0</v>
       </c>
@@ -14161,14 +14370,22 @@
           <t>Nota informativa, scheda I costi (marzo 2026)</t>
         </is>
       </c>
-      <c r="S16" s="67" t="n"/>
-      <c r="T16" s="67" t="n"/>
+      <c r="S16" s="67" t="inlineStr">
+        <is>
+          <t>Rate trimestrali, semestrali o annuali; prelievi una volta l'anno; comparto predefinito Linea Garantita; 2 € a rata o prelievo</t>
+        </is>
+      </c>
+      <c r="T16" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
       <c r="U16" s="83" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="V16" s="67" t="inlineStr">
         <is>
-          <t>Documento sulle rendite e supplemento non trovati sul sito pubblico. RITA: 2 € su ogni rata.</t>
+          <t>Oltre all'1,25% compreso nel coefficiente, 2,50 € su ogni rata di rendita e 0,75% trattenuto dal rendimento della gestione separata. RITA: 2 € su ogni rata.</t>
         </is>
       </c>
     </row>
@@ -14177,24 +14394,56 @@
         <f>Sheet1!$A$18</f>
         <v>ZED OMNIFUND - FONDO PENSIONE APERTO</v>
       </c>
-      <c r="B17" s="67" t="n"/>
-      <c r="C17" s="67" t="n"/>
-      <c r="D17" s="67" t="n"/>
-      <c r="E17" s="67" t="n"/>
-      <c r="F17" s="67" t="n"/>
-      <c r="G17" s="67" t="n"/>
+      <c r="B17" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C17" s="67" t="inlineStr">
+        <is>
+          <t>Zurich Investments Life S.p.A.</t>
+        </is>
+      </c>
+      <c r="D17" s="67" t="inlineStr">
+        <is>
+          <t>Sì (100% o 60%)</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F17" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H17" s="78">
         <f>COUNTIF(D17:G17,"Sì*")</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="79" t="n"/>
-      <c r="J17" s="80" t="str">
+        <v>1</v>
+      </c>
+      <c r="I17" s="79" t="n">
+        <v>421.6</v>
+      </c>
+      <c r="J17" s="80">
         <f>IF(I17="","",I17/10000)</f>
-        <v/>
+        <v>0.04216</v>
       </c>
       <c r="K17" s="81" t="n"/>
-      <c r="L17" s="67" t="n"/>
-      <c r="M17" s="80" t="n"/>
+      <c r="L17" s="67" t="inlineStr">
+        <is>
+          <t>Coefficienti nel Regolamento (allegato 2), nati 1958–1966 senza correzione d'età (42,16 € per 1.000 €); tavola e tasso tecnico non indicati</t>
+        </is>
+      </c>
+      <c r="M17" s="80" t="n">
+        <v>0.0125</v>
+      </c>
       <c r="N17" s="79" t="n">
         <v>0</v>
       </c>
@@ -14212,14 +14461,22 @@
           <t>Nota informativa, scheda I costi (marzo 2026)</t>
         </is>
       </c>
-      <c r="S17" s="67" t="n"/>
-      <c r="T17" s="67" t="n"/>
+      <c r="S17" s="67" t="inlineStr">
+        <is>
+          <t>Rate trimestrali, semestrali o annuali; prelievi una volta l'anno; comparto predefinito Linea Garantita; 2 € a rata o prelievo</t>
+        </is>
+      </c>
+      <c r="T17" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
       <c r="U17" s="83" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="V17" s="67" t="inlineStr">
         <is>
-          <t>Documento sulle rendite e supplemento non trovati sul sito pubblico. RITA: 2 € su ogni rata.</t>
+          <t>Oltre all'1,25% compreso nel coefficiente, 2,50 € su ogni rata di rendita e 0,75% trattenuto dal rendimento della gestione separata. RITA: 2 € su ogni rata.</t>
         </is>
       </c>
     </row>
@@ -14334,33 +14591,93 @@
         <f>Sheet1!$A$21</f>
         <v>FONDO PENSIONE APERTO AUREO</v>
       </c>
-      <c r="B20" s="67" t="n"/>
-      <c r="C20" s="67" t="n"/>
-      <c r="D20" s="67" t="n"/>
-      <c r="E20" s="67" t="n"/>
-      <c r="F20" s="67" t="n"/>
-      <c r="G20" s="67" t="n"/>
+      <c r="B20" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite</t>
+        </is>
+      </c>
+      <c r="C20" s="67" t="inlineStr">
+        <is>
+          <t>Assimoco Vita S.p.A.</t>
+        </is>
+      </c>
+      <c r="D20" s="67" t="inlineStr">
+        <is>
+          <t>Sì (100%, 75% o 50%)</t>
+        </is>
+      </c>
+      <c r="E20" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F20" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H20" s="78">
         <f>COUNTIF(D20:G20,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I20" s="79" t="n">
+        <v>430.6</v>
+      </c>
+      <c r="J20" s="80">
+        <f>IF(I20="","",I20/10000)</f>
+        <v>0.04306</v>
+      </c>
+      <c r="K20" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="79" t="n"/>
-      <c r="J20" s="80" t="str">
-        <f>IF(I20="","",I20/10000)</f>
-        <v/>
-      </c>
-      <c r="K20" s="81" t="n"/>
-      <c r="L20" s="67" t="n"/>
-      <c r="M20" s="80" t="n"/>
-      <c r="N20" s="79" t="n"/>
-      <c r="O20" s="79" t="n"/>
-      <c r="P20" s="79" t="n"/>
-      <c r="Q20" s="79" t="n"/>
-      <c r="R20" s="67" t="n"/>
-      <c r="S20" s="67" t="n"/>
-      <c r="T20" s="67" t="n"/>
-      <c r="U20" s="83" t="n"/>
-      <c r="V20" s="67" t="n"/>
+      <c r="L20" s="67" t="inlineStr">
+        <is>
+          <t>Tavola IPS55U-I unisex, nati 1949–1960 senza correzione d'età, tasso tecnico 0% (43,06 € per 1.000 €)</t>
+        </is>
+      </c>
+      <c r="M20" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N20" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="79" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q20" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi</t>
+        </is>
+      </c>
+      <c r="S20" s="67" t="inlineStr">
+        <is>
+          <t>Rate mensili, trimestrali, semestrali o annuali (minimo 100 € a rata, altrimenti meno frequenti)</t>
+        </is>
+      </c>
+      <c r="T20" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U20" s="83" t="n">
+        <v>46305</v>
+      </c>
+      <c r="V20" s="67" t="inlineStr">
+        <is>
+          <t>Le nuove prestazioni sono descritte nell'«Integrazione documento Rendite» pubblicata accanto al documento. Stessa compagnia e stesse basi tecniche di Raiffeisen (IPS55U-I, tasso tecnico 0%).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="67" t="str">
@@ -14895,33 +15212,91 @@
         <f>Sheet1!$A$28</f>
         <v>AZIMUT PREVIDENZA - FONDO PENSIONE APERTO</v>
       </c>
-      <c r="B27" s="67" t="n"/>
-      <c r="C27" s="67" t="n"/>
-      <c r="D27" s="67" t="n"/>
-      <c r="E27" s="67" t="n"/>
-      <c r="F27" s="67" t="n"/>
-      <c r="G27" s="67" t="n"/>
+      <c r="B27" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (valido dal 1/1/2025, aggiornato al 31/7/2026)</t>
+        </is>
+      </c>
+      <c r="C27" s="67" t="inlineStr">
+        <is>
+          <t>Generali Italia S.p.A.</t>
+        </is>
+      </c>
+      <c r="D27" s="67" t="inlineStr">
+        <is>
+          <t>Sì (100% o 60%)</t>
+        </is>
+      </c>
+      <c r="E27" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F27" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="G27" s="67" t="inlineStr">
+        <is>
+          <t>Sì (rendita raddoppiata)</t>
+        </is>
+      </c>
       <c r="H27" s="78">
         <f>COUNTIF(D27:G27,"Sì*")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I27" s="79" t="n"/>
       <c r="J27" s="80" t="str">
         <f>IF(I27="","",I27/10000)</f>
         <v/>
       </c>
-      <c r="K27" s="81" t="n"/>
-      <c r="L27" s="67" t="n"/>
-      <c r="M27" s="80" t="n"/>
-      <c r="N27" s="79" t="n"/>
-      <c r="O27" s="79" t="n"/>
-      <c r="P27" s="79" t="n"/>
-      <c r="Q27" s="79" t="n"/>
-      <c r="R27" s="67" t="n"/>
-      <c r="S27" s="67" t="n"/>
-      <c r="T27" s="67" t="n"/>
-      <c r="U27" s="83" t="n"/>
-      <c r="V27" s="67" t="n"/>
+      <c r="K27" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62D con coefficienti distinti per uomini e donne, tasso tecnico 0% (0,5% per una delle tabelle della controassicurata)</t>
+        </is>
+      </c>
+      <c r="M27" s="80" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N27" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q27" s="79" t="n">
+        <v>30</v>
+      </c>
+      <c r="R27" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (aprile 2026)</t>
+        </is>
+      </c>
+      <c r="S27" s="67" t="inlineStr">
+        <is>
+          <t>Rate mensili, bimestrali, trimestrali, semestrali o annuali (minimo 250 € a rata, altrimenti meno frequenti); comparto predefinito Obbligazionario; 30 € per accedere, nessun costo a rata</t>
+        </is>
+      </c>
+      <c r="T27" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U27" s="83" t="n">
+        <v>46305</v>
+      </c>
+      <c r="V27" s="67" t="inlineStr">
+        <is>
+          <t>Coefficienti pubblicati distinti per uomini e donne (A62D, tasso tecnico 0%): a 67 anni 457,44 € (uomini) e 395,65 € (donne) l'anno ogni 10.000 €, non confrontabili con i coefficienti unisex degli altri fondi. Oltre all'1,25% sulle rate (1,50% con LTC), caricamento dello 0,50% sul premio. RITA: 30 € all'apertura della pratica.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="67" t="str">
@@ -15201,23 +15576,55 @@
         <f>Sheet1!$A$32</f>
         <v>FONDO PENSIONE APERTO BIM VITA</v>
       </c>
-      <c r="B31" s="67" t="n"/>
-      <c r="C31" s="67" t="n"/>
-      <c r="D31" s="67" t="n"/>
-      <c r="E31" s="67" t="n"/>
-      <c r="F31" s="67" t="n"/>
-      <c r="G31" s="67" t="n"/>
+      <c r="B31" s="68" t="inlineStr">
+        <is>
+          <t>Documento sull'erogazione delle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C31" s="67" t="inlineStr">
+        <is>
+          <t>Unipol Assicurazioni S.p.A.</t>
+        </is>
+      </c>
+      <c r="D31" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E31" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F31" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G31" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H31" s="78">
         <f>COUNTIF(D31:G31,"Sì*")</f>
+        <v>2</v>
+      </c>
+      <c r="I31" s="79" t="n">
+        <v>408.18</v>
+      </c>
+      <c r="J31" s="80">
+        <f>IF(I31="","",I31/10000)</f>
+        <v>0.040818</v>
+      </c>
+      <c r="K31" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="79" t="n"/>
-      <c r="J31" s="80" t="str">
-        <f>IF(I31="","",I31/10000)</f>
-        <v/>
-      </c>
-      <c r="K31" s="81" t="n"/>
-      <c r="L31" s="67" t="n"/>
+      <c r="L31" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62I unisex (40% uomini, 60% donne), tasso tecnico 0% (40,8184 € per 1.000 €)</t>
+        </is>
+      </c>
       <c r="M31" s="80" t="n"/>
       <c r="N31" s="79" t="n">
         <v>0</v>
@@ -15247,11 +15654,11 @@
         </is>
       </c>
       <c r="U31" s="83" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="V31" s="67" t="inlineStr">
         <is>
-          <t>Oggi si chiama Unipol Fondo Pensione Aperto BV. Documento sulle rendite non trovato sul sito pubblico. RITA: 3 € su ogni rata.</t>
+          <t>Oggi si chiama Unipol Fondo Pensione Aperto BV. RITA: 3 € su ogni rata.</t>
         </is>
       </c>
     </row>
@@ -15748,33 +16155,93 @@
         <f>Sheet1!$A$39</f>
         <v>CORE PENSION FONDO PENSIONE APERTO</v>
       </c>
-      <c r="B38" s="67" t="n"/>
-      <c r="C38" s="67" t="n"/>
-      <c r="D38" s="67" t="n"/>
-      <c r="E38" s="67" t="n"/>
-      <c r="F38" s="67" t="n"/>
-      <c r="G38" s="67" t="n"/>
+      <c r="B38" s="68" t="inlineStr">
+        <is>
+          <t>Documento sulle rendite (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="C38" s="67" t="inlineStr">
+        <is>
+          <t>Crédit Agricole Vita S.p.A.</t>
+        </is>
+      </c>
+      <c r="D38" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="E38" s="67" t="inlineStr">
+        <is>
+          <t>Sì (5 o 10 anni)</t>
+        </is>
+      </c>
+      <c r="F38" s="67" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="G38" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H38" s="78">
         <f>COUNTIF(D38:G38,"Sì*")</f>
+        <v>3</v>
+      </c>
+      <c r="I38" s="79" t="n">
+        <v>443.46</v>
+      </c>
+      <c r="J38" s="80">
+        <f>IF(I38="","",I38/10000)</f>
+        <v>0.044346</v>
+      </c>
+      <c r="K38" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="79" t="n"/>
-      <c r="J38" s="80" t="str">
-        <f>IF(I38="","",I38/10000)</f>
-        <v/>
-      </c>
-      <c r="K38" s="81" t="n"/>
-      <c r="L38" s="67" t="n"/>
-      <c r="M38" s="80" t="n"/>
-      <c r="N38" s="79" t="n"/>
-      <c r="O38" s="79" t="n"/>
-      <c r="P38" s="79" t="n"/>
-      <c r="Q38" s="79" t="n"/>
-      <c r="R38" s="67" t="n"/>
-      <c r="S38" s="67" t="n"/>
-      <c r="T38" s="67" t="n"/>
-      <c r="U38" s="83" t="n"/>
-      <c r="V38" s="67" t="n"/>
+      <c r="L38" s="67" t="inlineStr">
+        <is>
+          <t>Tavola A62I unisex, nati 1958–1966 senza correzione d'età, tasso tecnico 0%, rate annuali anticipate (22,5498 € per 1 € di rendita)</t>
+        </is>
+      </c>
+      <c r="M38" s="80" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="N38" s="79" t="n">
+        <v>10</v>
+      </c>
+      <c r="O38" s="79" t="n">
+        <v>10</v>
+      </c>
+      <c r="P38" s="79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="68" t="inlineStr">
+        <is>
+          <t>Nota informativa, scheda I costi (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="S38" s="67" t="inlineStr">
+        <is>
+          <t>Rate trimestrali, semestrali o annuali (minimo 500 € a rata, altrimenti meno frequenti); comparto predefinito Core Pension Obbligazionario Misto; nessun costo per accedere né a rata</t>
+        </is>
+      </c>
+      <c r="T38" s="68" t="inlineStr">
+        <is>
+          <t>Supplemento alla Nota informativa (luglio 2026)</t>
+        </is>
+      </c>
+      <c r="U38" s="83" t="n">
+        <v>46305</v>
+      </c>
+      <c r="V38" s="67" t="inlineStr">
+        <is>
+          <t>Stessi coefficienti di Secondapensione (stessa compagnia e stesse basi tecniche).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="67" t="str">
@@ -15827,58 +16294,81 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T7" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T21" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T23" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T24" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T25" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T26" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T28" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T29" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T30" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T31" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T35" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T36" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T37" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T14" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T16" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T17" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T20" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T21" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T23" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T24" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T25" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T26" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T27" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T28" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T29" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T30" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T31" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T32" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T33" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T35" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T36" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T37" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T38" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
